--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -760,7 +760,7 @@
         <v>3.35</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="H2" t="n">
         <v>1.78</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 01:09:10</t>
+          <t>2026-04-28 03:16:11</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G2" t="n">
         <v>5.4</v>
@@ -772,7 +772,7 @@
         <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -790,7 +790,7 @@
         <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
         <v>1.17</v>
       </c>
       <c r="G3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="H3" t="n">
         <v>15</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="Q4" t="n">
         <v>1.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 03:16:11</t>
+          <t>2026-04-28 05:23:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="I2" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,10 +787,10 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>1.7</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 05:23:04</t>
+          <t>2026-04-28 07:30:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH4"/>
+  <dimension ref="A1:BH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,191 +743,191 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>04:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Beijing Tech FC</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,378 +937,960 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>4.2</v>
+        <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 07:30:14</t>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Chinese League 2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>08:30:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Lanzhou Longyuan Athletic</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Haimen Codion</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>Saudi Professional League</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Al-Akhdoud</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H6" t="n">
+        <v>15</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22</v>
+      </c>
+      <c r="J6" t="n">
+        <v>9</v>
+      </c>
+      <c r="K6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>Al-Kholood Club</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Al-Feiha</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F7" t="n">
         <v>2.38</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G7" t="n">
         <v>3.4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H7" t="n">
         <v>2.36</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I7" t="n">
         <v>2.82</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J7" t="n">
         <v>3.05</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K7" t="n">
         <v>6.6</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q7" t="n">
         <v>1.7</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>2026-04-28 07:30:14</t>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-28 09:38:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH7"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,10 +769,10 @@
         <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,22 +781,22 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -963,10 +963,10 @@
         <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
@@ -984,7 +984,7 @@
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>1.02</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1169,7 +1169,7 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
@@ -1178,7 +1178,7 @@
         <v>1.07</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R4" t="n">
         <v>1.07</v>
@@ -1253,52 +1253,52 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF4" t="n">
         <v>1.01</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.85</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.15</v>
+        <v>3.8</v>
       </c>
       <c r="G6" t="n">
-        <v>1.19</v>
+        <v>5.1</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>1.85</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>2.02</v>
       </c>
       <c r="J6" t="n">
-        <v>9</v>
+        <v>3.85</v>
       </c>
       <c r="K6" t="n">
-        <v>11.5</v>
+        <v>4.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>4.4</v>
+        <v>2.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,201 +1696,395 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 09:38:52</t>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="H7" t="n">
+        <v>15</v>
+      </c>
+      <c r="I7" t="n">
+        <v>22</v>
+      </c>
+      <c r="J7" t="n">
+        <v>9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:47:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Saudi Professional League</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Al-Kholood Club</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Al-Feiha</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" t="n">
         <v>2.38</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" t="n">
         <v>3.4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" t="n">
         <v>2.36</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>2.82</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>3.05</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" t="n">
         <v>6.6</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q8" t="n">
         <v>1.7</v>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2026-04-28 09:38:52</t>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:47:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,19 +784,19 @@
         <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P2" t="n">
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1366,7 +1366,7 @@
         <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5" t="n">
         <v>1.07</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,186 +1524,186 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X6" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>42</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF6" t="n">
         <v>3.8</v>
       </c>
-      <c r="G6" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="I6" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,184 +1713,184 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1.19</v>
+        <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>1.02</v>
       </c>
       <c r="K7" t="n">
-        <v>11.5</v>
+        <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 11:47:23</t>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>
@@ -1907,184 +1907,572 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Al-Akhdoud</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Al-Ettifaq</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X8" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n">
+        <v>24</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K9" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>Al-Kholood Club</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Al-Feiha</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>2.38</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G10" t="n">
         <v>3.4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H10" t="n">
         <v>2.36</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I10" t="n">
         <v>2.82</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J10" t="n">
         <v>3.05</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K10" t="n">
         <v>6.6</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q8" t="n">
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q10" t="n">
         <v>1.7</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2026-04-28 11:47:23</t>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-28 13:56:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH10"/>
+  <dimension ref="A1:BH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,19 +784,19 @@
         <v>1.01</v>
       </c>
       <c r="O2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="P2" t="n">
         <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="R2" t="n">
         <v>1.07</v>
       </c>
       <c r="S2" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L6" t="n">
         <v>1.21</v>
@@ -1557,43 +1557,43 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="X6" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1602,101 +1602,101 @@
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
         <v>12.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AJ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK6" t="n">
         <v>16</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>16.5</v>
       </c>
       <c r="AL6" t="n">
         <v>32</v>
       </c>
       <c r="AM6" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.8</v>
+        <v>2.58</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>3.95</v>
       </c>
       <c r="G8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I8" t="n">
         <v>2.02</v>
@@ -1972,10 +1972,10 @@
         <v>1.98</v>
       </c>
       <c r="W8" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Y8" t="n">
         <v>15.5</v>
@@ -1990,7 +1990,7 @@
         <v>22</v>
       </c>
       <c r="AC8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD8" t="n">
         <v>15</v>
@@ -2026,10 +2026,10 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.3</v>
+        <v>2.78</v>
       </c>
       <c r="AQ8" t="n">
         <v>9</v>
@@ -2038,60 +2038,60 @@
         <v>9.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.36</v>
+        <v>2.92</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="BA8" t="n">
         <v>20</v>
       </c>
       <c r="BB8" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="BD8" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.44</v>
+        <v>3.05</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>7.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,373 +2106,955 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.14</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1.17</v>
+        <v>2.88</v>
       </c>
       <c r="H9" t="n">
-        <v>20</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>9.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>12.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P9" t="n">
-        <v>4.5</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.26</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 13:56:30</t>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Norwegian Eliteserien</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bodo Glimt</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Start</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Concarneau</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Paris 13 Atletico</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>French National</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:30:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Dijon</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Chateauroux</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Saudi Professional League</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>15:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>Al-Kholood Club</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Al-Feiha</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G10" t="n">
+      <c r="F13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G13" t="n">
         <v>3.4</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="I10" t="n">
+      <c r="H13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="I13" t="n">
         <v>2.82</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="J13" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="O13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q13" t="n">
         <v>1.7</v>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-04-28 13:56:30</t>
+      <c r="R13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>2026-04-28 16:05:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH13"/>
+  <dimension ref="A1:BH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1536,16 +1536,16 @@
         <v>1.37</v>
       </c>
       <c r="G6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="K6" t="n">
         <v>7.6</v>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="O6" t="n">
         <v>1.14</v>
@@ -1566,7 +1566,7 @@
         <v>2.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="R6" t="n">
         <v>1.75</v>
@@ -1575,7 +1575,7 @@
         <v>1.98</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1599,22 +1599,22 @@
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>36</v>
       </c>
       <c r="AE6" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>26</v>
@@ -1623,10 +1623,10 @@
         <v>90</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AL6" t="n">
         <v>32</v>
@@ -1653,7 +1653,7 @@
         <v>5.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AU6" t="n">
         <v>4</v>
@@ -1668,7 +1668,7 @@
         <v>3.75</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AZ6" t="n">
         <v>4.4</v>
@@ -1677,7 +1677,7 @@
         <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
         <v>2.18</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
         <v>2.78</v>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.78</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>1.37</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
         <v>2.3</v>
       </c>
       <c r="S10" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="T10" t="n">
         <v>1.67</v>
@@ -2411,34 +2411,34 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>2.86</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.46</v>
+        <v>2.98</v>
       </c>
       <c r="AU10" t="n">
         <v>18</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.52</v>
+        <v>3.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="AX10" t="n">
         <v>9</v>
@@ -2447,32 +2447,32 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.39</v>
+        <v>2.7</v>
       </c>
       <c r="BC10" t="n">
         <v>9.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.5</v>
+        <v>3.15</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.55</v>
+        <v>1.86</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.55</v>
+        <v>3.35</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G11" t="n">
         <v>1.93</v>
@@ -2518,7 +2518,7 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2539,7 +2539,7 @@
         <v>2.06</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
         <v>3.35</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="R12" t="n">
         <v>1.06</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>
@@ -2897,40 +2897,40 @@
         <v>3.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.85</v>
+        <v>2.36</v>
       </c>
       <c r="I13" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="O13" t="n">
         <v>1.28</v>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>1.28</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.7</v>
+        <v>1.84</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="W13" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,783 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 16:05:14</t>
+          <t>2026-04-28 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>75</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-28 18:13:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1372,13 +1372,13 @@
         <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R5" t="n">
         <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1566,16 +1566,16 @@
         <v>2.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="R6" t="n">
         <v>1.75</v>
       </c>
       <c r="S6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
         <v>2.16</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1751,7 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2142,7 @@
         <v>3.05</v>
       </c>
       <c r="O9" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
         <v>1.78</v>
@@ -2151,7 +2151,7 @@
         <v>2.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="S9" t="n">
         <v>2.12</v>
@@ -2166,7 +2166,7 @@
         <v>1.46</v>
       </c>
       <c r="W9" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2351,10 +2351,10 @@
         <v>1.69</v>
       </c>
       <c r="T10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="U10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2378,10 +2378,10 @@
         <v>26</v>
       </c>
       <c r="AC10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AD10" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AE10" t="n">
         <v>1000</v>
@@ -2393,7 +2393,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2402,77 +2402,77 @@
         <v>13.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AU10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AW10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="AX10" t="n">
-        <v>9</v>
+        <v>2.62</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BB10" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="BC10" t="n">
         <v>9.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G11" t="n">
         <v>1.93</v>
@@ -2518,7 +2518,7 @@
         <v>3.45</v>
       </c>
       <c r="K11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2533,13 +2533,13 @@
         <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.06</v>
       </c>
       <c r="S11" t="n">
         <v>3.35</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>1.42</v>
       </c>
       <c r="G12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="H12" t="n">
         <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
         <v>6.6</v>
@@ -2727,10 +2727,10 @@
         <v>1.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.06</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
         <v>3.4</v>
@@ -2906,7 +2906,7 @@
         <v>2.98</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2924,13 +2924,13 @@
         <v>1.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.28</v>
+        <v>1.7</v>
       </c>
       <c r="R13" t="n">
         <v>1.12</v>
       </c>
       <c r="S13" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3085,10 +3085,10 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H14" t="n">
         <v>2.06</v>
@@ -3097,10 +3097,10 @@
         <v>2.08</v>
       </c>
       <c r="J14" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3130,13 +3130,13 @@
         <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V14" t="n">
         <v>1.92</v>
       </c>
       <c r="W14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X14" t="n">
         <v>12</v>
@@ -3217,7 +3217,7 @@
         <v>21</v>
       </c>
       <c r="AX14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY14" t="n">
         <v>15</v>
@@ -3241,14 +3241,14 @@
         <v>17.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
         <v>16.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.32</v>
       </c>
       <c r="H15" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
         <v>3.65</v>
@@ -3312,7 +3312,7 @@
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.31</v>
@@ -3330,7 +3330,7 @@
         <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X15" t="n">
         <v>12.5</v>
@@ -3345,7 +3345,7 @@
         <v>70</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>7.4</v>
@@ -3354,10 +3354,10 @@
         <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG15" t="n">
         <v>11</v>
@@ -3420,7 +3420,7 @@
         <v>17</v>
       </c>
       <c r="BA15" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BB15" t="n">
         <v>27</v>
@@ -3438,11 +3438,11 @@
         <v>19</v>
       </c>
       <c r="BG15" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3473,10 +3473,10 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.64</v>
-      </c>
-      <c r="G16" t="n">
-        <v>2.66</v>
       </c>
       <c r="H16" t="n">
         <v>3.05</v>
@@ -3497,13 +3497,13 @@
         <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q16" t="n">
         <v>2.12</v>
@@ -3512,10 +3512,10 @@
         <v>1.32</v>
       </c>
       <c r="S16" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
         <v>2.14</v>
@@ -3557,7 +3557,7 @@
         <v>12</v>
       </c>
       <c r="AH16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI16" t="n">
         <v>50</v>
@@ -3566,13 +3566,13 @@
         <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL16" t="n">
         <v>44</v>
       </c>
       <c r="AM16" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN16" t="n">
         <v>26</v>
@@ -3614,7 +3614,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB16" t="n">
         <v>34</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>
@@ -3670,28 +3670,28 @@
         <v>2.52</v>
       </c>
       <c r="G17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I17" t="n">
         <v>3.35</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="J17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
         <v>3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M17" t="n">
         <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.43</v>
@@ -3709,7 +3709,7 @@
         <v>4.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -3739,7 +3739,7 @@
         <v>7.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE17" t="n">
         <v>44</v>
@@ -3775,7 +3775,7 @@
         <v>48</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ17" t="n">
         <v>10</v>
@@ -3805,10 +3805,10 @@
         <v>11</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BB17" t="n">
         <v>32</v>
@@ -3817,7 +3817,7 @@
         <v>28</v>
       </c>
       <c r="BD17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BE17" t="n">
         <v>40</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 18:13:25</t>
+          <t>2026-04-28 20:21:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH17"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Shanghai Port B</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Taian Tiankuang</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -978,19 +978,19 @@
         <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.02</v>
+        <v>1.32</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.53</v>
+        <v>1.32</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1131,17 +1131,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>08:30:00</t>
+          <t>04:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lanzhou Longyuan Athletic</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Haimen Codion</t>
+          <t>Taian Tiankuang</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1184,7 +1184,7 @@
         <v>1.07</v>
       </c>
       <c r="S4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1330,12 +1330,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Guangdong Mingtu</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jiangxi Lushan</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1366,19 +1366,19 @@
         <v>1.01</v>
       </c>
       <c r="O5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
         <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.44</v>
+        <v>1.02</v>
       </c>
       <c r="R5" t="n">
         <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="T5" t="n">
         <v>1.01</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Jiangxi Lushan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.46</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>4.6</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="O6" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>2.66</v>
+        <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="R6" t="n">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="S6" t="n">
-        <v>1.96</v>
+        <v>1.44</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.58</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
         <v>15.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AA8" t="n">
         <v>30</v>
@@ -2029,69 +2029,69 @@
         <v>14.5</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>2.76</v>
       </c>
       <c r="AR8" t="n">
         <v>9.6</v>
       </c>
       <c r="AS8" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AW8" t="n">
         <v>2.84</v>
       </c>
-      <c r="AT8" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AX8" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="BA8" t="n">
         <v>20</v>
       </c>
       <c r="BB8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BD8" t="n">
         <v>3.05</v>
       </c>
-      <c r="BC8" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>3</v>
-      </c>
       <c r="BE8" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.07</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>1.18</v>
       </c>
       <c r="R9" t="n">
         <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>2.12</v>
+        <v>1.18</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.14</v>
       </c>
-      <c r="G10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="H10" t="n">
-        <v>20</v>
-      </c>
-      <c r="I10" t="n">
-        <v>24</v>
-      </c>
-      <c r="J10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.08</v>
-      </c>
       <c r="P10" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X10" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD10" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.94</v>
-      </c>
       <c r="BE10" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.89</v>
+        <v>2.68</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.64</v>
+        <v>2.66</v>
       </c>
       <c r="G11" t="n">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>4.9</v>
+        <v>2.78</v>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>2.12</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.42</v>
+        <v>1.14</v>
       </c>
       <c r="G12" t="n">
-        <v>1.52</v>
+        <v>1.17</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I12" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J12" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="K12" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2721,153 +2721,153 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.06</v>
+        <v>2.3</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W12" t="n">
         <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,60 +2877,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>3.4</v>
+        <v>1.93</v>
       </c>
       <c r="H13" t="n">
-        <v>2.36</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="J13" t="n">
-        <v>2.98</v>
+        <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>7.4</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.12</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>1.71</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>1.42</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.78</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G15" t="n">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>2.36</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5</v>
+        <v>5.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>1.83</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
         <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="S15" t="n">
-        <v>3.95</v>
+        <v>1.71</v>
       </c>
       <c r="T15" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.58</v>
       </c>
       <c r="W15" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>3.6</v>
       </c>
       <c r="O16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
         <v>1.87</v>
@@ -3614,7 +3614,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB16" t="n">
         <v>34</v>
@@ -3623,27 +3623,27 @@
         <v>27</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BF16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 20:21:32</t>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,179 +3658,567 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="G17" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="H17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N17" t="n">
         <v>3.3</v>
       </c>
-      <c r="I17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S17" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U17" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V17" t="n">
-        <v>1.42</v>
+        <v>1.92</v>
       </c>
       <c r="W17" t="n">
-        <v>1.64</v>
+        <v>1.31</v>
       </c>
       <c r="X17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD17" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y17" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AE17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH17" t="n">
         <v>21</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AI17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK17" t="n">
         <v>60</v>
       </c>
-      <c r="AB17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>32</v>
-      </c>
       <c r="AL17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AM17" t="n">
         <v>130</v>
       </c>
       <c r="AN17" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="AO17" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>13</v>
-      </c>
       <c r="AW17" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AY17" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
         <v>18.5</v>
       </c>
       <c r="BA17" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-04-28 22:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="X18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>19</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-04-28 22:29:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK19" t="n">
         <v>32</v>
       </c>
-      <c r="BB17" t="n">
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>29</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA19" t="n">
         <v>32</v>
       </c>
-      <c r="BC17" t="n">
+      <c r="BB19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC19" t="n">
         <v>28</v>
       </c>
-      <c r="BD17" t="n">
+      <c r="BD19" t="n">
         <v>44</v>
       </c>
-      <c r="BE17" t="n">
+      <c r="BE19" t="n">
         <v>40</v>
       </c>
-      <c r="BF17" t="n">
-        <v>26</v>
-      </c>
-      <c r="BG17" t="n">
+      <c r="BF19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BG19" t="n">
         <v>42</v>
       </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>2026-04-28 20:21:32</t>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-04-28 22:29:43</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -978,19 +978,19 @@
         <v>1.01</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,22 +1718,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
         <v>1000</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I7" t="n">
         <v>1000</v>
@@ -1751,22 +1751,22 @@
         <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.07</v>
       </c>
       <c r="S7" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,186 +1912,186 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.95</v>
+        <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>5</v>
+        <v>1.46</v>
       </c>
       <c r="H8" t="n">
-        <v>1.86</v>
+        <v>6.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.02</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.18</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="P8" t="n">
-        <v>2.18</v>
+        <v>2.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="T8" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="V8" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="X8" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="Y8" t="n">
-        <v>15.5</v>
+        <v>44</v>
       </c>
       <c r="Z8" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
         <v>970</v>
       </c>
-      <c r="AA8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>22</v>
-      </c>
       <c r="AC8" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AE8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH8" t="n">
         <v>26</v>
       </c>
-      <c r="AF8" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>24</v>
-      </c>
       <c r="AI8" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="AK8" t="n">
-        <v>65</v>
+        <v>970</v>
       </c>
       <c r="AL8" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
         <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>14.5</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.82</v>
+        <v>4.7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.76</v>
+        <v>4.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="AU8" t="n">
-        <v>2.64</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>2.74</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.84</v>
+        <v>5.1</v>
       </c>
       <c r="AX8" t="n">
-        <v>2.96</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>2.82</v>
+        <v>3.7</v>
       </c>
       <c r="AZ8" t="n">
-        <v>2.82</v>
+        <v>4.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>3.15</v>
+        <v>5</v>
       </c>
       <c r="BF8" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="BG8" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,28 +2106,28 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TSV Grafenstein</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
         <v>1000</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
         <v>1.07</v>
       </c>
       <c r="S9" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,79 +2300,79 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.46</v>
       </c>
-      <c r="H10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="S10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
         <v>1.98</v>
       </c>
-      <c r="T10" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W10" t="n">
-        <v>3.05</v>
+        <v>1.28</v>
       </c>
       <c r="X10" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>44</v>
+        <v>970</v>
       </c>
       <c r="Z10" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
@@ -2381,105 +2381,105 @@
         <v>970</v>
       </c>
       <c r="AD10" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>120</v>
+        <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO10" t="n">
         <v>970</v>
       </c>
-      <c r="AK10" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>100</v>
-      </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
-        <v>5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>6.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA10" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.9</v>
+        <v>7.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.68</v>
+        <v>28</v>
       </c>
       <c r="BG10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.66</v>
+        <v>1.14</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>1.17</v>
       </c>
       <c r="H11" t="n">
-        <v>2.78</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
-        <v>3.2</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="K11" t="n">
-        <v>3.55</v>
+        <v>12.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,153 +2527,153 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>1.08</v>
       </c>
       <c r="P11" t="n">
-        <v>1.78</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.12</v>
+        <v>1.26</v>
       </c>
       <c r="R11" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="S11" t="n">
-        <v>2.12</v>
+        <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V11" t="n">
-        <v>1.46</v>
+        <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>2.46</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.14</v>
+        <v>2.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.17</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
-        <v>20</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z12" t="n">
         <v>24</v>
       </c>
-      <c r="J12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="AA12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="O12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X12" t="n">
-        <v>85</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>120</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>300</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>29</v>
-      </c>
       <c r="AD12" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
-        <v>360</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH12" t="n">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AL12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO12" t="n">
         <v>40</v>
       </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>320</v>
-      </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AS12" t="n">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="AV12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AW12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.800000000000001</v>
+        <v>3.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.18</v>
+        <v>21</v>
       </c>
       <c r="BG12" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -2909,16 +2909,16 @@
         <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
         <v>1.73</v>
@@ -2927,134 +2927,134 @@
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3106,10 +3106,10 @@
         <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3121,134 +3121,134 @@
         <v>1.68</v>
       </c>
       <c r="R14" t="n">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.26</v>
+        <v>2.6</v>
       </c>
       <c r="G15" t="n">
         <v>3.4</v>
@@ -3294,7 +3294,7 @@
         <v>2.98</v>
       </c>
       <c r="K15" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.62</v>
+        <v>4.1</v>
       </c>
       <c r="G16" t="n">
-        <v>2.64</v>
+        <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>3.05</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.08</v>
       </c>
       <c r="J16" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M16" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="U16" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.92</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6</v>
+        <v>1.31</v>
       </c>
       <c r="X16" t="n">
         <v>12</v>
       </c>
       <c r="Y16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT16" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z16" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AU16" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AV16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD16" t="n">
         <v>16</v>
       </c>
-      <c r="AG16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH16" t="n">
+      <c r="BE16" t="n">
         <v>17.5</v>
       </c>
-      <c r="AI16" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>80</v>
-      </c>
       <c r="BF16" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>32</v>
+        <v>16.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2</v>
+        <v>2.32</v>
       </c>
       <c r="H17" t="n">
-        <v>2.06</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>2.08</v>
+        <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M17" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T17" t="n">
-        <v>1.97</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.92</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.31</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG17" t="n">
         <v>11</v>
       </c>
-      <c r="AA17" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD17" t="n">
+      <c r="AH17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="BC17" t="n">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="BE17" t="n">
         <v>17.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="G18" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M18" t="n">
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF18" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AG18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="AK18" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>44</v>
       </c>
       <c r="AM18" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN18" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR18" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AX18" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AY18" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ18" t="n">
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="BB18" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC18" t="n">
         <v>27</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>23</v>
       </c>
       <c r="BD18" t="n">
         <v>38</v>
       </c>
       <c r="BE18" t="n">
-        <v>17.5</v>
+        <v>75</v>
       </c>
       <c r="BF18" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BG18" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>
@@ -4085,10 +4085,10 @@
         <v>1.43</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4121,7 +4121,7 @@
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
         <v>7.2</v>
@@ -4160,7 +4160,7 @@
         <v>29</v>
       </c>
       <c r="AO19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP19" t="n">
         <v>9.800000000000001</v>
@@ -4218,7 +4218,589 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-28 22:29:43</t>
+          <t>2026-04-29 00:38:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CD Victoria</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Real Espana</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K20" t="n">
+        <v>950</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:38:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K21" t="n">
+        <v>950</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:38:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Platense FC</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K22" t="n">
+        <v>950</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-04-29 00:38:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="K4" t="n">
         <v>950</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -1960,10 +1960,10 @@
         <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
         <v>2.16</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.81</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.28</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2166,7 +2166,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="I10" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2327,43 +2327,43 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.72</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="n">
         <v>970</v>
@@ -2372,7 +2372,7 @@
         <v>970</v>
       </c>
       <c r="AA10" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AB10" t="n">
         <v>970</v>
@@ -2384,10 +2384,10 @@
         <v>970</v>
       </c>
       <c r="AE10" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AF10" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AG10" t="n">
         <v>970</v>
@@ -2396,13 +2396,13 @@
         <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AJ10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AK10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL10" t="n">
         <v>50</v>
@@ -2411,7 +2411,7 @@
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AO10" t="n">
         <v>970</v>
@@ -2420,10 +2420,10 @@
         <v>6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AS10" t="n">
         <v>6.2</v>
@@ -2432,10 +2432,10 @@
         <v>5.9</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.5</v>
+        <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2447,32 +2447,32 @@
         <v>5.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.8</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB10" t="n">
         <v>7.8</v>
       </c>
       <c r="BC10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF10" t="n">
         <v>7.2</v>
       </c>
-      <c r="BD10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>28</v>
-      </c>
       <c r="BG10" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2518,7 @@
         <v>10.5</v>
       </c>
       <c r="K11" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2545,10 +2545,10 @@
         <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V11" t="n">
         <v>1.03</v>
@@ -2563,7 +2563,7 @@
         <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
@@ -2575,10 +2575,10 @@
         <v>29</v>
       </c>
       <c r="AD11" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AE11" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AF11" t="n">
         <v>12</v>
@@ -2590,7 +2590,7 @@
         <v>44</v>
       </c>
       <c r="AI11" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
         <v>10.5</v>
@@ -2602,22 +2602,22 @@
         <v>40</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AN11" t="n">
         <v>2.46</v>
       </c>
       <c r="AO11" t="n">
-        <v>320</v>
+        <v>270</v>
       </c>
       <c r="AP11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS11" t="n">
         <v>10</v>
@@ -2629,10 +2629,10 @@
         <v>8</v>
       </c>
       <c r="AV11" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX11" t="n">
         <v>9.800000000000001</v>
@@ -2641,32 +2641,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC11" t="n">
         <v>11.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF11" t="n">
         <v>2.18</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
         <v>3.05</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2721,13 +2721,13 @@
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q12" t="n">
         <v>2.04</v>
@@ -2742,13 +2742,13 @@
         <v>1.79</v>
       </c>
       <c r="U12" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="H13" t="n">
         <v>4.9</v>
@@ -2906,16 +2906,16 @@
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="O13" t="n">
         <v>1.38</v>
@@ -2924,7 +2924,7 @@
         <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
@@ -2933,10 +2933,10 @@
         <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V13" t="n">
         <v>1.16</v>
@@ -2945,10 +2945,10 @@
         <v>2.02</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y13" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="Z13" t="n">
         <v>55</v>
@@ -2957,10 +2957,10 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AC13" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AD13" t="n">
         <v>27</v>
@@ -2969,16 +2969,16 @@
         <v>110</v>
       </c>
       <c r="AF13" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG13" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH13" t="n">
         <v>27</v>
       </c>
       <c r="AI13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ13" t="n">
         <v>22</v>
@@ -2993,7 +2993,7 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3011,7 +3011,7 @@
         <v>5</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
         <v>6.6</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3115,19 +3115,19 @@
         <v>1.25</v>
       </c>
       <c r="P14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="R14" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S14" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
         <v>1.85</v>
@@ -3136,7 +3136,7 @@
         <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="X14" t="n">
         <v>23</v>
@@ -3187,19 +3187,19 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
         <v>4.3</v>
@@ -3208,13 +3208,13 @@
         <v>6.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
         <v>6.6</v>
@@ -3223,32 +3223,32 @@
         <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF14" t="n">
         <v>5.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="H15" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="I15" t="n">
         <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
@@ -3303,146 +3303,146 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.83</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="R15" t="n">
-        <v>1.12</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>1.71</v>
+        <v>3.05</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V15" t="n">
         <v>1.58</v>
       </c>
       <c r="W15" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
@@ -3503,7 +3503,7 @@
         <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
         <v>2.2</v>
@@ -3539,7 +3539,7 @@
         <v>25</v>
       </c>
       <c r="AB16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3554,7 +3554,7 @@
         <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>21</v>
@@ -3569,7 +3569,7 @@
         <v>60</v>
       </c>
       <c r="AL16" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM16" t="n">
         <v>130</v>
@@ -3578,10 +3578,10 @@
         <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ16" t="n">
         <v>7.6</v>
@@ -3593,7 +3593,7 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU16" t="n">
         <v>7.2</v>
@@ -3614,29 +3614,29 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC16" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD16" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>16</v>
       </c>
       <c r="BE16" t="n">
         <v>17.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG16" t="n">
         <v>16.5</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G17" t="n">
         <v>2.32</v>
@@ -3691,37 +3691,37 @@
         <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R17" t="n">
         <v>1.31</v>
       </c>
       <c r="S17" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U17" t="n">
         <v>2.12</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W17" t="n">
         <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
         <v>12.5</v>
@@ -3733,7 +3733,7 @@
         <v>70</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC17" t="n">
         <v>7.4</v>
@@ -3742,7 +3742,7 @@
         <v>15</v>
       </c>
       <c r="AE17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF17" t="n">
         <v>13.5</v>
@@ -3751,10 +3751,10 @@
         <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3766,7 +3766,7 @@
         <v>44</v>
       </c>
       <c r="AM17" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -3775,7 +3775,7 @@
         <v>48</v>
       </c>
       <c r="AP17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>11.5</v>
@@ -3784,10 +3784,10 @@
         <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
@@ -3796,7 +3796,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -3808,29 +3808,29 @@
         <v>17</v>
       </c>
       <c r="BA17" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
       </c>
       <c r="BD17" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BF17" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -3891,10 +3891,10 @@
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R18" t="n">
         <v>1.32</v>
@@ -3903,7 +3903,7 @@
         <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U18" t="n">
         <v>2.14</v>
@@ -3981,7 +3981,7 @@
         <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -4002,7 +4002,7 @@
         <v>17</v>
       </c>
       <c r="BA18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB18" t="n">
         <v>34</v>
@@ -4011,20 +4011,20 @@
         <v>27</v>
       </c>
       <c r="BD18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE18" t="n">
         <v>75</v>
       </c>
       <c r="BF18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG18" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>2.58</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I19" t="n">
         <v>3.35</v>
@@ -4196,7 +4196,7 @@
         <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB19" t="n">
         <v>32</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 00:38:29</t>
+          <t>2026-04-29 02:46:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.04</v>
+        <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="H2" t="n">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>1.02</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1.86</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.35</v>
+        <v>3.05</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1145,100 +1145,100 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.07</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.02</v>
+        <v>2.38</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1247,10 +1247,10 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP4" t="n">
         <v>1.03</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1748,22 +1748,22 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O7" t="n">
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S7" t="n">
         <v>1.18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>1.37</v>
       </c>
       <c r="G8" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H8" t="n">
         <v>6.6</v>
@@ -1933,7 +1933,7 @@
         <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K8" t="n">
         <v>7.6</v>
@@ -1942,7 +1942,7 @@
         <v>1.21</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8" t="n">
         <v>3.55</v>
@@ -1960,10 +1960,10 @@
         <v>1.75</v>
       </c>
       <c r="S8" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="T8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U8" t="n">
         <v>2.16</v>
@@ -1972,7 +1972,7 @@
         <v>1.11</v>
       </c>
       <c r="W8" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="X8" t="n">
         <v>40</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.04</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.28</v>
-      </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2136,22 +2136,22 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q9" t="n">
         <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
         <v>1.33</v>
@@ -2166,7 +2166,7 @@
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
         <v>1.85</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2333,7 +2333,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
@@ -2348,7 +2348,7 @@
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
@@ -2357,7 +2357,7 @@
         <v>2.3</v>
       </c>
       <c r="V10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
@@ -2411,68 +2411,68 @@
         <v>80</v>
       </c>
       <c r="AN10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AO10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR10" t="n">
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.8</v>
+        <v>14.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD10" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
         <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2521,7 +2521,7 @@
         <v>12</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
@@ -2545,10 +2545,10 @@
         <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V11" t="n">
         <v>1.03</v>
@@ -2605,68 +2605,68 @@
         <v>170</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="AO11" t="n">
         <v>270</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>16</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AW11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX11" t="n">
         <v>10</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AY11" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H12" t="n">
         <v>2.78</v>
       </c>
       <c r="I12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J12" t="n">
         <v>3.25</v>
@@ -2745,10 +2745,10 @@
         <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W12" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -2891,13 +2891,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="G13" t="n">
         <v>1.96</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I13" t="n">
         <v>7</v>
@@ -2906,10 +2906,10 @@
         <v>3.45</v>
       </c>
       <c r="K13" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M13" t="n">
         <v>1.08</v>
@@ -2924,7 +2924,7 @@
         <v>1.73</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R13" t="n">
         <v>1.27</v>
@@ -2933,10 +2933,10 @@
         <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="V13" t="n">
         <v>1.16</v>
@@ -2963,7 +2963,7 @@
         <v>970</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AE13" t="n">
         <v>110</v>
@@ -2999,10 +2999,10 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AR13" t="n">
         <v>4.7</v>
@@ -3023,10 +3023,10 @@
         <v>4.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
       <c r="AZ13" t="n">
         <v>4.3</v>
@@ -3035,7 +3035,7 @@
         <v>4.9</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
         <v>4.2</v>
@@ -3047,14 +3047,14 @@
         <v>5</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="BG13" t="n">
         <v>5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>6.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
@@ -3127,7 +3127,7 @@
         <v>2.92</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
         <v>1.85</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3282,22 +3282,22 @@
         <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K15" t="n">
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3309,13 +3309,13 @@
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
         <v>3.05</v>
@@ -3330,19 +3330,19 @@
         <v>1.58</v>
       </c>
       <c r="W15" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z15" t="n">
         <v>23</v>
       </c>
       <c r="AA15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AB15" t="n">
         <v>14.5</v>
@@ -3351,10 +3351,10 @@
         <v>9.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF15" t="n">
         <v>23</v>
@@ -3369,28 +3369,28 @@
         <v>46</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
         <v>34</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM15" t="n">
         <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
         <v>27</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR15" t="n">
         <v>15</v>
@@ -3399,25 +3399,25 @@
         <v>4.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.800000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="AW15" t="n">
         <v>4.4</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AY15" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA15" t="n">
         <v>4.5</v>
@@ -3426,7 +3426,7 @@
         <v>4.5</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>4.5</v>
@@ -3435,14 +3435,14 @@
         <v>4.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG15" t="n">
         <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
         <v>4.2</v>
@@ -3491,7 +3491,7 @@
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M16" t="n">
         <v>1.09</v>
@@ -3614,7 +3614,7 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BB16" t="n">
         <v>16.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G17" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H17" t="n">
         <v>3.55</v>
@@ -3679,13 +3679,13 @@
         <v>3.65</v>
       </c>
       <c r="J17" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
         <v>3.5</v>
       </c>
       <c r="L17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -3718,10 +3718,10 @@
         <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
         <v>12.5</v>
@@ -3745,7 +3745,7 @@
         <v>44</v>
       </c>
       <c r="AF17" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG17" t="n">
         <v>11</v>
@@ -3757,7 +3757,7 @@
         <v>55</v>
       </c>
       <c r="AJ17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
         <v>26</v>
@@ -3784,10 +3784,10 @@
         <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
@@ -3796,7 +3796,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -3805,10 +3805,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3820,17 +3820,17 @@
         <v>29</v>
       </c>
       <c r="BE17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BF17" t="n">
         <v>18.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="G18" t="n">
         <v>2.64</v>
@@ -3891,7 +3891,7 @@
         <v>1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q18" t="n">
         <v>2.14</v>
@@ -3966,7 +3966,7 @@
         <v>26</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP18" t="n">
         <v>11.5</v>
@@ -4017,14 +4017,14 @@
         <v>75</v>
       </c>
       <c r="BF18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG18" t="n">
         <v>32</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G19" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H19" t="n">
         <v>3.25</v>
@@ -4088,7 +4088,7 @@
         <v>1.73</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4106,7 +4106,7 @@
         <v>1.42</v>
       </c>
       <c r="W19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
@@ -4133,7 +4133,7 @@
         <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -4145,7 +4145,7 @@
         <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK19" t="n">
         <v>32</v>
@@ -4157,13 +4157,13 @@
         <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO19" t="n">
         <v>46</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ19" t="n">
         <v>10</v>
@@ -4199,7 +4199,7 @@
         <v>30</v>
       </c>
       <c r="BB19" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4273,13 +4273,13 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O20" t="n">
         <v>1.2</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q20" t="n">
         <v>1.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4467,13 +4467,13 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O21" t="n">
         <v>1.23</v>
       </c>
       <c r="P21" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q21" t="n">
         <v>1.23</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>
@@ -4661,19 +4661,19 @@
         <v>1.01</v>
       </c>
       <c r="N22" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q22" t="n">
         <v>1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S22" t="n">
         <v>1.2</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 02:46:56</t>
+          <t>2026-04-29 04:55:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH22"/>
+  <dimension ref="A1:BH23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,7 +784,7 @@
         <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
         <v>1.86</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="G3" t="n">
         <v>1000</v>
@@ -960,10 +960,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -975,22 +975,22 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.07</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="R3" t="n">
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -999,7 +999,7 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="G4" t="n">
         <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
         <v>2.72</v>
@@ -1166,10 +1166,10 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1178,7 +1178,7 @@
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -1187,37 +1187,37 @@
         <v>1.01</v>
       </c>
       <c r="T4" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U4" t="n">
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
         <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AA4" t="n">
         <v>55</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD4" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE4" t="n">
         <v>44</v>
@@ -1226,7 +1226,7 @@
         <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>17</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
         <v>25</v>
@@ -1253,62 +1253,62 @@
         <v>48</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
         <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="O6" t="n">
         <v>1.02</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2139,13 +2139,13 @@
         <v>1.06</v>
       </c>
       <c r="N9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O9" t="n">
         <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q9" t="n">
         <v>1.33</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G10" t="n">
         <v>4.6</v>
@@ -2318,7 +2318,7 @@
         <v>1.85</v>
       </c>
       <c r="I10" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="J10" t="n">
         <v>3.85</v>
@@ -2327,19 +2327,19 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
         <v>1.66</v>
@@ -2348,76 +2348,76 @@
         <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="T10" t="n">
         <v>1.64</v>
       </c>
       <c r="U10" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="W10" t="n">
         <v>1.27</v>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y10" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AA10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB10" t="n">
         <v>23</v>
       </c>
-      <c r="AB10" t="n">
-        <v>970</v>
-      </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="AF10" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AH10" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AJ10" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ10" t="n">
         <v>9.6</v>
@@ -2426,22 +2426,22 @@
         <v>11</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT10" t="n">
-        <v>15.5</v>
+        <v>4.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AY10" t="n">
         <v>14.5</v>
@@ -2450,29 +2450,29 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="BB10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2536,10 +2536,10 @@
         <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="R11" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S11" t="n">
         <v>1.69</v>
@@ -2563,76 +2563,76 @@
         <v>120</v>
       </c>
       <c r="Z11" t="n">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC11" t="n">
         <v>29</v>
       </c>
       <c r="AD11" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AE11" t="n">
-        <v>320</v>
+        <v>350</v>
       </c>
       <c r="AF11" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AI11" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK11" t="n">
         <v>14.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN11" t="n">
         <v>2.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AR11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV11" t="n">
         <v>11</v>
       </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="AW11" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>10</v>
@@ -2641,32 +2641,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE11" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>10.5</v>
       </c>
       <c r="BF11" t="n">
         <v>2.24</v>
       </c>
       <c r="BG11" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2700,22 +2700,22 @@
         <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
         <v>2.78</v>
       </c>
       <c r="I12" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="K12" t="n">
         <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -2745,10 +2745,10 @@
         <v>2.08</v>
       </c>
       <c r="V12" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
         <v>1.96</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3109,7 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.25</v>
@@ -3136,7 +3136,7 @@
         <v>1.09</v>
       </c>
       <c r="W14" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="X14" t="n">
         <v>23</v>
@@ -3187,34 +3187,34 @@
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU14" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AV14" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AX14" t="n">
         <v>6.6</v>
@@ -3223,32 +3223,32 @@
         <v>7.4</v>
       </c>
       <c r="AZ14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD14" t="n">
         <v>3.9</v>
       </c>
-      <c r="BA14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
         <v>5.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="G15" t="n">
         <v>2.8</v>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3312,7 +3312,7 @@
         <v>2.04</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="R15" t="n">
         <v>1.41</v>
@@ -3330,7 +3330,7 @@
         <v>1.58</v>
       </c>
       <c r="W15" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -3387,7 +3387,7 @@
         <v>27</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.95</v>
+        <v>12.5</v>
       </c>
       <c r="AQ15" t="n">
         <v>3.75</v>
@@ -3399,10 +3399,10 @@
         <v>4.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
         <v>3.75</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -3479,10 +3479,10 @@
         <v>4.2</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I16" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
@@ -3491,22 +3491,22 @@
         <v>3.7</v>
       </c>
       <c r="L16" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
         <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R16" t="n">
         <v>1.29</v>
@@ -3521,7 +3521,7 @@
         <v>1.97</v>
       </c>
       <c r="V16" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="W16" t="n">
         <v>1.31</v>
@@ -3533,7 +3533,7 @@
         <v>8.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA16" t="n">
         <v>25</v>
@@ -3563,7 +3563,7 @@
         <v>44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AK16" t="n">
         <v>60</v>
@@ -3578,7 +3578,7 @@
         <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AP16" t="n">
         <v>11</v>
@@ -3593,19 +3593,19 @@
         <v>22</v>
       </c>
       <c r="AT16" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
         <v>21</v>
       </c>
       <c r="AX16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY16" t="n">
         <v>15</v>
@@ -3614,29 +3614,29 @@
         <v>18.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BC16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>55</v>
+      </c>
+      <c r="BE16" t="n">
         <v>15</v>
       </c>
-      <c r="BD16" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>55</v>
       </c>
       <c r="BG16" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -3673,19 +3673,19 @@
         <v>2.36</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J17" t="n">
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -3697,10 +3697,10 @@
         <v>1.37</v>
       </c>
       <c r="P17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
         <v>1.31</v>
@@ -3709,7 +3709,7 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
         <v>2.12</v>
@@ -3718,10 +3718,10 @@
         <v>1.38</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
         <v>12.5</v>
@@ -3754,7 +3754,7 @@
         <v>18.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
         <v>32</v>
@@ -3784,10 +3784,10 @@
         <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
         <v>7</v>
@@ -3796,7 +3796,7 @@
         <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -3808,29 +3808,29 @@
         <v>16.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC17" t="n">
         <v>23</v>
       </c>
       <c r="BD17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BE17" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="BF17" t="n">
         <v>18.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -3888,22 +3888,22 @@
         <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R18" t="n">
         <v>1.32</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U18" t="n">
         <v>2.14</v>
@@ -3912,7 +3912,7 @@
         <v>1.47</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -3981,7 +3981,7 @@
         <v>46</v>
       </c>
       <c r="AT18" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU18" t="n">
         <v>7</v>
@@ -4014,7 +4014,7 @@
         <v>40</v>
       </c>
       <c r="BE18" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BF18" t="n">
         <v>23</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>3.3</v>
@@ -4082,10 +4082,10 @@
         <v>3.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P19" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q19" t="n">
         <v>2.34</v>
@@ -4097,19 +4097,19 @@
         <v>4.4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U19" t="n">
         <v>2</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W19" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y19" t="n">
         <v>11</v>
@@ -4121,19 +4121,19 @@
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC19" t="n">
         <v>7.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG19" t="n">
         <v>12</v>
@@ -4142,10 +4142,10 @@
         <v>19.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK19" t="n">
         <v>32</v>
@@ -4157,10 +4157,10 @@
         <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO19" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AP19" t="n">
         <v>10</v>
@@ -4169,13 +4169,13 @@
         <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.8</v>
@@ -4184,10 +4184,10 @@
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY19" t="n">
         <v>11</v>
@@ -4196,10 +4196,10 @@
         <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BB19" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BC19" t="n">
         <v>28</v>
@@ -4208,17 +4208,17 @@
         <v>44</v>
       </c>
       <c r="BE19" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BF19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BG19" t="n">
         <v>42</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CD Victoria</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>CD Victoria</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4667,13 +4667,13 @@
         <v>1.2</v>
       </c>
       <c r="P22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
         <v>1.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="S22" t="n">
         <v>1.2</v>
@@ -4800,7 +4800,201 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 04:55:21</t>
+          <t>2026-04-29 07:03:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Genesis Huracan</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K23" t="n">
+        <v>950</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-29 07:03:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH23"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.37</v>
@@ -781,34 +781,34 @@
         <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
         <v>18</v>
@@ -820,19 +820,19 @@
         <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>460</v>
+        <v>490</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE2" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AF2" t="n">
         <v>9</v>
@@ -841,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AJ2" t="n">
         <v>14</v>
@@ -856,71 +856,71 @@
         <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="AP2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC2" t="n">
         <v>4.1</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR2" t="n">
+      <c r="BD2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG2" t="n">
         <v>5.1</v>
       </c>
-      <c r="AS2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1169,7 +1169,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1178,7 +1178,7 @@
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -1193,7 +1193,7 @@
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
         <v>1.37</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -1339,154 +1339,154 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.02</v>
+        <v>2.7</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.08</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52</v>
+        <v>4.3</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
         <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
         <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
         <v>1.03</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
@@ -1533,46 +1533,46 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="H6" t="n">
-        <v>1.04</v>
+        <v>1.88</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="J6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
         <v>1.02</v>
       </c>
-      <c r="K6" t="n">
-        <v>950</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.44</v>
+        <v>2.06</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="S6" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1581,100 +1581,100 @@
         <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
         <v>1.03</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,33 +1713,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>Sportive De Tunis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>TSV Grafenstein</t>
+          <t>Club Sportif Sfaxien</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H7" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
         <v>950</v>
@@ -1748,25 +1748,25 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P7" t="n">
         <v>1.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="R7" t="n">
         <v>1.08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Avenir S Marsa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Esperance Sportive Zarzis</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>1.45</v>
+        <v>110</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>170</v>
       </c>
       <c r="J8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>2.68</v>
+        <v>1.08</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="T8" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W8" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y8" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX8" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY8" t="n">
-        <v>3.7</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB8" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE8" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BG8" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,33 +2101,33 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Olympique De Beja</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H9" t="n">
         <v>1.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K9" t="n">
         <v>950</v>
@@ -2136,25 +2136,25 @@
         <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>4.6</v>
+        <v>110</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>2.02</v>
+        <v>110</v>
       </c>
       <c r="J10" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="O10" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="T10" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Ilirija Extra-Lux</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Nafta Lendava</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="G11" t="n">
-        <v>1.17</v>
+        <v>110</v>
       </c>
       <c r="H11" t="n">
-        <v>20</v>
+        <v>1.02</v>
       </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
-        <v>10.5</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>12</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="O11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R11" t="n">
         <v>1.08</v>
       </c>
-      <c r="P11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.28</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.69</v>
+        <v>1.23</v>
       </c>
       <c r="T11" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
         <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.38</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>320</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Dravinja Kostroj</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>160</v>
       </c>
       <c r="H12" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>3.05</v>
+        <v>160</v>
       </c>
       <c r="J12" t="n">
-        <v>2.88</v>
+        <v>1.03</v>
       </c>
       <c r="K12" t="n">
-        <v>3.6</v>
+        <v>950</v>
       </c>
       <c r="L12" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.08</v>
       </c>
-      <c r="N12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.82</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.04</v>
+        <v>1.28</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>3.7</v>
+        <v>1.28</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Triglav</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="G13" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="I13" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P13" t="n">
         <v>1.08</v>
       </c>
-      <c r="N13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>1.15</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.42</v>
+        <v>3.95</v>
       </c>
       <c r="G14" t="n">
-        <v>1.58</v>
+        <v>4.6</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>1.85</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>1.99</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="M14" t="n">
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="P14" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="R14" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="S14" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="T14" t="n">
-        <v>1.97</v>
+        <v>1.64</v>
       </c>
       <c r="U14" t="n">
-        <v>1.85</v>
+        <v>2.24</v>
       </c>
       <c r="V14" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="W14" t="n">
-        <v>2.64</v>
+        <v>1.28</v>
       </c>
       <c r="X14" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB14" t="n">
         <v>23</v>
       </c>
-      <c r="Y14" t="n">
-        <v>34</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>970</v>
-      </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AH14" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ14" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AK14" t="n">
-        <v>970</v>
+        <v>60</v>
       </c>
       <c r="AL14" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>8.6</v>
+        <v>48</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>9.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AU14" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.85</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX14" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA14" t="n">
+      <c r="BC14" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD14" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BE14" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.62</v>
+        <v>1.37</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>1.45</v>
       </c>
       <c r="H15" t="n">
-        <v>2.68</v>
+        <v>6.8</v>
       </c>
       <c r="I15" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.04</v>
+        <v>2.76</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>3.05</v>
+        <v>1.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U15" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V15" t="n">
-        <v>1.58</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="X15" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
         <v>970</v>
       </c>
-      <c r="Y15" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AC15" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="AE15" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="AF15" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>970</v>
       </c>
-      <c r="AI15" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>46</v>
-      </c>
       <c r="AK15" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="AM15" t="n">
         <v>100</v>
       </c>
       <c r="AN15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX15" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="AY15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX15" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BA15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
         <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF15" t="n">
-        <v>16</v>
+        <v>2.68</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>1.05</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>2.08</v>
+        <v>1.04</v>
       </c>
       <c r="I16" t="n">
-        <v>2.12</v>
+        <v>1000</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7</v>
+        <v>950</v>
       </c>
       <c r="L16" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.08</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S16" t="n">
-        <v>4.1</v>
+        <v>1.33</v>
       </c>
       <c r="T16" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR16" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AT16" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AX16" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AY16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA16" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB16" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BC16" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD16" t="n">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BE16" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BF16" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
-        <v>2.36</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N17" t="n">
         <v>1.08</v>
       </c>
-      <c r="N17" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="P17" t="n">
-        <v>1.82</v>
+        <v>1.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>1.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>1.18</v>
       </c>
       <c r="T17" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W17" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY17" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB17" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BC17" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD17" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE17" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF17" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Neftchi Baku</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="G18" t="n">
-        <v>2.64</v>
+        <v>8.4</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>1.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>3.6</v>
+        <v>1.9</v>
       </c>
       <c r="O18" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.12</v>
+        <v>1.64</v>
       </c>
       <c r="R18" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>2.54</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>1.47</v>
+        <v>1.84</v>
       </c>
       <c r="W18" t="n">
-        <v>1.61</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS18" t="n">
-        <v>46</v>
+        <v>1.03</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV18" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX18" t="n">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY18" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA18" t="n">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BB18" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BC18" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE18" t="n">
-        <v>85</v>
+        <v>1.03</v>
       </c>
       <c r="BF18" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="G19" t="n">
-        <v>2.54</v>
+        <v>2.86</v>
       </c>
       <c r="H19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
         <v>3.3</v>
       </c>
-      <c r="I19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.25</v>
-      </c>
       <c r="O19" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.34</v>
+        <v>2.12</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S19" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U19" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="W19" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
         <v>60</v>
       </c>
       <c r="AB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC19" t="n">
         <v>9</v>
       </c>
-      <c r="AC19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AH19" t="n">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AK19" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
         <v>130</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AO19" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR19" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>50</v>
+        <v>4.2</v>
       </c>
       <c r="AT19" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="AX19" t="n">
         <v>13</v>
       </c>
       <c r="AY19" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BB19" t="n">
-        <v>32</v>
+        <v>4.1</v>
       </c>
       <c r="BC19" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>4.1</v>
       </c>
       <c r="BE19" t="n">
-        <v>42</v>
+        <v>4.3</v>
       </c>
       <c r="BF19" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BG19" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.17</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O20" t="n">
         <v>1.08</v>
       </c>
-      <c r="O20" t="n">
-        <v>1.2</v>
-      </c>
       <c r="P20" t="n">
-        <v>1.08</v>
+        <v>4.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R20" t="n">
-        <v>1.07</v>
+        <v>2.28</v>
       </c>
       <c r="S20" t="n">
-        <v>1.2</v>
+        <v>1.69</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
         <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>8.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>1.65</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>1.96</v>
       </c>
       <c r="H21" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>1.08</v>
+        <v>2.92</v>
       </c>
       <c r="O21" t="n">
-        <v>1.23</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.08</v>
+        <v>1.73</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.23</v>
+        <v>2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.07</v>
+        <v>1.27</v>
       </c>
       <c r="S21" t="n">
-        <v>1.23</v>
+        <v>3.6</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,378 +4623,2124 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>CD Victoria</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G22" t="n">
-        <v>1000</v>
+        <v>1.58</v>
       </c>
       <c r="H22" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M22" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>1.08</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.74</v>
       </c>
       <c r="R22" t="n">
-        <v>1.07</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>1.2</v>
+        <v>2.92</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V22" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE22" t="n">
         <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI22" t="n">
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 07:03:32</t>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Saudi Professional League</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>15:00:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Al-Kholood Club</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Al-Feiha</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="X23" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Shakhtar</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>4</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I24" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="X24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>18</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UEFA Europa Conference League</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="X25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>15</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Nottm Forest</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="X26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>50</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Union Espanola</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S28" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Platense FC</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G29" t="n">
+        <v>110</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I29" t="n">
+        <v>110</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K29" t="n">
+        <v>950</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G30" t="n">
+        <v>110</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I30" t="n">
+        <v>110</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K30" t="n">
+        <v>950</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CD Victoria</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Real Espana</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G31" t="n">
+        <v>110</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I31" t="n">
+        <v>110</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Genesis Huracan</t>
         </is>
       </c>
-      <c r="F23" t="n">
+      <c r="F32" t="n">
         <v>1.04</v>
       </c>
-      <c r="G23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H23" t="n">
+      <c r="G32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H32" t="n">
         <v>1.04</v>
       </c>
-      <c r="I23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J23" t="n">
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
         <v>1.02</v>
       </c>
-      <c r="K23" t="n">
+      <c r="K32" t="n">
         <v>950</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N32" t="n">
         <v>1.08</v>
       </c>
-      <c r="O23" t="n">
+      <c r="O32" t="n">
         <v>1.26</v>
       </c>
-      <c r="P23" t="n">
+      <c r="P32" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="Q32" t="n">
         <v>1.26</v>
       </c>
-      <c r="R23" t="n">
+      <c r="R32" t="n">
         <v>1.07</v>
       </c>
-      <c r="S23" t="n">
+      <c r="S32" t="n">
         <v>1.26</v>
       </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>2026-04-29 07:03:32</t>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-29 09:14:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,61 +757,61 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.3</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.34</v>
-      </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="X2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="Y2" t="n">
         <v>32</v>
@@ -820,22 +820,22 @@
         <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AE2" t="n">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -844,83 +844,83 @@
         <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AJ2" t="n">
         <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO2" t="n">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="AP2" t="n">
         <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT2" t="n">
         <v>3.2</v>
       </c>
       <c r="AU2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY2" t="n">
         <v>3.7</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>4.6</v>
       </c>
-      <c r="AW2" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BA2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1169,7 +1169,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="O4" t="n">
         <v>1.47</v>
@@ -1178,7 +1178,7 @@
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
@@ -1193,10 +1193,10 @@
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -1384,7 +1384,7 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
         <v>1.45</v>
@@ -1447,62 +1447,62 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -1533,177 +1533,177 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.88</v>
+        <v>1.7</v>
       </c>
       <c r="I6" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.02</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
         <v>1.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
         <v>9</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AB6" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AF6" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AG6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AL6" t="n">
         <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN6" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AO6" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Tunisian Ligue Professionelle 1</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,60 +1713,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sportive De Tunis</t>
+          <t>Adana 1954 FK</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Club Sportif Sfaxien</t>
+          <t>Elazigspor</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.04</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>3.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="I7" t="n">
-        <v>110</v>
+        <v>3.85</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>2.46</v>
       </c>
       <c r="K7" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="O7" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S7" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,10 +1775,10 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
         <v>1000</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tunisian Ligue Professionelle 1</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11:30:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Avenir S Marsa</t>
+          <t>Aliaga Futbol AS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Esperance Sportive Zarzis</t>
+          <t>Mus Spor</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>110</v>
+        <v>2.18</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>170</v>
+        <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,22 +1945,22 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,10 +1969,10 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -2106,55 +2106,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Olympique De Beja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G9" t="n">
-        <v>110</v>
+        <v>3.65</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.82</v>
       </c>
       <c r="I9" t="n">
-        <v>110</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.42</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.08</v>
+        <v>1.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R9" t="n">
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,122 +2163,122 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>2.9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -2300,25 +2300,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique De Beja</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J10" t="n">
         <v>1.03</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="P10" t="n">
         <v>1.08</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R10" t="n">
         <v>1.08</v>
       </c>
       <c r="S10" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ilirija Extra-Lux</t>
+          <t>Avenir S Marsa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nafta Lendava</t>
+          <t>Esperance Sportive Zarzis</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="G11" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI11" t="n">
         <v>110</v>
       </c>
-      <c r="H11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="AJ11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO11" t="n">
         <v>110</v>
       </c>
-      <c r="J11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K11" t="n">
-        <v>950</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>2.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Tunisian Ligue Professionelle 1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,30 +2683,30 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Dravinja Kostroj</t>
+          <t>Sportive De Tunis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Krka</t>
+          <t>Club Sportif Sfaxien</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="H12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="J12" t="n">
         <v>1.03</v>
@@ -2730,13 +2730,13 @@
         <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Jesenice</t>
+          <t>Ilirija Extra-Lux</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Triglav</t>
+          <t>Nafta Lendava</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>6.2</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>1.61</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>3.65</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M13" t="n">
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P13" t="n">
-        <v>1.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>1.15</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Dravinja Kostroj</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Krka</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="G14" t="n">
-        <v>4.6</v>
+        <v>970</v>
       </c>
       <c r="H14" t="n">
-        <v>1.85</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
-        <v>1.99</v>
+        <v>110</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>4.6</v>
+        <v>1.09</v>
       </c>
       <c r="O14" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>1.08</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.49</v>
+        <v>1.08</v>
       </c>
       <c r="S14" t="n">
-        <v>2.68</v>
+        <v>1.32</v>
       </c>
       <c r="T14" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Jesenice</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Triglav</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1.45</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>6.8</v>
+        <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K15" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L15" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>2.76</v>
+        <v>1.08</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="S15" t="n">
-        <v>1.96</v>
+        <v>1.14</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA15" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.9</v>
+        <v>1.03</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE15" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,27 +3459,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Svg Bleiburg</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="G16" t="n">
         <v>1000</v>
       </c>
       <c r="H16" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="I16" t="n">
         <v>1000</v>
@@ -3494,25 +3494,25 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="R16" t="n">
         <v>1.08</v>
       </c>
       <c r="S16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,33 +3653,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>Krsko</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TSV Grafenstein</t>
+          <t>Slovan Ljublana</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3688,25 +3688,25 @@
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
         <v>1.08</v>
       </c>
       <c r="O17" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>1.08</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="R17" t="n">
         <v>1.08</v>
       </c>
       <c r="S17" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Neftchi Baku</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="G18" t="n">
-        <v>8.4</v>
+        <v>4.6</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="I18" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P18" t="n">
         <v>2.2</v>
       </c>
-      <c r="J18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>950</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="T18" t="n">
         <v>1.64</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.64</v>
+        <v>1.51</v>
       </c>
       <c r="G19" t="n">
-        <v>2.86</v>
+        <v>1.58</v>
       </c>
       <c r="H19" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
       <c r="I19" t="n">
-        <v>3.1</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="L19" t="n">
         <v>1.38</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.12</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="X19" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>210</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>150</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF19" t="n">
         <v>4</v>
       </c>
-      <c r="T19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="U19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="X19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>13</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU19" t="n">
+      <c r="BG19" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>4</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Neftchi Baku</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.14</v>
+        <v>3.65</v>
       </c>
       <c r="G20" t="n">
-        <v>1.17</v>
+        <v>5.8</v>
       </c>
       <c r="H20" t="n">
-        <v>20</v>
+        <v>1.7</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>2.08</v>
       </c>
       <c r="J20" t="n">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N20" t="n">
-        <v>9.199999999999999</v>
+        <v>3.65</v>
       </c>
       <c r="O20" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="P20" t="n">
-        <v>4.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.21</v>
+        <v>1.76</v>
       </c>
       <c r="R20" t="n">
-        <v>2.28</v>
+        <v>1.37</v>
       </c>
       <c r="S20" t="n">
-        <v>1.69</v>
+        <v>2.92</v>
       </c>
       <c r="T20" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="U20" t="n">
         <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.92</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X20" t="n">
-        <v>85</v>
+        <v>970</v>
       </c>
       <c r="Y20" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>300</v>
+        <v>970</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AB20" t="n">
         <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="AD20" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="AE20" t="n">
-        <v>340</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="AG20" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AH20" t="n">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>210</v>
+        <v>40</v>
       </c>
       <c r="AJ20" t="n">
-        <v>10</v>
+        <v>130</v>
       </c>
       <c r="AK20" t="n">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AM20" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.38</v>
+        <v>80</v>
       </c>
       <c r="AO20" t="n">
-        <v>310</v>
+        <v>970</v>
       </c>
       <c r="AP20" t="n">
-        <v>8.4</v>
+        <v>3.9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>8.6</v>
+        <v>3.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>16</v>
+        <v>3.95</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>3.35</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.4</v>
+        <v>3.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AX20" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BC20" t="n">
-        <v>12.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.800000000000001</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.24</v>
+        <v>4.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>9</v>
+        <v>3.65</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.65</v>
+        <v>1.02</v>
       </c>
       <c r="G21" t="n">
-        <v>1.96</v>
+        <v>110</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>1.02</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N21" t="n">
         <v>1.08</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.92</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.18</v>
       </c>
       <c r="P21" t="n">
-        <v>1.73</v>
+        <v>1.08</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S21" t="n">
-        <v>3.6</v>
+        <v>1.18</v>
       </c>
       <c r="T21" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W21" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
         <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
         <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS21" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT21" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY21" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,81 +4623,81 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="G22" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="K22" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="M22" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="O22" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.66</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.74</v>
+        <v>1.43</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.75</v>
       </c>
       <c r="S22" t="n">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="T22" t="n">
-        <v>1.97</v>
+        <v>1.69</v>
       </c>
       <c r="U22" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W22" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="X22" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="Y22" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Z22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
@@ -4709,10 +4709,10 @@
         <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
         <v>970</v>
@@ -4721,10 +4721,10 @@
         <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ22" t="n">
         <v>970</v>
@@ -4733,81 +4733,81 @@
         <v>970</v>
       </c>
       <c r="AL22" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX22" t="n">
         <v>8.6</v>
       </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AY22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB22" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BC22" t="n">
-        <v>11.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.9</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.3</v>
+        <v>2.68</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="G23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H23" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="J23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N23" t="n">
         <v>3.45</v>
       </c>
-      <c r="K23" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N23" t="n">
-        <v>4</v>
-      </c>
       <c r="O23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="S23" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="T23" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U23" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="V23" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="W23" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X23" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG23" t="n">
         <v>15</v>
       </c>
-      <c r="Z23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AH23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>50</v>
       </c>
-      <c r="AB23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AK23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV23" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="AW23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ23" t="n">
         <v>12.5</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AW23" t="n">
+      <c r="BA23" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE23" t="n">
         <v>4.4</v>
       </c>
-      <c r="AX23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC23" t="n">
+      <c r="BF23" t="n">
         <v>21</v>
       </c>
-      <c r="BD23" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>16</v>
-      </c>
       <c r="BG23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>4</v>
+        <v>1.14</v>
       </c>
       <c r="G24" t="n">
-        <v>4.2</v>
+        <v>1.17</v>
       </c>
       <c r="H24" t="n">
-        <v>2.08</v>
+        <v>20</v>
       </c>
       <c r="I24" t="n">
-        <v>2.12</v>
+        <v>24</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="M24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O24" t="n">
         <v>1.08</v>
       </c>
-      <c r="N24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>4.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>1.24</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>2.28</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>1.69</v>
       </c>
       <c r="T24" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="V24" t="n">
-        <v>1.89</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>85</v>
       </c>
       <c r="Y24" t="n">
-        <v>8.4</v>
+        <v>120</v>
       </c>
       <c r="Z24" t="n">
-        <v>11.5</v>
+        <v>300</v>
       </c>
       <c r="AA24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="AD24" t="n">
+        <v>85</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>340</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>310</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS24" t="n">
         <v>10.5</v>
       </c>
-      <c r="AE24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>90</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AO24" t="n">
+      <c r="AT24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU24" t="n">
         <v>19</v>
       </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AV24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" t="n">
         <v>10</v>
       </c>
-      <c r="AW24" t="n">
-        <v>21</v>
-      </c>
       <c r="AX24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD24" t="n">
         <v>25</v>
       </c>
-      <c r="AY24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>16</v>
-      </c>
       <c r="BE24" t="n">
-        <v>18</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF24" t="n">
-        <v>16</v>
+        <v>2.24</v>
       </c>
       <c r="BG24" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Muglaspor</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="G25" t="n">
-        <v>2.36</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>950</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>1.15</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="T25" t="n">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS25" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV25" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW25" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX25" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY25" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA25" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BC25" t="n">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD25" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BE25" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF25" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.6</v>
+        <v>1.64</v>
       </c>
       <c r="G26" t="n">
-        <v>2.62</v>
+        <v>1.96</v>
       </c>
       <c r="H26" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
         <v>1.08</v>
       </c>
       <c r="N26" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
         <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>1.93</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="U26" t="n">
-        <v>2.14</v>
+        <v>1.81</v>
       </c>
       <c r="V26" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y26" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>55</v>
       </c>
       <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL26" t="n">
         <v>55</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF26" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC26" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>16</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>15</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>23</v>
-      </c>
       <c r="BG26" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="G27" t="n">
-        <v>2.52</v>
+        <v>1.56</v>
       </c>
       <c r="H27" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>14</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X27" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB27" t="n">
         <v>3.3</v>
       </c>
-      <c r="L27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U27" t="n">
-        <v>2</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="BC27" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>28</v>
-      </c>
       <c r="BD27" t="n">
-        <v>44</v>
+        <v>3.9</v>
       </c>
       <c r="BE27" t="n">
-        <v>40</v>
+        <v>4.2</v>
       </c>
       <c r="BF27" t="n">
-        <v>26</v>
+        <v>5.3</v>
       </c>
       <c r="BG27" t="n">
-        <v>42</v>
+        <v>4.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.7</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>2.82</v>
       </c>
       <c r="J28" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N28" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="O28" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.08</v>
+        <v>2.02</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="R28" t="n">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S28" t="n">
-        <v>1.38</v>
+        <v>3.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V28" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>4.2</v>
       </c>
       <c r="H29" t="n">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="I29" t="n">
-        <v>110</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
-        <v>1.02</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.7</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N29" t="n">
-        <v>1.08</v>
+        <v>3.35</v>
       </c>
       <c r="O29" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="P29" t="n">
-        <v>1.08</v>
+        <v>1.79</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>2.18</v>
       </c>
       <c r="R29" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S29" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.03</v>
+        <v>22</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.03</v>
+        <v>25</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.04</v>
+        <v>2.32</v>
       </c>
       <c r="G30" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM30" t="n">
         <v>110</v>
       </c>
-      <c r="H30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I30" t="n">
-        <v>110</v>
-      </c>
-      <c r="J30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="K30" t="n">
-        <v>950</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.03</v>
+        <v>29</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,378 +6369,1348 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CD Victoria</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G31" t="n">
-        <v>110</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I31" t="n">
-        <v>110</v>
+        <v>3.15</v>
       </c>
       <c r="J31" t="n">
-        <v>1.02</v>
+        <v>3.35</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>1.08</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.07</v>
+        <v>1.85</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="S31" t="n">
-        <v>1.2</v>
+        <v>3.85</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.03</v>
+        <v>48</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.03</v>
+        <v>32</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.03</v>
+        <v>42</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.03</v>
+        <v>34</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.03</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.03</v>
+        <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.03</v>
+        <v>85</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 09:14:08</t>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>UEFA Europa League</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>25</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>25</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>42</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chilean Primera B</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Union Espanola</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Curico Unido</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="X33" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Honduras Liga Nacional</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>22:00:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CD Victoria</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Real Espana</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G34" t="n">
+        <v>110</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I34" t="n">
+        <v>110</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K34" t="n">
+        <v>950</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CD Olimpia</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Platense FC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G35" t="n">
+        <v>110</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I35" t="n">
+        <v>110</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K35" t="n">
+        <v>950</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G36" t="n">
+        <v>110</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I36" t="n">
+        <v>110</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K36" t="n">
+        <v>950</v>
+      </c>
+      <c r="L36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="R36" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Genesis Huracan</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F37" t="n">
         <v>1.04</v>
       </c>
-      <c r="G32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H32" t="n">
+      <c r="G37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H37" t="n">
         <v>1.04</v>
       </c>
-      <c r="I32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J32" t="n">
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
         <v>1.02</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K37" t="n">
         <v>950</v>
       </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="L37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N37" t="n">
         <v>1.08</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O37" t="n">
         <v>1.26</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P37" t="n">
         <v>1.08</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q37" t="n">
         <v>1.26</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R37" t="n">
         <v>1.07</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S37" t="n">
         <v>1.26</v>
       </c>
-      <c r="T32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-04-29 09:14:08</t>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:26:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH37"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,16 +760,16 @@
         <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -799,10 +799,10 @@
         <v>3.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V2" t="n">
         <v>1.08</v>
@@ -811,19 +811,19 @@
         <v>2.92</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Z2" t="n">
         <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
         <v>12.5</v>
@@ -832,7 +832,7 @@
         <v>46</v>
       </c>
       <c r="AE2" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AF2" t="n">
         <v>8.800000000000001</v>
@@ -841,10 +841,10 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AI2" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AJ2" t="n">
         <v>14</v>
@@ -856,28 +856,28 @@
         <v>60</v>
       </c>
       <c r="AM2" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="AN2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
         <v>5.2</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU2" t="n">
         <v>3.75</v>
@@ -886,10 +886,10 @@
         <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AY2" t="n">
         <v>3.7</v>
@@ -898,29 +898,29 @@
         <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BC2" t="n">
         <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BE2" t="n">
         <v>5.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
         <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -975,19 +975,19 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
         <v>1.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S3" t="n">
         <v>1.34</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
         <v>2.72</v>
@@ -1166,25 +1166,25 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="N4" t="n">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
         <v>1.95</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="H5" t="n">
         <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
         <v>3.3</v>
@@ -1372,13 +1372,13 @@
         <v>1.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
@@ -1387,10 +1387,10 @@
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
@@ -1557,22 +1557,22 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T6" t="n">
         <v>1.92</v>
@@ -1605,7 +1605,7 @@
         <v>10.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AE6" t="n">
         <v>25</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -1727,154 +1727,154 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Q7" t="n">
         <v>2.44</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="K7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.24</v>
-      </c>
       <c r="R7" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.24</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
         <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
         <v>1.03</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
         <v>2.18</v>
@@ -1930,13 +1930,13 @@
         <v>3.5</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
         <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1960,7 +1960,7 @@
         <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -1969,7 +1969,7 @@
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
         <v>1.84</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -2148,13 +2148,13 @@
         <v>1.31</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.67</v>
+        <v>1.02</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -2309,28 +2309,28 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>970</v>
+        <v>3.6</v>
       </c>
       <c r="H10" t="n">
-        <v>1.09</v>
+        <v>2.82</v>
       </c>
       <c r="I10" t="n">
-        <v>970</v>
+        <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
         <v>2.08</v>
@@ -2339,16 +2339,16 @@
         <v>1.61</v>
       </c>
       <c r="P10" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="R10" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2357,122 +2357,122 @@
         <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.15</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -2697,100 +2697,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G12" t="n">
-        <v>110</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>110</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="O12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.08</v>
+        <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="R12" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12" t="n">
         <v>1000</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>2.22</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
         <v>1.19</v>
@@ -2927,7 +2927,7 @@
         <v>1.55</v>
       </c>
       <c r="R13" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="S13" t="n">
         <v>2.38</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>970</v>
       </c>
       <c r="H14" t="n">
-        <v>1.09</v>
+        <v>1.49</v>
       </c>
       <c r="I14" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J14" t="n">
         <v>1.03</v>
@@ -3109,19 +3109,19 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
         <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
         <v>1.32</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H15" t="n">
         <v>1.02</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J15" t="n">
         <v>1.02</v>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="R15" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,19 +3497,19 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O16" t="n">
         <v>1.18</v>
       </c>
       <c r="P16" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q16" t="n">
         <v>1.18</v>
       </c>
       <c r="R16" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
         <v>1.18</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -3667,19 +3667,19 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="G17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K17" t="n">
         <v>950</v>
@@ -3691,19 +3691,19 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.23</v>
       </c>
       <c r="R17" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S17" t="n">
         <v>1.23</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G18" t="n">
         <v>4.6</v>
@@ -3870,7 +3870,7 @@
         <v>1.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
@@ -3885,13 +3885,13 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.22</v>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q18" t="n">
         <v>1.66</v>
@@ -3909,43 +3909,43 @@
         <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
         <v>25</v>
       </c>
       <c r="Y18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z18" t="n">
         <v>14</v>
       </c>
-      <c r="Z18" t="n">
-        <v>16</v>
-      </c>
       <c r="AA18" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB18" t="n">
         <v>23</v>
       </c>
       <c r="AC18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AI18" t="n">
         <v>36</v>
@@ -3966,22 +3966,22 @@
         <v>48</v>
       </c>
       <c r="AO18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3990,10 +3990,10 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4005,26 +4005,26 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.2</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.5</v>
+        <v>28</v>
       </c>
       <c r="BG18" t="n">
         <v>8.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -4055,25 +4055,25 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="L19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
@@ -4088,144 +4088,144 @@
         <v>1.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R19" t="n">
         <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.88</v>
+        <v>1.96</v>
       </c>
       <c r="U19" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="V19" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
       </c>
       <c r="Y19" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AA19" t="n">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK19" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL19" t="n">
         <v>44</v>
       </c>
       <c r="AM19" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO19" t="n">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ19" t="n">
         <v>4.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU19" t="n">
         <v>3.9</v>
       </c>
       <c r="AV19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3.75</v>
       </c>
-      <c r="AY19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>4</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azerbaijan Premier League</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,186 +4240,186 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Neftchi Baku</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Qarabag FK</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.65</v>
+        <v>1.37</v>
       </c>
       <c r="G20" t="n">
-        <v>5.8</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7</v>
+        <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.08</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>2.92</v>
+        <v>4.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="M20" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="N20" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.28</v>
+        <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>1.95</v>
+        <v>2.86</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.76</v>
+        <v>1.43</v>
       </c>
       <c r="R20" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.92</v>
+        <v>2.06</v>
       </c>
       <c r="T20" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V20" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>1.21</v>
+        <v>3.2</v>
       </c>
       <c r="X20" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>44</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
         <v>970</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>20</v>
       </c>
       <c r="AC20" t="n">
         <v>970</v>
       </c>
       <c r="AD20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF20" t="n">
         <v>970</v>
       </c>
-      <c r="AE20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>44</v>
-      </c>
       <c r="AG20" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI20" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="AJ20" t="n">
-        <v>130</v>
+        <v>970</v>
       </c>
       <c r="AK20" t="n">
-        <v>70</v>
+        <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AM20" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN20" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="AO20" t="n">
-        <v>970</v>
+        <v>100</v>
       </c>
       <c r="AP20" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR20" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB20" t="n">
         <v>4.1</v>
       </c>
-      <c r="AT20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BC20" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>20</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF20" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="BG20" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Azerbaijan Premier League</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SAK Klagenfurt</t>
+          <t>Neftchi Baku</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TSV Grafenstein</t>
+          <t>Qarabag FK</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.02</v>
+        <v>3.7</v>
       </c>
       <c r="G21" t="n">
-        <v>110</v>
+        <v>5.6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.02</v>
+        <v>1.73</v>
       </c>
       <c r="I21" t="n">
-        <v>110</v>
+        <v>2.02</v>
       </c>
       <c r="J21" t="n">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>1.08</v>
+        <v>3.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.18</v>
+        <v>1.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.08</v>
+        <v>1.34</v>
       </c>
       <c r="S21" t="n">
-        <v>1.18</v>
+        <v>1.8</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT21" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,186 +4628,186 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>SAK Klagenfurt</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>TSV Grafenstein</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1.45</v>
+        <v>110</v>
       </c>
       <c r="H22" t="n">
-        <v>7.4</v>
+        <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>10.5</v>
+        <v>110</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7</v>
+        <v>1.02</v>
       </c>
       <c r="K22" t="n">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L22" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>6.4</v>
+        <v>1.29</v>
       </c>
       <c r="O22" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>2.66</v>
+        <v>1.29</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>2.06</v>
+        <v>1.18</v>
       </c>
       <c r="T22" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AR22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU22" t="n">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AV22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX22" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AY22" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ22" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BA22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BE22" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF22" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,186 +4822,186 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>SV Donau Klagenfurt</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.64</v>
+        <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.82</v>
+        <v>110</v>
       </c>
       <c r="H23" t="n">
-        <v>2.78</v>
+        <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>3.05</v>
+        <v>110</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>1.02</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="O23" t="n">
-        <v>1.35</v>
+        <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7</v>
+        <v>1.14</v>
       </c>
       <c r="T23" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="W23" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ23" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR23" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AT23" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU23" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV23" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX23" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AY23" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF23" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.14</v>
+        <v>2.64</v>
       </c>
       <c r="G24" t="n">
-        <v>1.17</v>
+        <v>2.82</v>
       </c>
       <c r="H24" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>38</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF24" t="n">
         <v>20</v>
       </c>
-      <c r="I24" t="n">
-        <v>24</v>
-      </c>
-      <c r="J24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="K24" t="n">
-        <v>12</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>85</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>120</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>300</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>20</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>85</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>340</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>210</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>310</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>2.24</v>
-      </c>
       <c r="BG24" t="n">
-        <v>10</v>
+        <v>3.85</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sanliurfaspor</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Muglaspor</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>1.17</v>
       </c>
       <c r="H25" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>1.15</v>
+        <v>4.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="R25" t="n">
-        <v>1.07</v>
+        <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,66 +5399,66 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Muglaspor</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="G26" t="n">
-        <v>1.96</v>
+        <v>160</v>
       </c>
       <c r="H26" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="J26" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.6</v>
+        <v>1.41</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
@@ -5467,116 +5467,116 @@
         <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>5</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -5598,76 +5598,76 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.42</v>
+        <v>1.64</v>
       </c>
       <c r="G27" t="n">
-        <v>1.56</v>
+        <v>1.96</v>
       </c>
       <c r="H27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I27" t="n">
         <v>7</v>
       </c>
-      <c r="I27" t="n">
-        <v>14</v>
-      </c>
       <c r="J27" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="K27" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O27" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>1.71</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="R27" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>2.92</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V27" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>2.64</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
@@ -5679,10 +5679,10 @@
         <v>970</v>
       </c>
       <c r="AD27" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF27" t="n">
         <v>970</v>
@@ -5691,93 +5691,93 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
         <v>970</v>
       </c>
-      <c r="AK27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AQ27" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AS27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB27" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT27" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BC27" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD27" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.7</v>
+        <v>1.42</v>
       </c>
       <c r="G28" t="n">
-        <v>2.9</v>
+        <v>1.54</v>
       </c>
       <c r="H28" t="n">
-        <v>2.62</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>2.82</v>
+        <v>14</v>
       </c>
       <c r="J28" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="X28" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AQ28" t="n">
         <v>3.85</v>
       </c>
-      <c r="L28" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="AR28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD28" t="n">
         <v>3.95</v>
       </c>
-      <c r="O28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U28" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="X28" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX28" t="n">
+      <c r="BE28" t="n">
         <v>4.2</v>
       </c>
-      <c r="AY28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BF28" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F29" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I29" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N29" t="n">
         <v>4</v>
       </c>
-      <c r="G29" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N29" t="n">
-        <v>3.35</v>
-      </c>
       <c r="O29" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="P29" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.18</v>
+        <v>1.72</v>
       </c>
       <c r="R29" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>4.1</v>
+        <v>2.88</v>
       </c>
       <c r="T29" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.9</v>
+        <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="X29" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AB29" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AF29" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI29" t="n">
         <v>44</v>
       </c>
       <c r="AJ29" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM29" t="n">
         <v>90</v>
       </c>
-      <c r="AK29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>130</v>
-      </c>
       <c r="AN29" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AO29" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.6</v>
+        <v>3.75</v>
       </c>
       <c r="AR29" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>22</v>
+        <v>4.6</v>
       </c>
       <c r="AT29" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>3.75</v>
       </c>
       <c r="AZ29" t="n">
-        <v>17.5</v>
+        <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="BB29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF29" t="n">
         <v>17</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>16</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>18</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>55</v>
       </c>
       <c r="BG29" t="n">
         <v>17</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.32</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>2.36</v>
+        <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="I30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J30" t="n">
         <v>3.6</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q30" t="n">
         <v>2.18</v>
       </c>
       <c r="R30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="W30" t="n">
         <v>1.31</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U30" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.74</v>
-      </c>
       <c r="X30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AB30" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE30" t="n">
         <v>24</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AF30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AL30" t="n">
         <v>70</v>
       </c>
-      <c r="AB30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AM30" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AY30" t="n">
         <v>15</v>
       </c>
-      <c r="AE30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI30" t="n">
+      <c r="AZ30" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>30</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF30" t="n">
         <v>55</v>
       </c>
-      <c r="AJ30" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>23</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>20</v>
-      </c>
       <c r="BG30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62</v>
+        <v>2.36</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U31" t="n">
         <v>2.12</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.14</v>
-      </c>
       <c r="V31" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="X31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Z31" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AF31" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI31" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AJ31" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>44</v>
       </c>
       <c r="AM31" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN31" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AO31" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AP31" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
       </c>
       <c r="AV31" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX31" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX31" t="n">
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>18</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG31" t="n">
         <v>15</v>
       </c>
-      <c r="AY31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>85</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>32</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -6568,148 +6568,148 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="G32" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="H32" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J32" t="n">
         <v>3.35</v>
       </c>
-      <c r="J32" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K32" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="U32" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="W32" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y32" t="n">
         <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC32" t="n">
         <v>7.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AF32" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI32" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO32" t="n">
         <v>36</v>
       </c>
-      <c r="AK32" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO32" t="n">
+      <c r="AP32" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AS32" t="n">
         <v>48</v>
       </c>
-      <c r="AP32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>50</v>
-      </c>
       <c r="AT32" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>13</v>
       </c>
       <c r="AW32" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AX32" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AY32" t="n">
         <v>11</v>
@@ -6718,36 +6718,36 @@
         <v>17</v>
       </c>
       <c r="BA32" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>34</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG32" t="n">
         <v>32</v>
       </c>
-      <c r="BB32" t="n">
-        <v>32</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>40</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>25</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>42</v>
-      </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T33" t="n">
         <v>1.94</v>
       </c>
-      <c r="G33" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.86</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>1.84</v>
+        <v>1.64</v>
       </c>
       <c r="X33" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z33" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB33" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC33" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AI33" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK33" t="n">
         <v>30</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>28</v>
       </c>
       <c r="AL33" t="n">
         <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AO33" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="AT33" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,174 +6951,174 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CD Victoria</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Espana</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>110</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="I34" t="n">
-        <v>110</v>
+        <v>5.5</v>
       </c>
       <c r="J34" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.07</v>
+        <v>1.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
       <c r="R34" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="S34" t="n">
-        <v>1.2</v>
+        <v>3.35</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AV34" t="n">
         <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -7150,12 +7150,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CD Olimpia</t>
+          <t>Lobos UPNFM</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>CD Motagua</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -7183,22 +7183,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="O35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -7344,12 +7344,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>CD Victoria</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Real Espana</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -7377,22 +7377,22 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O36" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="R36" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S36" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 11:26:42</t>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>
@@ -7538,25 +7538,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Olancho</t>
+          <t>CD Olimpia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Genesis Huracan</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H37" t="n">
         <v>1.04</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J37" t="n">
         <v>1.02</v>
@@ -7571,146 +7571,340 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:40:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Olancho</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Genesis Huracan</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G38" t="n">
+        <v>110</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I38" t="n">
+        <v>110</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="K38" t="n">
+        <v>950</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O38" t="n">
         <v>1.26</v>
       </c>
-      <c r="P37" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Q37" t="n">
+      <c r="P38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1.26</v>
       </c>
-      <c r="R37" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="R38" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S38" t="n">
         <v>1.26</v>
       </c>
-      <c r="T37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>2026-04-29 11:26:42</t>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-29 13:40:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -760,16 +760,16 @@
         <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="H2" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
         <v>5.3</v>
@@ -808,7 +808,7 @@
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -865,7 +865,7 @@
         <v>450</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -1166,13 +1166,13 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="N4" t="n">
         <v>1.45</v>
       </c>
       <c r="O4" t="n">
-        <v>1.08</v>
+        <v>1.45</v>
       </c>
       <c r="P4" t="n">
         <v>1.45</v>
@@ -1193,10 +1193,10 @@
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
         <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
         <v>2.88</v>
@@ -1384,13 +1384,13 @@
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V5" t="n">
         <v>1.43</v>
       </c>
       <c r="W5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1447,22 +1447,22 @@
         <v>60</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
         <v>4.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AV5" t="n">
         <v>3.8</v>
@@ -1492,7 +1492,7 @@
         <v>4.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF5" t="n">
         <v>4.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>4.3</v>
       </c>
       <c r="G6" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="H6" t="n">
         <v>1.69</v>
@@ -1545,7 +1545,7 @@
         <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1572,7 +1572,7 @@
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="T6" t="n">
         <v>1.92</v>
@@ -1584,7 +1584,7 @@
         <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1644,10 +1644,10 @@
         <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AS6" t="n">
         <v>3.6</v>
@@ -1656,10 +1656,10 @@
         <v>3.55</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AW6" t="n">
         <v>3.65</v>
@@ -1692,11 +1692,11 @@
         <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
         <v>2.66</v>
       </c>
       <c r="I7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S7" t="n">
         <v>3.45</v>
       </c>
-      <c r="J7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.02</v>
-      </c>
       <c r="T7" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W7" t="n">
         <v>1.41</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.42</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1790,7 +1790,7 @@
         <v>23</v>
       </c>
       <c r="AA7" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -1802,7 +1802,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1811,86 +1811,86 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
         <v>55</v>
       </c>
-      <c r="AL7" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>65</v>
-      </c>
       <c r="AO7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>1.58</v>
       </c>
       <c r="P9" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -2154,13 +2154,13 @@
         <v>1.12</v>
       </c>
       <c r="S9" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9" t="n">
         <v>1.35</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -2333,28 +2333,28 @@
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>2.08</v>
+        <v>1.28</v>
       </c>
       <c r="O10" t="n">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.39</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -2697,19 +2697,19 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>1.92</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
         <v>4</v>
@@ -2730,7 +2730,7 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -2748,13 +2748,13 @@
         <v>1.18</v>
       </c>
       <c r="W12" t="n">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Z12" t="n">
         <v>50</v>
@@ -2763,10 +2763,10 @@
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD12" t="n">
         <v>28</v>
@@ -2775,10 +2775,10 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG12" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH12" t="n">
         <v>34</v>
@@ -2787,7 +2787,7 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK12" t="n">
         <v>32</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.95</v>
+        <v>2.54</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.8</v>
+        <v>2.86</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="AT12" t="n">
         <v>3</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.75</v>
+        <v>2.46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.22</v>
+        <v>2.98</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.4</v>
+        <v>2.72</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.9</v>
+        <v>2.92</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.08</v>
+        <v>3</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.4</v>
+        <v>2.74</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.06</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3002,13 +3002,13 @@
         <v>4.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AT13" t="n">
         <v>4.4</v>
@@ -3017,7 +3017,7 @@
         <v>3.7</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AW13" t="n">
         <v>3.95</v>
@@ -3050,11 +3050,11 @@
         <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G14" t="n">
         <v>970</v>
@@ -3118,13 +3118,13 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.05</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -3885,10 +3885,10 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P18" t="n">
         <v>2.22</v>
@@ -3903,7 +3903,7 @@
         <v>2.68</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
         <v>2.28</v>
@@ -3924,7 +3924,7 @@
         <v>14</v>
       </c>
       <c r="AA18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AB18" t="n">
         <v>23</v>
@@ -3948,7 +3948,7 @@
         <v>970</v>
       </c>
       <c r="AI18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ18" t="n">
         <v>100</v>
@@ -3957,7 +3957,7 @@
         <v>60</v>
       </c>
       <c r="AL18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM18" t="n">
         <v>90</v>
@@ -3969,7 +3969,7 @@
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.800000000000001</v>
@@ -3978,10 +3978,10 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3990,10 +3990,10 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4005,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4014,7 +4014,7 @@
         <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="BF18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="H19" t="n">
         <v>6.4</v>
@@ -4067,7 +4067,7 @@
         <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
         <v>5.4</v>
@@ -4106,7 +4106,7 @@
         <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="K20" t="n">
         <v>7.6</v>
@@ -4279,7 +4279,7 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="Q20" t="n">
         <v>1.43</v>
@@ -4360,7 +4360,7 @@
         <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AR20" t="n">
         <v>5</v>
@@ -4369,7 +4369,7 @@
         <v>5.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AU20" t="n">
         <v>4.2</v>
@@ -4381,7 +4381,7 @@
         <v>5.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AY20" t="n">
         <v>8.4</v>
@@ -4396,7 +4396,7 @@
         <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BD20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -4443,28 +4443,28 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="I21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="K21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M21" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
         <v>3.6</v>
@@ -4476,25 +4476,25 @@
         <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="R21" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S21" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="T21" t="n">
         <v>1.8</v>
       </c>
-      <c r="T21" t="n">
-        <v>1.78</v>
-      </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4506,61 +4506,61 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AG21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
       </c>
       <c r="AJ21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM21" t="n">
         <v>130</v>
       </c>
-      <c r="AK21" t="n">
-        <v>70</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>120</v>
-      </c>
       <c r="AN21" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AO21" t="n">
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT21" t="n">
         <v>4</v>
@@ -4569,44 +4569,44 @@
         <v>3.35</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE21" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF21" t="n">
         <v>4.8</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -4661,19 +4661,19 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="Q22" t="n">
         <v>1.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
         <v>1.18</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H24" t="n">
         <v>2.84</v>
@@ -5037,7 +5037,7 @@
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
         <v>3.55</v>
@@ -5052,10 +5052,10 @@
         <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
         <v>2.04</v>
@@ -5070,19 +5070,19 @@
         <v>1.79</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
       </c>
       <c r="W24" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X24" t="n">
         <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
         <v>24</v>
@@ -5136,16 +5136,16 @@
         <v>9.6</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
         <v>5.8</v>
@@ -5154,7 +5154,7 @@
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5166,16 +5166,16 @@
         <v>12.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
         <v>4.1</v>
@@ -5184,11 +5184,11 @@
         <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         <v>1.08</v>
       </c>
       <c r="P25" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q25" t="n">
         <v>1.21</v>
@@ -5258,13 +5258,13 @@
         <v>2.3</v>
       </c>
       <c r="S25" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="T25" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U25" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -5288,13 +5288,13 @@
         <v>24</v>
       </c>
       <c r="AC25" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AD25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AE25" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AF25" t="n">
         <v>14.5</v>
@@ -5306,7 +5306,7 @@
         <v>50</v>
       </c>
       <c r="AI25" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -5315,28 +5315,28 @@
         <v>16.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="AO25" t="n">
-        <v>330</v>
+        <v>310</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AR25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AT25" t="n">
         <v>14</v>
@@ -5345,10 +5345,10 @@
         <v>19.5</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
@@ -5357,10 +5357,10 @@
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
         <v>8.800000000000001</v>
@@ -5369,20 +5369,20 @@
         <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BE25" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.99</v>
+        <v>2.16</v>
       </c>
       <c r="BG25" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>160</v>
+        <v>3.9</v>
       </c>
       <c r="H26" t="n">
-        <v>1.03</v>
+        <v>2.32</v>
       </c>
       <c r="I26" t="n">
-        <v>970</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
-        <v>1.02</v>
+        <v>2.62</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5437,22 +5437,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5461,10 +5461,10 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="G27" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="J27" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="K27" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L27" t="n">
         <v>1.01</v>
@@ -5631,28 +5631,28 @@
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="O27" t="n">
         <v>1.37</v>
       </c>
       <c r="P27" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S27" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>1.64</v>
       </c>
       <c r="U27" t="n">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
         <v>1.01</v>
@@ -5667,25 +5667,25 @@
         <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
         <v>26</v>
       </c>
       <c r="AE27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG27" t="n">
         <v>970</v>
@@ -5697,10 +5697,10 @@
         <v>110</v>
       </c>
       <c r="AJ27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL27" t="n">
         <v>55</v>
@@ -5712,10 +5712,10 @@
         <v>970</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP27" t="n">
-        <v>3.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
         <v>4.1</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
         <v>4.3</v>
@@ -5739,22 +5739,22 @@
         <v>4.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AY27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BA27" t="n">
         <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD27" t="n">
         <v>4.7</v>
@@ -5763,14 +5763,14 @@
         <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG27" t="n">
         <v>5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>1.42</v>
       </c>
       <c r="G28" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="H28" t="n">
         <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="K28" t="n">
         <v>6.6</v>
@@ -5828,7 +5828,7 @@
         <v>4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
         <v>2.12</v>
@@ -5843,13 +5843,13 @@
         <v>2.92</v>
       </c>
       <c r="T28" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W28" t="n">
         <v>2.64</v>
@@ -5861,13 +5861,13 @@
         <v>34</v>
       </c>
       <c r="Z28" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AC28" t="n">
         <v>970</v>
@@ -5876,10 +5876,10 @@
         <v>38</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
         <v>970</v>
@@ -5891,7 +5891,7 @@
         <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>970</v>
@@ -5903,19 +5903,19 @@
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AQ28" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS28" t="n">
         <v>4.3</v>
@@ -5927,7 +5927,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AW28" t="n">
         <v>4.2</v>
@@ -5939,32 +5939,32 @@
         <v>7.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BA28" t="n">
         <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC28" t="n">
         <v>11.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="G29" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H29" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="I29" t="n">
         <v>2.82</v>
@@ -6022,13 +6022,13 @@
         <v>4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q29" t="n">
         <v>1.84</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.72</v>
       </c>
       <c r="R29" t="n">
         <v>1.18</v>
@@ -6043,7 +6043,7 @@
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W29" t="n">
         <v>1.53</v>
@@ -6055,7 +6055,7 @@
         <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA29" t="n">
         <v>48</v>
@@ -6091,7 +6091,7 @@
         <v>34</v>
       </c>
       <c r="AL29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM29" t="n">
         <v>90</v>
@@ -6106,49 +6106,49 @@
         <v>12.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AR29" t="n">
         <v>14.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>14.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF29" t="n">
         <v>17</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -6189,64 +6189,64 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G30" t="n">
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.08</v>
-      </c>
-      <c r="I30" t="n">
-        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>3.6</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T30" t="n">
         <v>1.96</v>
       </c>
       <c r="U30" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="W30" t="n">
         <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z30" t="n">
         <v>11.5</v>
@@ -6276,31 +6276,31 @@
         <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
         <v>90</v>
       </c>
       <c r="AK30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN30" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO30" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR30" t="n">
         <v>10.5</v>
@@ -6309,7 +6309,7 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU30" t="n">
         <v>7.2</v>
@@ -6324,35 +6324,35 @@
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
         <v>17</v>
       </c>
       <c r="BC30" t="n">
-        <v>15.5</v>
+        <v>46</v>
       </c>
       <c r="BD30" t="n">
         <v>16</v>
       </c>
       <c r="BE30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BF30" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -6389,10 +6389,10 @@
         <v>2.36</v>
       </c>
       <c r="H31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
@@ -6401,7 +6401,7 @@
         <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
@@ -6410,7 +6410,7 @@
         <v>3.4</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P31" t="n">
         <v>1.82</v>
@@ -6422,7 +6422,7 @@
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>1.87</v>
@@ -6434,13 +6434,13 @@
         <v>1.38</v>
       </c>
       <c r="W31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
         <v>24</v>
@@ -6458,10 +6458,10 @@
         <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
@@ -6488,7 +6488,7 @@
         <v>22</v>
       </c>
       <c r="AO31" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP31" t="n">
         <v>11.5</v>
@@ -6500,10 +6500,10 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6512,7 +6512,7 @@
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -6524,29 +6524,29 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>23</v>
       </c>
       <c r="BD31" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF31" t="n">
         <v>20</v>
       </c>
       <c r="BG31" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G32" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H32" t="n">
         <v>3.05</v>
       </c>
       <c r="I32" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J32" t="n">
         <v>3.35</v>
@@ -6613,10 +6613,10 @@
         <v>2.14</v>
       </c>
       <c r="R32" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T32" t="n">
         <v>1.85</v>
@@ -6625,16 +6625,16 @@
         <v>2.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W32" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X32" t="n">
         <v>12.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z32" t="n">
         <v>19.5</v>
@@ -6664,46 +6664,46 @@
         <v>18</v>
       </c>
       <c r="AI32" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ32" t="n">
         <v>38</v>
       </c>
       <c r="AK32" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
       </c>
       <c r="AM32" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN32" t="n">
         <v>26</v>
       </c>
       <c r="AO32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP32" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR32" t="n">
         <v>18.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU32" t="n">
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW32" t="n">
         <v>32</v>
@@ -6724,7 +6724,7 @@
         <v>34</v>
       </c>
       <c r="BC32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
@@ -6736,11 +6736,11 @@
         <v>23</v>
       </c>
       <c r="BG32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -6771,61 +6771,61 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G33" t="n">
         <v>2.56</v>
       </c>
       <c r="H33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I33" t="n">
         <v>3.3</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.35</v>
       </c>
-      <c r="J33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="R33" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W33" t="n">
         <v>1.64</v>
       </c>
       <c r="X33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
         <v>11</v>
@@ -6837,16 +6837,16 @@
         <v>60</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC33" t="n">
         <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE33" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF33" t="n">
         <v>14.5</v>
@@ -6870,16 +6870,16 @@
         <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ33" t="n">
         <v>10</v>
@@ -6891,7 +6891,7 @@
         <v>50</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU33" t="n">
         <v>6.8</v>
@@ -6900,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6912,7 +6912,7 @@
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="BB33" t="n">
         <v>32</v>
@@ -6924,17 +6924,17 @@
         <v>44</v>
       </c>
       <c r="BE33" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BF33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG33" t="n">
         <v>25</v>
       </c>
-      <c r="BG33" t="n">
-        <v>42</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -6968,10 +6968,10 @@
         <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H34" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="I34" t="n">
         <v>5.5</v>
@@ -6989,7 +6989,7 @@
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
@@ -6998,13 +6998,13 @@
         <v>1.77</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
         <v>1.84</v>
@@ -7013,10 +7013,10 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
         <v>970</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Q35" t="n">
         <v>1.23</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -7547,46 +7547,46 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.4</v>
       </c>
       <c r="G37" t="n">
-        <v>110</v>
+        <v>1.6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I37" t="n">
-        <v>110</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>1.02</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O37" t="n">
         <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="R37" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2</v>
+        <v>2.28</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7595,70 +7595,70 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W37" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="X37" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
         <v>1.03</v>
@@ -7667,37 +7667,37 @@
         <v>1.03</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
         <v>1.03</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
         <v>1.03</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
         <v>1.03</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 13:40:10</t>
+          <t>2026-04-29 15:53:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -760,19 +760,19 @@
         <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="H2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
@@ -790,10 +790,10 @@
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -808,7 +808,7 @@
         <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -871,13 +871,13 @@
         <v>4.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AU2" t="n">
         <v>3.75</v>
@@ -886,7 +886,7 @@
         <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX2" t="n">
         <v>3.3</v>
@@ -898,7 +898,7 @@
         <v>4.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB2" t="n">
         <v>3.85</v>
@@ -907,7 +907,7 @@
         <v>4.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE2" t="n">
         <v>5.2</v>
@@ -916,11 +916,11 @@
         <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="n">
         <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -972,25 +972,25 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>1.02</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q3" t="n">
         <v>1.34</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="K4" t="n">
         <v>3.85</v>
@@ -1166,25 +1166,25 @@
         <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R4" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="T4" t="n">
         <v>1.95</v>
@@ -1193,10 +1193,10 @@
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W4" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -1342,13 +1342,13 @@
         <v>2.76</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="H5" t="n">
         <v>2.78</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
         <v>2.88</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
@@ -1557,7 +1557,7 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.72</v>
+        <v>2.82</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
@@ -1566,7 +1566,7 @@
         <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
@@ -1584,7 +1584,7 @@
         <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="X6" t="n">
         <v>970</v>
@@ -1692,11 +1692,11 @@
         <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.56</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H7" t="n">
         <v>2.66</v>
@@ -1751,7 +1751,7 @@
         <v>1.1</v>
       </c>
       <c r="N7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
         <v>1.43</v>
@@ -1760,7 +1760,7 @@
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.21</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>3.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="K9" t="n">
         <v>3.2</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>3.55</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="K10" t="n">
         <v>3.15</v>
@@ -2333,13 +2333,13 @@
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.14</v>
       </c>
       <c r="P10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10" t="n">
         <v>1.66</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
         <v>4.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="K11" t="n">
         <v>3.3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2730,7 +2730,7 @@
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
@@ -2799,25 +2799,25 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ12" t="n">
         <v>2.54</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="AU12" t="n">
         <v>3.5</v>
@@ -2835,10 +2835,10 @@
         <v>2.46</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BB12" t="n">
         <v>2.72</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
         <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.52</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
         <v>1.14</v>
@@ -3321,7 +3321,7 @@
         <v>1.54</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -3506,13 +3506,13 @@
         <v>1.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="R16" t="n">
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="T16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>1.85</v>
       </c>
       <c r="I18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
@@ -3912,7 +3912,7 @@
         <v>2.02</v>
       </c>
       <c r="W18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X18" t="n">
         <v>25</v>
@@ -3924,10 +3924,10 @@
         <v>14</v>
       </c>
       <c r="AA18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AB18" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3939,7 +3939,7 @@
         <v>22</v>
       </c>
       <c r="AF18" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG18" t="n">
         <v>970</v>
@@ -3948,7 +3948,7 @@
         <v>970</v>
       </c>
       <c r="AI18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ18" t="n">
         <v>100</v>
@@ -3960,16 +3960,16 @@
         <v>55</v>
       </c>
       <c r="AM18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AO18" t="n">
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.800000000000001</v>
@@ -3978,10 +3978,10 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3990,10 +3990,10 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4005,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4014,7 +4014,7 @@
         <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
         <v>5.4</v>
@@ -4106,7 +4106,7 @@
         <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
@@ -4169,31 +4169,31 @@
         <v>4.8</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS19" t="n">
         <v>5.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AV19" t="n">
         <v>4.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA19" t="n">
         <v>5.5</v>
@@ -4211,14 +4211,14 @@
         <v>5.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BG19" t="n">
         <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G20" t="n">
         <v>1.45</v>
@@ -4264,7 +4264,7 @@
         <v>5.3</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -4279,7 +4279,7 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>3.2</v>
+        <v>2.84</v>
       </c>
       <c r="Q20" t="n">
         <v>1.43</v>
@@ -4360,7 +4360,7 @@
         <v>5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AR20" t="n">
         <v>5</v>
@@ -4369,7 +4369,7 @@
         <v>5.2</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU20" t="n">
         <v>4.2</v>
@@ -4381,7 +4381,7 @@
         <v>5.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AY20" t="n">
         <v>8.4</v>
@@ -4396,7 +4396,7 @@
         <v>4.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD20" t="n">
         <v>20</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -4443,25 +4443,25 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="I21" t="n">
-        <v>2.04</v>
+        <v>1.92</v>
       </c>
       <c r="J21" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M21" t="n">
         <v>1.05</v>
@@ -4473,25 +4473,25 @@
         <v>1.3</v>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>1.81</v>
+        <v>2.52</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="W21" t="n">
         <v>1.2</v>
@@ -4506,7 +4506,7 @@
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
@@ -4518,7 +4518,7 @@
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF21" t="n">
         <v>44</v>
@@ -4551,62 +4551,62 @@
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU21" t="n">
         <v>3.4</v>
       </c>
-      <c r="AR21" t="n">
+      <c r="AV21" t="n">
         <v>3.65</v>
       </c>
-      <c r="AS21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>3.55</v>
-      </c>
       <c r="AW21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG21" t="n">
         <v>3.75</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -4661,19 +4661,19 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="O22" t="n">
         <v>1.18</v>
       </c>
       <c r="P22" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q22" t="n">
         <v>1.18</v>
       </c>
       <c r="R22" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S22" t="n">
         <v>1.18</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5031,19 +5031,19 @@
         <v>2.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
         <v>3.55</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5064,7 +5064,7 @@
         <v>1.32</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T24" t="n">
         <v>1.79</v>
@@ -5082,7 +5082,7 @@
         <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z24" t="n">
         <v>24</v>
@@ -5109,7 +5109,7 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
         <v>60</v>
@@ -5142,10 +5142,10 @@
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT24" t="n">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AU24" t="n">
         <v>5.8</v>
@@ -5154,31 +5154,31 @@
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>12.5</v>
+        <v>3.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC24" t="n">
         <v>4.3</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF24" t="n">
         <v>20</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5252,19 +5252,19 @@
         <v>4.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="R25" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S25" t="n">
         <v>1.64</v>
       </c>
       <c r="T25" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="U25" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -5279,7 +5279,7 @@
         <v>120</v>
       </c>
       <c r="Z25" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
@@ -5294,7 +5294,7 @@
         <v>80</v>
       </c>
       <c r="AE25" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AF25" t="n">
         <v>14.5</v>
@@ -5306,7 +5306,7 @@
         <v>50</v>
       </c>
       <c r="AI25" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -5324,10 +5324,10 @@
         <v>2.44</v>
       </c>
       <c r="AO25" t="n">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AP25" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ25" t="n">
         <v>6.2</v>
@@ -5369,7 +5369,7 @@
         <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE25" t="n">
         <v>6.4</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5416,7 @@
         <v>2.46</v>
       </c>
       <c r="G26" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="H26" t="n">
         <v>2.32</v>
@@ -5428,7 +5428,7 @@
         <v>2.62</v>
       </c>
       <c r="K26" t="n">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
         <v>1.01</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
         <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
         <v>100</v>
@@ -5691,7 +5691,7 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
         <v>110</v>
@@ -5715,7 +5715,7 @@
         <v>140</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AQ27" t="n">
         <v>4.1</v>
@@ -5727,10 +5727,10 @@
         <v>5</v>
       </c>
       <c r="AT27" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV27" t="n">
         <v>4.3</v>
@@ -5739,22 +5739,22 @@
         <v>4.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="AY27" t="n">
         <v>8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="BA27" t="n">
         <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BD27" t="n">
         <v>4.7</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="G28" t="n">
         <v>1.5</v>
@@ -5813,10 +5813,10 @@
         <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="K28" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.29</v>
@@ -5912,7 +5912,7 @@
         <v>3.85</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR28" t="n">
         <v>4.2</v>
@@ -5927,7 +5927,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
         <v>4.2</v>
@@ -5939,7 +5939,7 @@
         <v>7.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BA28" t="n">
         <v>4.2</v>
@@ -5951,7 +5951,7 @@
         <v>11.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BE28" t="n">
         <v>4.3</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -5995,13 +5995,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="H29" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="I29" t="n">
         <v>2.82</v>
@@ -6025,7 +6025,7 @@
         <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q29" t="n">
         <v>1.84</v>
@@ -6034,31 +6034,31 @@
         <v>1.18</v>
       </c>
       <c r="S29" t="n">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U29" t="n">
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.55</v>
       </c>
-      <c r="W29" t="n">
-        <v>1.53</v>
-      </c>
       <c r="X29" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z29" t="n">
         <v>22</v>
       </c>
       <c r="AA29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AB29" t="n">
         <v>14.5</v>
@@ -6073,7 +6073,7 @@
         <v>34</v>
       </c>
       <c r="AF29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG29" t="n">
         <v>14.5</v>
@@ -6085,7 +6085,7 @@
         <v>44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK29" t="n">
         <v>34</v>
@@ -6097,68 +6097,68 @@
         <v>90</v>
       </c>
       <c r="AN29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO29" t="n">
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>12.5</v>
+        <v>4.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>14.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT29" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY29" t="n">
         <v>4.3</v>
       </c>
-      <c r="AY29" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BC29" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF29" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BG29" t="n">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -6189,19 +6189,19 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G30" t="n">
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K30" t="n">
         <v>3.65</v>
@@ -6213,13 +6213,13 @@
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
         <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q30" t="n">
         <v>2.14</v>
@@ -6231,13 +6231,13 @@
         <v>4</v>
       </c>
       <c r="T30" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U30" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V30" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="W30" t="n">
         <v>1.31</v>
@@ -6249,7 +6249,7 @@
         <v>8.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA30" t="n">
         <v>26</v>
@@ -6294,13 +6294,13 @@
         <v>65</v>
       </c>
       <c r="AO30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AR30" t="n">
         <v>10.5</v>
@@ -6309,10 +6309,10 @@
         <v>22</v>
       </c>
       <c r="AT30" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
         <v>10</v>
@@ -6324,7 +6324,7 @@
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ30" t="n">
         <v>17.5</v>
@@ -6333,26 +6333,26 @@
         <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC30" t="n">
         <v>46</v>
       </c>
       <c r="BD30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BE30" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BG30" t="n">
         <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6386,7 @@
         <v>2.32</v>
       </c>
       <c r="G31" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H31" t="n">
         <v>3.55</v>
@@ -6401,7 +6401,7 @@
         <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
@@ -6413,10 +6413,10 @@
         <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -6425,22 +6425,22 @@
         <v>4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U31" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="V31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W31" t="n">
         <v>1.74</v>
       </c>
       <c r="X31" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y31" t="n">
         <v>12.5</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>12</v>
       </c>
       <c r="Z31" t="n">
         <v>24</v>
@@ -6461,7 +6461,7 @@
         <v>46</v>
       </c>
       <c r="AF31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
@@ -6485,13 +6485,13 @@
         <v>110</v>
       </c>
       <c r="AN31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ31" t="n">
         <v>11.5</v>
@@ -6500,10 +6500,10 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6512,7 +6512,7 @@
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AX31" t="n">
         <v>12.5</v>
@@ -6524,29 +6524,29 @@
         <v>16.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC31" t="n">
         <v>23</v>
       </c>
       <c r="BD31" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="BE31" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BF31" t="n">
         <v>20</v>
       </c>
       <c r="BG31" t="n">
-        <v>15.5</v>
+        <v>42</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G32" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H32" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I32" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J32" t="n">
         <v>3.35</v>
@@ -6601,7 +6601,7 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.37</v>
@@ -6619,49 +6619,49 @@
         <v>3.9</v>
       </c>
       <c r="T32" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
         <v>2.14</v>
       </c>
       <c r="V32" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="X32" t="n">
         <v>12.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z32" t="n">
         <v>19.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB32" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC32" t="n">
         <v>7.2</v>
       </c>
       <c r="AD32" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE32" t="n">
         <v>36</v>
       </c>
       <c r="AF32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
         <v>50</v>
@@ -6670,7 +6670,7 @@
         <v>38</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
@@ -6679,7 +6679,7 @@
         <v>100</v>
       </c>
       <c r="AN32" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO32" t="n">
         <v>34</v>
@@ -6688,13 +6688,13 @@
         <v>11.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AS32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AT32" t="n">
         <v>9.6</v>
@@ -6703,28 +6703,28 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW32" t="n">
         <v>32</v>
       </c>
       <c r="AX32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY32" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB32" t="n">
         <v>34</v>
       </c>
       <c r="BC32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="G33" t="n">
         <v>2.56</v>
@@ -6789,19 +6789,19 @@
         <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M33" t="n">
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P33" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="Q33" t="n">
         <v>2.28</v>
@@ -6813,10 +6813,10 @@
         <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U33" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
         <v>1.43</v>
@@ -6837,7 +6837,7 @@
         <v>60</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC33" t="n">
         <v>7.2</v>
@@ -6873,7 +6873,7 @@
         <v>110</v>
       </c>
       <c r="AN33" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO33" t="n">
         <v>46</v>
@@ -6882,7 +6882,7 @@
         <v>10.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR33" t="n">
         <v>19</v>
@@ -6900,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6912,7 +6912,7 @@
         <v>17</v>
       </c>
       <c r="BA33" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB33" t="n">
         <v>32</v>
@@ -6930,11 +6930,11 @@
         <v>24</v>
       </c>
       <c r="BG33" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -6971,7 +6971,7 @@
         <v>2.26</v>
       </c>
       <c r="H34" t="n">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="I34" t="n">
         <v>5.5</v>
@@ -7013,7 +7013,7 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W34" t="n">
         <v>1.79</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="Q35" t="n">
         <v>1.23</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -7547,25 +7547,25 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
@@ -7577,16 +7577,16 @@
         <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.48</v>
+        <v>1.02</v>
       </c>
       <c r="R37" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7595,122 +7595,122 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="X37" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y37" t="n">
         <v>34</v>
       </c>
       <c r="Z37" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>13.5</v>
+        <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AK37" t="n">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL37" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 15:53:50</t>
+          <t>2026-04-29 18:09:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -769,10 +769,10 @@
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
@@ -784,16 +784,16 @@
         <v>3.35</v>
       </c>
       <c r="O2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
         <v>1.81</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S2" t="n">
         <v>3.25</v>
@@ -811,7 +811,7 @@
         <v>2.92</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y2" t="n">
         <v>30</v>
@@ -850,7 +850,7 @@
         <v>14</v>
       </c>
       <c r="AK2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
         <v>60</v>
@@ -868,59 +868,59 @@
         <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA2" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>1.09</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -981,140 +981,140 @@
         <v>1.34</v>
       </c>
       <c r="P3" t="n">
-        <v>1.29</v>
+        <v>1.83</v>
       </c>
       <c r="Q3" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R3" t="n">
         <v>1.34</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H4" t="n">
         <v>2.5</v>
@@ -1160,7 +1160,7 @@
         <v>2.86</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.45</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1193,7 +1193,7 @@
         <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W4" t="n">
         <v>1.39</v>
@@ -1223,13 +1223,13 @@
         <v>44</v>
       </c>
       <c r="AF4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>48</v>
       </c>
       <c r="AP4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AU4" t="n">
         <v>3.5</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AV4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="BB4" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.7</v>
+        <v>2.22</v>
       </c>
       <c r="BD4" t="n">
-        <v>4.8</v>
+        <v>1.85</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.9</v>
+        <v>1.88</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.7</v>
+        <v>1.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
         <v>1.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
@@ -1545,7 +1545,7 @@
         <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
@@ -1584,10 +1584,10 @@
         <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="Y6" t="n">
         <v>9</v>
@@ -1644,59 +1644,59 @@
         <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -1727,55 +1727,55 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="G7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="J7" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="W7" t="n">
         <v>1.41</v>
@@ -1814,83 +1814,83 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
         <v>60</v>
       </c>
       <c r="AK7" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO7" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AQ7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BA7" t="n">
         <v>3.1</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="BB7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BD7" t="n">
         <v>3.1</v>
       </c>
-      <c r="AU7" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>4</v>
-      </c>
       <c r="BE7" t="n">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.95</v>
+        <v>3.1</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>8</v>
+        <v>950</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1945,34 +1945,34 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="S8" t="n">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U8" t="n">
         <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.54</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -2330,25 +2330,25 @@
         <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="O10" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="P10" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
         <v>1.11</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>2.34</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="I11" t="n">
         <v>4.5</v>
@@ -2527,7 +2527,7 @@
         <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O11" t="n">
         <v>1.55</v>
@@ -2554,7 +2554,7 @@
         <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X11" t="n">
         <v>9.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
         <v>1.92</v>
@@ -2712,7 +2712,7 @@
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>9.4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="I13" t="n">
         <v>1.61</v>
@@ -2915,7 +2915,7 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="O13" t="n">
         <v>1.19</v>
@@ -2927,7 +2927,7 @@
         <v>1.58</v>
       </c>
       <c r="R13" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
         <v>2.38</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="G14" t="n">
         <v>970</v>
       </c>
       <c r="H14" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="I14" t="n">
         <v>970</v>
@@ -3100,7 +3100,7 @@
         <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3127,7 +3127,7 @@
         <v>1.33</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U14" t="n">
         <v>1.01</v>
@@ -3136,7 +3136,7 @@
         <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X14" t="n">
         <v>1000</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="H15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J15" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,13 +3303,13 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
         <v>1.14</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="G17" t="n">
         <v>110</v>
       </c>
       <c r="H17" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="I17" t="n">
         <v>110</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -3894,7 +3894,7 @@
         <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
         <v>1.49</v>
@@ -3909,7 +3909,7 @@
         <v>2.28</v>
       </c>
       <c r="V18" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W18" t="n">
         <v>1.28</v>
@@ -3954,10 +3954,10 @@
         <v>100</v>
       </c>
       <c r="AK18" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AL18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM18" t="n">
         <v>80</v>
@@ -3981,7 +3981,7 @@
         <v>5.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3990,7 +3990,7 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX18" t="n">
         <v>6.2</v>
@@ -4005,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G19" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="H19" t="n">
         <v>6.4</v>
@@ -4067,7 +4067,7 @@
         <v>9.6</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>5.4</v>
@@ -4106,7 +4106,7 @@
         <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
@@ -4118,7 +4118,7 @@
         <v>70</v>
       </c>
       <c r="AA19" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
@@ -4178,19 +4178,19 @@
         <v>3.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AV19" t="n">
         <v>4.9</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="AX19" t="n">
         <v>3.65</v>
       </c>
       <c r="AY19" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AZ19" t="n">
         <v>4.9</v>
@@ -4199,7 +4199,7 @@
         <v>5.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC19" t="n">
         <v>4.4</v>
@@ -4211,14 +4211,14 @@
         <v>5.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG19" t="n">
         <v>5.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G20" t="n">
         <v>1.45</v>
@@ -4261,10 +4261,10 @@
         <v>10.5</v>
       </c>
       <c r="J20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K20" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -4288,10 +4288,10 @@
         <v>1.75</v>
       </c>
       <c r="S20" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T20" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="U20" t="n">
         <v>2.16</v>
@@ -4318,7 +4318,7 @@
         <v>970</v>
       </c>
       <c r="AC20" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AD20" t="n">
         <v>36</v>
@@ -4357,22 +4357,22 @@
         <v>100</v>
       </c>
       <c r="AP20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AQ20" t="n">
         <v>4.8</v>
       </c>
       <c r="AR20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT20" t="n">
         <v>4.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
@@ -4381,7 +4381,7 @@
         <v>5.1</v>
       </c>
       <c r="AX20" t="n">
-        <v>3.8</v>
+        <v>8.6</v>
       </c>
       <c r="AY20" t="n">
         <v>8.4</v>
@@ -4390,29 +4390,29 @@
         <v>4.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC20" t="n">
         <v>4.3</v>
       </c>
       <c r="BD20" t="n">
-        <v>20</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF20" t="n">
         <v>3.85</v>
       </c>
       <c r="BG20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -4443,43 +4443,43 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="I21" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="P21" t="n">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="S21" t="n">
         <v>2.52</v>
@@ -4491,10 +4491,10 @@
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
@@ -4521,7 +4521,7 @@
         <v>22</v>
       </c>
       <c r="AF21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG21" t="n">
         <v>23</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.26</v>
+        <v>1.02</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
         <v>2.8</v>
       </c>
       <c r="H24" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I24" t="n">
         <v>3.05</v>
       </c>
       <c r="J24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.44</v>
@@ -5049,28 +5049,28 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S24" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T24" t="n">
         <v>1.79</v>
       </c>
       <c r="U24" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -5097,7 +5097,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE24" t="n">
         <v>42</v>
@@ -5166,7 +5166,7 @@
         <v>3.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
         <v>4.3</v>
@@ -5178,7 +5178,7 @@
         <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF24" t="n">
         <v>20</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="G25" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="H25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L25" t="n">
         <v>1.13</v>
@@ -5243,28 +5243,28 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="O25" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P25" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R25" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S25" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="T25" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -5273,94 +5273,94 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AC25" t="n">
         <v>29</v>
       </c>
       <c r="AD25" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
         <v>14.5</v>
       </c>
-      <c r="AG25" t="n">
-        <v>18</v>
-      </c>
       <c r="AH25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>280</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>36</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR25" t="n">
         <v>50</v>
       </c>
-      <c r="AI25" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ25" t="n">
+      <c r="AS25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY25" t="n">
         <v>12</v>
       </c>
-      <c r="AK25" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL25" t="n">
+      <c r="AZ25" t="n">
+        <v>34</v>
+      </c>
+      <c r="BA25" t="n">
         <v>44</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>180</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>290</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>6</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>6.4</v>
       </c>
       <c r="BB25" t="n">
         <v>8.800000000000001</v>
@@ -5369,20 +5369,20 @@
         <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.4</v>
+        <v>44</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.46</v>
+        <v>2.26</v>
       </c>
       <c r="G26" t="n">
         <v>3.75</v>
@@ -5425,7 +5425,7 @@
         <v>3.3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5437,25 +5437,25 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="U26" t="n">
         <v>1.01</v>
@@ -5464,7 +5464,7 @@
         <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5751,10 +5751,10 @@
         <v>4.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BD27" t="n">
         <v>4.7</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5804,10 +5804,10 @@
         <v>1.38</v>
       </c>
       <c r="G28" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="I28" t="n">
         <v>11</v>
@@ -5825,7 +5825,7 @@
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
         <v>1.26</v>
@@ -5834,10 +5834,10 @@
         <v>2.12</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S28" t="n">
         <v>2.92</v>
@@ -5852,7 +5852,7 @@
         <v>1.1</v>
       </c>
       <c r="W28" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X28" t="n">
         <v>23</v>
@@ -5897,19 +5897,19 @@
         <v>970</v>
       </c>
       <c r="AL28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AQ28" t="n">
         <v>4.2</v>
@@ -5918,7 +5918,7 @@
         <v>4.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT28" t="n">
         <v>6.2</v>
@@ -5927,10 +5927,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX28" t="n">
         <v>6.6</v>
@@ -5939,10 +5939,10 @@
         <v>7.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB28" t="n">
         <v>9.199999999999999</v>
@@ -5951,7 +5951,7 @@
         <v>11.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE28" t="n">
         <v>4.3</v>
@@ -5960,11 +5960,11 @@
         <v>5.4</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I29" t="n">
         <v>2.82</v>
@@ -6013,7 +6013,7 @@
         <v>3.85</v>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
@@ -6046,7 +6046,7 @@
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
@@ -6061,7 +6061,7 @@
         <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC29" t="n">
         <v>9.6</v>
@@ -6097,68 +6097,68 @@
         <v>90</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ29" t="n">
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY29" t="n">
         <v>4.4</v>
       </c>
-      <c r="AY29" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AZ29" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA29" t="n">
         <v>5.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD29" t="n">
         <v>5.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -6195,13 +6195,13 @@
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I30" t="n">
         <v>2.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K30" t="n">
         <v>3.65</v>
@@ -6213,13 +6213,13 @@
         <v>1.08</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O30" t="n">
         <v>1.39</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q30" t="n">
         <v>2.14</v>
@@ -6228,13 +6228,13 @@
         <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T30" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U30" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="V30" t="n">
         <v>1.9</v>
@@ -6243,7 +6243,7 @@
         <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y30" t="n">
         <v>8.6</v>
@@ -6261,10 +6261,10 @@
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF30" t="n">
         <v>29</v>
@@ -6273,10 +6273,10 @@
         <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ30" t="n">
         <v>90</v>
@@ -6306,22 +6306,22 @@
         <v>10.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -6330,29 +6330,29 @@
         <v>17.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BD30" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BE30" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BF30" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BG30" t="n">
         <v>16</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -6383,49 +6383,49 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G31" t="n">
         <v>2.34</v>
       </c>
       <c r="H31" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U31" t="n">
         <v>2.08</v>
@@ -6452,13 +6452,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
         <v>15</v>
       </c>
       <c r="AE31" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF31" t="n">
         <v>14</v>
@@ -6485,10 +6485,10 @@
         <v>110</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP31" t="n">
         <v>11</v>
@@ -6500,13 +6500,13 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AT31" t="n">
         <v>8.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV31" t="n">
         <v>13.5</v>
@@ -6515,10 +6515,10 @@
         <v>40</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
         <v>16.5</v>
@@ -6527,26 +6527,26 @@
         <v>50</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>23</v>
       </c>
       <c r="BD31" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE31" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="G32" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="H32" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="I32" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="J32" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
         <v>1.45</v>
@@ -6601,34 +6601,34 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U32" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W32" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X32" t="n">
         <v>12.5</v>
@@ -6637,37 +6637,37 @@
         <v>11</v>
       </c>
       <c r="Z32" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AB32" t="n">
         <v>10.5</v>
       </c>
       <c r="AC32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD32" t="n">
         <v>13</v>
       </c>
       <c r="AE32" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK32" t="n">
         <v>29</v>
@@ -6676,7 +6676,7 @@
         <v>44</v>
       </c>
       <c r="AM32" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN32" t="n">
         <v>27</v>
@@ -6685,43 +6685,43 @@
         <v>34</v>
       </c>
       <c r="AP32" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR32" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS32" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT32" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY32" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BC32" t="n">
         <v>27</v>
@@ -6733,14 +6733,14 @@
         <v>85</v>
       </c>
       <c r="BF32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BG32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -6780,7 +6780,7 @@
         <v>3.25</v>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J33" t="n">
         <v>3.3</v>
@@ -6795,16 +6795,16 @@
         <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O33" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P33" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R33" t="n">
         <v>1.29</v>
@@ -6813,13 +6813,13 @@
         <v>4.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U33" t="n">
         <v>2.02</v>
       </c>
       <c r="V33" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
         <v>1.64</v>
@@ -6837,7 +6837,7 @@
         <v>60</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AC33" t="n">
         <v>7.2</v>
@@ -6873,10 +6873,10 @@
         <v>110</v>
       </c>
       <c r="AN33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP33" t="n">
         <v>10.5</v>
@@ -6891,7 +6891,7 @@
         <v>50</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU33" t="n">
         <v>6.8</v>
@@ -6918,7 +6918,7 @@
         <v>32</v>
       </c>
       <c r="BC33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD33" t="n">
         <v>44</v>
@@ -6930,11 +6930,11 @@
         <v>24</v>
       </c>
       <c r="BG33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>1.91</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H34" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="J34" t="n">
         <v>3</v>
@@ -7013,10 +7013,10 @@
         <v>1.94</v>
       </c>
       <c r="V34" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="X34" t="n">
         <v>970</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
         <v>1.23</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -7550,19 +7550,19 @@
         <v>1.41</v>
       </c>
       <c r="G37" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H37" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
         <v>10.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="K37" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="L37" t="n">
         <v>1.26</v>
@@ -7577,16 +7577,16 @@
         <v>1.2</v>
       </c>
       <c r="P37" t="n">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="R37" t="n">
         <v>1.36</v>
       </c>
       <c r="S37" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7598,7 +7598,7 @@
         <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="X37" t="n">
         <v>26</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 18:09:56</t>
+          <t>2026-04-29 20:25:36</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -760,7 +760,7 @@
         <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="H2" t="n">
         <v>8</v>
@@ -769,49 +769,49 @@
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.33</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U2" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="X2" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Y2" t="n">
         <v>30</v>
@@ -820,107 +820,107 @@
         <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>540</v>
+        <v>470</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
         <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AE2" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AJ2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
         <v>19.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
-        <v>280</v>
+        <v>230</v>
       </c>
       <c r="AN2" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>450</v>
+        <v>350</v>
       </c>
       <c r="AP2" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AU2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX2" t="n">
         <v>3.8</v>
       </c>
-      <c r="AV2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AY2" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -957,25 +957,25 @@
         <v>1.6</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
@@ -1011,7 +1011,7 @@
         <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="n">
         <v>330</v>
@@ -1041,7 +1041,7 @@
         <v>150</v>
       </c>
       <c r="AJ3" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
         <v>18</v>
@@ -1059,62 +1059,62 @@
         <v>240</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AU3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX3" t="n">
         <v>3.9</v>
       </c>
-      <c r="AV3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB3" t="n">
         <v>4.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1151,10 +1151,10 @@
         <v>3.55</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="I4" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J4" t="n">
         <v>2.86</v>
@@ -1172,28 +1172,28 @@
         <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
         <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
         <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.39</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
         <v>55</v>
@@ -1247,7 +1247,7 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
         <v>48</v>
@@ -1259,31 +1259,31 @@
         <v>3.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AW4" t="n">
         <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>3.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="BA4" t="n">
         <v>1.85</v>
@@ -1292,10 +1292,10 @@
         <v>1.85</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.22</v>
+        <v>1.84</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="BE4" t="n">
         <v>1.88</v>
@@ -1304,11 +1304,11 @@
         <v>1.85</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="G5" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J5" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="K5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
@@ -1366,61 +1366,61 @@
         <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AA5" t="n">
         <v>65</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>50</v>
       </c>
       <c r="AF5" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1429,7 +1429,7 @@
         <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AK5" t="n">
         <v>50</v>
@@ -1438,71 +1438,71 @@
         <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>230</v>
       </c>
       <c r="AN5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO5" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.7</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
@@ -1557,7 +1557,7 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
@@ -1566,13 +1566,13 @@
         <v>1.69</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="R6" t="n">
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>2.68</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.92</v>
@@ -1590,34 +1590,34 @@
         <v>15</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AA6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE6" t="n">
         <v>23</v>
       </c>
-      <c r="AB6" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>25</v>
-      </c>
       <c r="AF6" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AG6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI6" t="n">
         <v>55</v>
@@ -1641,62 +1641,62 @@
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="G7" t="n">
         <v>3.5</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I7" t="n">
         <v>3.6</v>
@@ -1742,10 +1742,10 @@
         <v>2.82</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
@@ -1754,7 +1754,7 @@
         <v>2.42</v>
       </c>
       <c r="O7" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
         <v>1.52</v>
@@ -1775,10 +1775,10 @@
         <v>1.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1814,7 +1814,7 @@
         <v>25</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ7" t="n">
         <v>60</v>
@@ -1835,62 +1835,62 @@
         <v>70</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.84</v>
+        <v>3.85</v>
       </c>
       <c r="AS7" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="AT7" t="n">
         <v>3.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.2</v>
+        <v>6</v>
       </c>
       <c r="AV7" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AW7" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="AY7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>3.9</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>2.86</v>
-      </c>
       <c r="BA7" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.05</v>
+        <v>4.3</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="H8" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="I8" t="n">
         <v>4.2</v>
@@ -1936,43 +1936,43 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M8" t="n">
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.3</v>
+        <v>1.87</v>
       </c>
       <c r="R8" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W8" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="X8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2345,7 +2345,7 @@
         <v>1.01</v>
       </c>
       <c r="R10" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S10" t="n">
         <v>1.05</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3088,16 +3088,16 @@
         <v>1.38</v>
       </c>
       <c r="G14" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="H14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="I14" t="n">
+        <v>990</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.09</v>
-      </c>
-      <c r="I14" t="n">
-        <v>970</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
@@ -3109,7 +3109,7 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O14" t="n">
         <v>1.01</v>
@@ -3118,19 +3118,19 @@
         <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="T14" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.02</v>
       </c>
       <c r="G15" t="n">
-        <v>300</v>
+        <v>990</v>
       </c>
       <c r="H15" t="n">
         <v>1.03</v>
       </c>
       <c r="I15" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,19 +3303,19 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
         <v>1.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
         <v>1.54</v>
@@ -3324,7 +3324,7 @@
         <v>1.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="H16" t="n">
         <v>1.02</v>
       </c>
       <c r="I16" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3497,7 +3497,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.18</v>
@@ -3515,10 +3515,10 @@
         <v>1.23</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3670,16 +3670,16 @@
         <v>1.35</v>
       </c>
       <c r="G17" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H17" t="n">
         <v>1.35</v>
       </c>
       <c r="I17" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J17" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
@@ -3709,10 +3709,10 @@
         <v>1.23</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G18" t="n">
         <v>4.5</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="I18" t="n">
         <v>2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.27</v>
@@ -3894,16 +3894,16 @@
         <v>2.22</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
         <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U18" t="n">
         <v>2.28</v>
@@ -3915,10 +3915,10 @@
         <v>1.28</v>
       </c>
       <c r="X18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
         <v>14</v>
@@ -3930,10 +3930,10 @@
         <v>970</v>
       </c>
       <c r="AC18" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE18" t="n">
         <v>22</v>
@@ -3969,7 +3969,7 @@
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.800000000000001</v>
@@ -3978,10 +3978,10 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
@@ -3990,10 +3990,10 @@
         <v>9</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4005,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4014,7 +4014,7 @@
         <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF18" t="n">
         <v>28</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="H19" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="K19" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4079,34 +4079,34 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
       </c>
       <c r="P19" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q19" t="n">
         <v>1.8</v>
       </c>
       <c r="R19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S19" t="n">
         <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U19" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.56</v>
+        <v>2.86</v>
       </c>
       <c r="X19" t="n">
         <v>18</v>
@@ -4115,10 +4115,10 @@
         <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AA19" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AB19" t="n">
         <v>8.800000000000001</v>
@@ -4127,98 +4127,98 @@
         <v>12</v>
       </c>
       <c r="AD19" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AE19" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="AF19" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK19" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AL19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM19" t="n">
         <v>200</v>
       </c>
       <c r="AN19" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO19" t="n">
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AQ19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>4.8</v>
       </c>
-      <c r="AR19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AS19" t="n">
+      <c r="BD19" t="n">
         <v>5.7</v>
       </c>
-      <c r="AT19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BE19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3.85</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.75</v>
-      </c>
       <c r="BG19" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4252,13 +4252,13 @@
         <v>1.37</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="H20" t="n">
         <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J20" t="n">
         <v>5.4</v>
@@ -4300,7 +4300,7 @@
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="X20" t="n">
         <v>40</v>
@@ -4360,7 +4360,7 @@
         <v>5.1</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR20" t="n">
         <v>5.1</v>
@@ -4372,7 +4372,7 @@
         <v>4.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AV20" t="n">
         <v>5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="G21" t="n">
         <v>6.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="I21" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -4464,13 +4464,13 @@
         <v>1.31</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N21" t="n">
         <v>2.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="P21" t="n">
         <v>1.79</v>
@@ -4485,13 +4485,13 @@
         <v>2.52</v>
       </c>
       <c r="T21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U21" t="n">
         <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="W21" t="n">
         <v>1.21</v>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AR21" t="n">
         <v>3.7</v>
@@ -4569,7 +4569,7 @@
         <v>3.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AW21" t="n">
         <v>4.2</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H23" t="n">
         <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>110</v>
+        <v>870</v>
       </c>
       <c r="J23" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K23" t="n">
         <v>950</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5040,16 +5040,16 @@
         <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
@@ -5067,10 +5067,10 @@
         <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V24" t="n">
         <v>1.48</v>
@@ -5106,16 +5106,16 @@
         <v>22</v>
       </c>
       <c r="AG24" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK24" t="n">
         <v>38</v>
@@ -5130,7 +5130,7 @@
         <v>34</v>
       </c>
       <c r="AO24" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP24" t="n">
         <v>9.6</v>
@@ -5142,7 +5142,7 @@
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT24" t="n">
         <v>9.4</v>
@@ -5154,7 +5154,7 @@
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5163,32 +5163,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
         <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5222,16 +5222,16 @@
         <v>1.13</v>
       </c>
       <c r="G25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="H25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I25" t="n">
         <v>32</v>
       </c>
       <c r="J25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="K25" t="n">
         <v>13</v>
@@ -5243,25 +5243,25 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.07</v>
       </c>
       <c r="P25" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Q25" t="n">
         <v>1.23</v>
       </c>
       <c r="R25" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="S25" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T25" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U25" t="n">
         <v>2.02</v>
@@ -5285,7 +5285,7 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AC25" t="n">
         <v>29</v>
@@ -5342,7 +5342,7 @@
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AV25" t="n">
         <v>32</v>
@@ -5354,10 +5354,10 @@
         <v>11</v>
       </c>
       <c r="AY25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BA25" t="n">
         <v>44</v>
@@ -5369,20 +5369,20 @@
         <v>12.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="BE25" t="n">
         <v>44</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="BG25" t="n">
         <v>50</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5431,13 +5431,13 @@
         <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.59</v>
+        <v>2.58</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
@@ -5452,13 +5452,13 @@
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>1.92</v>
+        <v>2.66</v>
       </c>
       <c r="T26" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V26" t="n">
         <v>1.43</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.01</v>
       </c>
       <c r="G27" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H27" t="n">
         <v>1.01</v>
@@ -5625,13 +5625,13 @@
         <v>1000</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.37</v>
@@ -5739,7 +5739,7 @@
         <v>4.9</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AY27" t="n">
         <v>8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -5807,13 +5807,13 @@
         <v>1.46</v>
       </c>
       <c r="H28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I28" t="n">
         <v>11</v>
       </c>
       <c r="J28" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K28" t="n">
         <v>6.4</v>
@@ -5840,7 +5840,7 @@
         <v>1.43</v>
       </c>
       <c r="S28" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="T28" t="n">
         <v>1.96</v>
@@ -5906,7 +5906,7 @@
         <v>8.4</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AP28" t="n">
         <v>3.9</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6031,16 +6031,16 @@
         <v>1.84</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="T29" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.54</v>
@@ -6112,7 +6112,7 @@
         <v>4.7</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT29" t="n">
         <v>4.4</v>
@@ -6145,7 +6145,7 @@
         <v>5.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
         <v>5.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I30" t="n">
         <v>2.1</v>
@@ -6222,7 +6222,7 @@
         <v>1.82</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R30" t="n">
         <v>1.3</v>
@@ -6288,7 +6288,7 @@
         <v>65</v>
       </c>
       <c r="AM30" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN30" t="n">
         <v>65</v>
@@ -6333,13 +6333,13 @@
         <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
         <v>48</v>
       </c>
       <c r="BD30" t="n">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="BE30" t="n">
         <v>18</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6401,19 +6401,19 @@
         <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="Q31" t="n">
         <v>2.14</v>
@@ -6422,13 +6422,13 @@
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T31" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V31" t="n">
         <v>1.37</v>
@@ -6437,7 +6437,7 @@
         <v>1.74</v>
       </c>
       <c r="X31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y31" t="n">
         <v>12.5</v>
@@ -6467,7 +6467,7 @@
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI31" t="n">
         <v>60</v>
@@ -6500,7 +6500,7 @@
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AT31" t="n">
         <v>8.4</v>
@@ -6515,7 +6515,7 @@
         <v>40</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
@@ -6533,7 +6533,7 @@
         <v>23</v>
       </c>
       <c r="BD31" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE31" t="n">
         <v>16.5</v>
@@ -6542,11 +6542,11 @@
         <v>19.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6580,13 +6580,13 @@
         <v>2.74</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I32" t="n">
         <v>2.9</v>
-      </c>
-      <c r="I32" t="n">
-        <v>2.92</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -6643,22 +6643,22 @@
         <v>46</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC32" t="n">
         <v>7.4</v>
       </c>
       <c r="AD32" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>17</v>
@@ -6667,7 +6667,7 @@
         <v>46</v>
       </c>
       <c r="AJ32" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK32" t="n">
         <v>29</v>
@@ -6679,10 +6679,10 @@
         <v>90</v>
       </c>
       <c r="AN32" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AO32" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP32" t="n">
         <v>12</v>
@@ -6709,19 +6709,19 @@
         <v>30</v>
       </c>
       <c r="AX32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY32" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA32" t="n">
         <v>42</v>
       </c>
       <c r="BB32" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BC32" t="n">
         <v>27</v>
@@ -6736,11 +6736,11 @@
         <v>25</v>
       </c>
       <c r="BG32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>2.52</v>
       </c>
       <c r="G33" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H33" t="n">
         <v>3.25</v>
@@ -6798,28 +6798,28 @@
         <v>3.35</v>
       </c>
       <c r="O33" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R33" t="n">
         <v>1.29</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T33" t="n">
         <v>1.9</v>
       </c>
       <c r="U33" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V33" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W33" t="n">
         <v>1.64</v>
@@ -6828,7 +6828,7 @@
         <v>11.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z33" t="n">
         <v>21</v>
@@ -6855,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI33" t="n">
         <v>60</v>
@@ -6873,7 +6873,7 @@
         <v>110</v>
       </c>
       <c r="AN33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO33" t="n">
         <v>44</v>
@@ -6900,7 +6900,7 @@
         <v>13</v>
       </c>
       <c r="AW33" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6909,7 +6909,7 @@
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA33" t="n">
         <v>50</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7079,10 +7079,10 @@
         <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT34" t="n">
         <v>6.2</v>
@@ -7091,10 +7091,10 @@
         <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX34" t="n">
         <v>8.800000000000001</v>
@@ -7103,32 +7103,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7553,13 +7553,13 @@
         <v>1.62</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I37" t="n">
         <v>10.5</v>
       </c>
       <c r="J37" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K37" t="n">
         <v>7</v>
@@ -7571,22 +7571,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="O37" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P37" t="n">
-        <v>1.93</v>
+        <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="R37" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>2.16</v>
+        <v>1.21</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 20:25:36</t>
+          <t>2026-04-29 22:41:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="G2" t="n">
         <v>1.5</v>
       </c>
       <c r="H2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2" t="n">
         <v>13</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -784,25 +784,25 @@
         <v>3.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q2" t="n">
         <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
         <v>1.09</v>
@@ -871,31 +871,31 @@
         <v>5.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AS2" t="n">
         <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AU2" t="n">
         <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
         <v>6.4</v>
@@ -907,20 +907,20 @@
         <v>5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BG2" t="n">
         <v>6.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -951,46 +951,46 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K3" t="n">
         <v>4.8</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P3" t="n">
         <v>1.83</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.77</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
         <v>2.02</v>
@@ -999,10 +999,10 @@
         <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1011,7 +1011,7 @@
         <v>24</v>
       </c>
       <c r="Z3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
         <v>330</v>
@@ -1029,7 +1029,7 @@
         <v>160</v>
       </c>
       <c r="AF3" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AG3" t="n">
         <v>12.5</v>
@@ -1059,62 +1059,62 @@
         <v>240</v>
       </c>
       <c r="AP3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU3" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AV3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR3" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BA3" t="n">
+      <c r="BD3" t="n">
         <v>5.9</v>
       </c>
-      <c r="BB3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE3" t="n">
-        <v>6</v>
+        <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="G4" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="H4" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="J4" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P4" t="n">
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="T4" t="n">
         <v>1.95</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W4" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X4" t="n">
         <v>970</v>
@@ -1208,7 +1208,7 @@
         <v>970</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB4" t="n">
         <v>970</v>
@@ -1220,10 +1220,10 @@
         <v>970</v>
       </c>
       <c r="AE4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>970</v>
@@ -1238,7 +1238,7 @@
         <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AL4" t="n">
         <v>1000</v>
@@ -1250,65 +1250,65 @@
         <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.8</v>
+        <v>2.96</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>2.9</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.3</v>
+        <v>2.84</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="AX4" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="AY4" t="n">
-        <v>3.7</v>
+        <v>2.56</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.84</v>
+        <v>3.35</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.86</v>
+        <v>2.96</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.88</v>
+        <v>130</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
         <v>2.8</v>
@@ -1372,7 +1372,7 @@
         <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1387,7 +1387,7 @@
         <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
         <v>1.46</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G6" t="n">
         <v>6.4</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I6" t="n">
         <v>1.9</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
@@ -1557,13 +1557,13 @@
         <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>1.35</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
         <v>1.94</v>
@@ -1572,19 +1572,19 @@
         <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>3.65</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V6" t="n">
         <v>2.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1602,13 +1602,13 @@
         <v>21</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
       </c>
       <c r="AE6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF6" t="n">
         <v>48</v>
@@ -1620,7 +1620,7 @@
         <v>24</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
@@ -1632,71 +1632,71 @@
         <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AU6" t="n">
         <v>3.95</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW6" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1751,10 +1751,10 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P7" t="n">
         <v>1.52</v>
@@ -1766,7 +1766,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.99</v>
@@ -1850,7 +1850,7 @@
         <v>3.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="AV7" t="n">
         <v>3.85</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -1921,170 +1921,170 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.95</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="H8" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="I8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="X8" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.2</v>
       </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG8" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="G9" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.56</v>
+        <v>2.74</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.14</v>
       </c>
-      <c r="N9" t="n">
-        <v>2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
         <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA9" t="n">
         <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG9" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI9" t="n">
         <v>120</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AL9" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AM9" t="n">
-        <v>340</v>
+        <v>320</v>
       </c>
       <c r="AN9" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.75</v>
+        <v>14</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>3.65</v>
+        <v>11.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX9" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BA9" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H10" t="n">
-        <v>2.82</v>
+        <v>2.42</v>
       </c>
       <c r="I10" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="J10" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="K10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34</v>
+        <v>2.26</v>
       </c>
       <c r="O10" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="P10" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
         <v>1.13</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>2.34</v>
       </c>
       <c r="U10" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="W10" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X10" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>130</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV10" t="n">
         <v>9</v>
       </c>
-      <c r="Z10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AW10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2503,70 +2503,70 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T11" t="n">
         <v>2.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.1</v>
-      </c>
       <c r="U11" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA11" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB11" t="n">
         <v>8.800000000000001</v>
@@ -2611,62 +2611,62 @@
         <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>2.98</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.92</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>3.65</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.5</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF11" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG11" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="G12" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="P12" t="n">
         <v>1.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="R12" t="n">
         <v>1.17</v>
       </c>
       <c r="S12" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.63</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X12" t="n">
         <v>970</v>
@@ -2757,7 +2757,7 @@
         <v>970</v>
       </c>
       <c r="Z12" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
@@ -2769,7 +2769,7 @@
         <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
@@ -2781,86 +2781,86 @@
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="AK12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.65</v>
+        <v>7.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.5</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.74</v>
+        <v>5.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.98</v>
+        <v>2.26</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.4</v>
+        <v>3.7</v>
       </c>
       <c r="AY12" t="n">
-        <v>2.46</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>3</v>
+        <v>2.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.72</v>
+        <v>4.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.92</v>
+        <v>2.22</v>
       </c>
       <c r="BE12" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="BG12" t="n">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
         <v>1.61</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="K13" t="n">
         <v>5.8</v>
@@ -2912,13 +2912,13 @@
         <v>1.27</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
         <v>2.16</v>
@@ -2930,13 +2930,13 @@
         <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T13" t="n">
         <v>1.76</v>
       </c>
       <c r="U13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="V13" t="n">
         <v>2.64</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.38</v>
+        <v>1.86</v>
       </c>
       <c r="G14" t="n">
-        <v>990</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="I14" t="n">
-        <v>990</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>3.85</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>1.24</v>
+        <v>3.7</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
-        <v>1.05</v>
+        <v>3.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W14" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3279,19 +3279,19 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G15" t="n">
         <v>990</v>
       </c>
       <c r="H15" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="I15" t="n">
         <v>990</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="K15" t="n">
         <v>950</v>
@@ -3303,22 +3303,22 @@
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="O15" t="n">
         <v>1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q15" t="n">
         <v>1.14</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T15" t="n">
         <v>1.81</v>
@@ -3327,7 +3327,7 @@
         <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.02</v>
       </c>
       <c r="G16" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H16" t="n">
         <v>1.02</v>
@@ -3485,7 +3485,7 @@
         <v>990</v>
       </c>
       <c r="J16" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K16" t="n">
         <v>950</v>
@@ -3500,7 +3500,7 @@
         <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
         <v>1.25</v>
@@ -3512,7 +3512,7 @@
         <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T16" t="n">
         <v>1.11</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="G17" t="n">
         <v>990</v>
       </c>
       <c r="H17" t="n">
-        <v>1.35</v>
+        <v>1.09</v>
       </c>
       <c r="I17" t="n">
         <v>990</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>4.1</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K18" t="n">
         <v>4.3</v>
@@ -3885,40 +3885,40 @@
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="R18" t="n">
         <v>1.49</v>
       </c>
       <c r="S18" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T18" t="n">
         <v>1.64</v>
       </c>
       <c r="U18" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V18" t="n">
         <v>2</v>
       </c>
       <c r="W18" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X18" t="n">
         <v>24</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z18" t="n">
         <v>14</v>
@@ -3933,10 +3933,10 @@
         <v>9.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AF18" t="n">
         <v>36</v>
@@ -3969,7 +3969,7 @@
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.800000000000001</v>
@@ -3978,7 +3978,7 @@
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT18" t="n">
         <v>16</v>
@@ -3993,7 +3993,7 @@
         <v>6.6</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4005,7 +4005,7 @@
         <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H19" t="n">
         <v>7</v>
@@ -4067,10 +4067,10 @@
         <v>10.5</v>
       </c>
       <c r="J19" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L19" t="n">
         <v>1.37</v>
@@ -4079,7 +4079,7 @@
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O19" t="n">
         <v>1.31</v>
@@ -4088,7 +4088,7 @@
         <v>1.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R19" t="n">
         <v>1.33</v>
@@ -4109,22 +4109,22 @@
         <v>2.86</v>
       </c>
       <c r="X19" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y19" t="n">
         <v>27</v>
       </c>
       <c r="Z19" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="n">
         <v>360</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AD19" t="n">
         <v>38</v>
@@ -4136,7 +4136,7 @@
         <v>8.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH19" t="n">
         <v>34</v>
@@ -4145,10 +4145,10 @@
         <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL19" t="n">
         <v>48</v>
@@ -4163,62 +4163,62 @@
         <v>270</v>
       </c>
       <c r="AP19" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC19" t="n">
         <v>6</v>
       </c>
-      <c r="AS19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4249,22 +4249,22 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="n">
         <v>7.4</v>
       </c>
       <c r="I20" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J20" t="n">
         <v>5.4</v>
       </c>
       <c r="K20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L20" t="n">
         <v>1.21</v>
@@ -4279,13 +4279,13 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S20" t="n">
         <v>2.08</v>
@@ -4300,13 +4300,13 @@
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="X20" t="n">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="Y20" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="Z20" t="n">
         <v>90</v>
@@ -4321,7 +4321,7 @@
         <v>16</v>
       </c>
       <c r="AD20" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE20" t="n">
         <v>110</v>
@@ -4333,7 +4333,7 @@
         <v>970</v>
       </c>
       <c r="AH20" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI20" t="n">
         <v>90</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="G21" t="n">
         <v>6.2</v>
@@ -4455,7 +4455,7 @@
         <v>1.91</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -4467,7 +4467,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="O21" t="n">
         <v>1.29</v>
@@ -4524,10 +4524,10 @@
         <v>46</v>
       </c>
       <c r="AG21" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AH21" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI21" t="n">
         <v>42</v>
@@ -4554,7 +4554,7 @@
         <v>4</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR21" t="n">
         <v>3.7</v>
@@ -4569,7 +4569,7 @@
         <v>3.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW21" t="n">
         <v>4.2</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4640,16 +4640,16 @@
         <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H22" t="n">
         <v>1.02</v>
       </c>
       <c r="I22" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J22" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K22" t="n">
         <v>950</v>
@@ -4679,10 +4679,10 @@
         <v>1.18</v>
       </c>
       <c r="T22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -4834,16 +4834,16 @@
         <v>1.02</v>
       </c>
       <c r="G23" t="n">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H23" t="n">
         <v>1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J23" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K23" t="n">
         <v>950</v>
@@ -4855,7 +4855,7 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
@@ -4873,10 +4873,10 @@
         <v>1.14</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23" t="n">
         <v>1.01</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G24" t="n">
         <v>2.8</v>
@@ -5049,13 +5049,13 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
@@ -5067,13 +5067,13 @@
         <v>3.7</v>
       </c>
       <c r="T24" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U24" t="n">
         <v>2.14</v>
       </c>
       <c r="V24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="W24" t="n">
         <v>1.55</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>22</v>
       </c>
       <c r="I25" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
         <v>11.5</v>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="O25" t="n">
         <v>1.07</v>
@@ -5255,10 +5255,10 @@
         <v>1.23</v>
       </c>
       <c r="R25" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="S25" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T25" t="n">
         <v>1.91</v>
@@ -5273,10 +5273,10 @@
         <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z25" t="n">
         <v>280</v>
@@ -5291,13 +5291,13 @@
         <v>29</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
         <v>320</v>
       </c>
       <c r="AF25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG25" t="n">
         <v>14.5</v>
@@ -5312,7 +5312,7 @@
         <v>10.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL25" t="n">
         <v>36</v>
@@ -5342,7 +5342,7 @@
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AV25" t="n">
         <v>32</v>
@@ -5366,7 +5366,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC25" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>22</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5437,22 +5437,22 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.58</v>
+        <v>2.48</v>
       </c>
       <c r="O26" t="n">
         <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R26" t="n">
         <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="T26" t="n">
         <v>1.11</v>
@@ -5464,7 +5464,7 @@
         <v>1.43</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
         <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
         <v>100</v>
@@ -5691,7 +5691,7 @@
         <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
         <v>110</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G28" t="n">
         <v>1.46</v>
@@ -5816,7 +5816,7 @@
         <v>4.7</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
         <v>1.29</v>
@@ -5852,13 +5852,13 @@
         <v>1.1</v>
       </c>
       <c r="W28" t="n">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="X28" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Y28" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z28" t="n">
         <v>90</v>
@@ -5873,19 +5873,19 @@
         <v>970</v>
       </c>
       <c r="AD28" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE28" t="n">
         <v>160</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG28" t="n">
         <v>970</v>
       </c>
       <c r="AH28" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="AI28" t="n">
         <v>1000</v>
@@ -5909,16 +5909,16 @@
         <v>220</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT28" t="n">
         <v>6.2</v>
@@ -5927,10 +5927,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX28" t="n">
         <v>6.6</v>
@@ -5939,10 +5939,10 @@
         <v>7.4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB28" t="n">
         <v>9.199999999999999</v>
@@ -5951,10 +5951,10 @@
         <v>11.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF28" t="n">
         <v>5.4</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -5998,10 +5998,10 @@
         <v>2.6</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H29" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="I29" t="n">
         <v>2.82</v>
@@ -6025,13 +6025,13 @@
         <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.84</v>
+        <v>1.73</v>
       </c>
       <c r="R29" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S29" t="n">
         <v>2.18</v>
@@ -6046,7 +6046,7 @@
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X29" t="n">
         <v>18.5</v>
@@ -6070,13 +6070,13 @@
         <v>14.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG29" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
         <v>19</v>
@@ -6085,10 +6085,10 @@
         <v>44</v>
       </c>
       <c r="AJ29" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL29" t="n">
         <v>44</v>
@@ -6097,68 +6097,68 @@
         <v>90</v>
       </c>
       <c r="AN29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO29" t="n">
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AQ29" t="n">
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB29" t="n">
         <v>5.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG29" t="n">
-        <v>4.6</v>
+        <v>17.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6198,55 +6198,55 @@
         <v>2.08</v>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="J30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.6</v>
       </c>
-      <c r="K30" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L30" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.24</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S30" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="U30" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="V30" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="W30" t="n">
         <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z30" t="n">
         <v>12</v>
@@ -6255,7 +6255,7 @@
         <v>26</v>
       </c>
       <c r="AB30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC30" t="n">
         <v>8</v>
@@ -6264,43 +6264,43 @@
         <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AF30" t="n">
         <v>29</v>
       </c>
       <c r="AG30" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AJ30" t="n">
         <v>90</v>
       </c>
       <c r="AK30" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO30" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AP30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AR30" t="n">
         <v>10.5</v>
@@ -6309,7 +6309,7 @@
         <v>23</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AU30" t="n">
         <v>7.2</v>
@@ -6321,38 +6321,38 @@
         <v>20</v>
       </c>
       <c r="AX30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="BC30" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="BD30" t="n">
         <v>50</v>
       </c>
       <c r="BE30" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BG30" t="n">
         <v>18</v>
       </c>
-      <c r="BF30" t="n">
-        <v>50</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>16</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6383,73 +6383,73 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.3</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H31" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I31" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O31" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P31" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="S31" t="n">
-        <v>3.95</v>
+        <v>3.65</v>
       </c>
       <c r="T31" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="U31" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="X31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AA31" t="n">
         <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
@@ -6470,40 +6470,40 @@
         <v>18</v>
       </c>
       <c r="AI31" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO31" t="n">
         <v>44</v>
       </c>
-      <c r="AM31" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>48</v>
-      </c>
       <c r="AP31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ31" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU31" t="n">
         <v>7.2</v>
@@ -6512,41 +6512,41 @@
         <v>13.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA31" t="n">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD31" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>17</v>
+      </c>
+      <c r="BG31" t="n">
         <v>38</v>
       </c>
-      <c r="BE31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>36</v>
-      </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6577,16 +6577,16 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="G32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H32" t="n">
         <v>2.78</v>
       </c>
-      <c r="H32" t="n">
-        <v>2.88</v>
-      </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -6595,13 +6595,13 @@
         <v>3.45</v>
       </c>
       <c r="L32" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O32" t="n">
         <v>1.36</v>
@@ -6625,10 +6625,10 @@
         <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W32" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X32" t="n">
         <v>12.5</v>
@@ -6640,7 +6640,7 @@
         <v>18</v>
       </c>
       <c r="AA32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB32" t="n">
         <v>11</v>
@@ -6655,19 +6655,19 @@
         <v>32</v>
       </c>
       <c r="AF32" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG32" t="n">
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI32" t="n">
         <v>46</v>
       </c>
       <c r="AJ32" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AK32" t="n">
         <v>29</v>
@@ -6679,7 +6679,7 @@
         <v>90</v>
       </c>
       <c r="AN32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO32" t="n">
         <v>30</v>
@@ -6691,25 +6691,25 @@
         <v>10</v>
       </c>
       <c r="AR32" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AS32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT32" t="n">
         <v>10</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV32" t="n">
         <v>12</v>
       </c>
       <c r="AW32" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX32" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY32" t="n">
         <v>11.5</v>
@@ -6724,7 +6724,7 @@
         <v>38</v>
       </c>
       <c r="BC32" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
@@ -6733,14 +6733,14 @@
         <v>85</v>
       </c>
       <c r="BF32" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BG32" t="n">
         <v>27</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="G33" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H33" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I33" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J33" t="n">
         <v>3.3</v>
@@ -6789,40 +6789,40 @@
         <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="V33" t="n">
         <v>1.4</v>
       </c>
-      <c r="P33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T33" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.43</v>
-      </c>
       <c r="W33" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X33" t="n">
         <v>11.5</v>
@@ -6834,19 +6834,19 @@
         <v>21</v>
       </c>
       <c r="AA33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB33" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC33" t="n">
         <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF33" t="n">
         <v>14.5</v>
@@ -6858,7 +6858,7 @@
         <v>18.5</v>
       </c>
       <c r="AI33" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ33" t="n">
         <v>36</v>
@@ -6870,13 +6870,13 @@
         <v>50</v>
       </c>
       <c r="AM33" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN33" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO33" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AP33" t="n">
         <v>10.5</v>
@@ -6885,22 +6885,22 @@
         <v>10.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT33" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU33" t="n">
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX33" t="n">
         <v>13.5</v>
@@ -6909,10 +6909,10 @@
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB33" t="n">
         <v>32</v>
@@ -6921,7 +6921,7 @@
         <v>27</v>
       </c>
       <c r="BD33" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE33" t="n">
         <v>60</v>
@@ -6930,11 +6930,11 @@
         <v>24</v>
       </c>
       <c r="BG33" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -6983,34 +6983,34 @@
         <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q34" t="n">
         <v>1.92</v>
       </c>
       <c r="R34" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="T34" t="n">
         <v>1.84</v>
       </c>
       <c r="U34" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V34" t="n">
         <v>1.25</v>
@@ -7028,7 +7028,7 @@
         <v>40</v>
       </c>
       <c r="AA34" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB34" t="n">
         <v>10</v>
@@ -7037,22 +7037,22 @@
         <v>9.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>22</v>
+        <v>950</v>
       </c>
       <c r="AE34" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF34" t="n">
         <v>970</v>
       </c>
       <c r="AG34" t="n">
-        <v>970</v>
+        <v>950</v>
       </c>
       <c r="AH34" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI34" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="n">
         <v>30</v>
@@ -7061,16 +7061,16 @@
         <v>28</v>
       </c>
       <c r="AL34" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM34" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN34" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AO34" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP34" t="n">
         <v>9.199999999999999</v>
@@ -7079,10 +7079,10 @@
         <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>6.2</v>
@@ -7091,10 +7091,10 @@
         <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX34" t="n">
         <v>8.800000000000001</v>
@@ -7103,32 +7103,32 @@
         <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BA34" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BB34" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB34" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BC34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BF34" t="n">
         <v>12.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.04</v>
       </c>
       <c r="G35" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H35" t="n">
         <v>1.04</v>
       </c>
       <c r="I35" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J35" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K35" t="n">
         <v>950</v>
@@ -7183,13 +7183,13 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q35" t="n">
         <v>1.23</v>
@@ -7201,10 +7201,10 @@
         <v>1.23</v>
       </c>
       <c r="T35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U35" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35" t="n">
         <v>1.01</v>
@@ -7267,52 +7267,52 @@
         <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7356,16 +7356,16 @@
         <v>1.04</v>
       </c>
       <c r="G36" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H36" t="n">
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J36" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K36" t="n">
         <v>950</v>
@@ -7395,10 +7395,10 @@
         <v>1.2</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36" t="n">
         <v>1.01</v>
@@ -7461,52 +7461,52 @@
         <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF36" t="n">
         <v>1.01</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7553,7 +7553,7 @@
         <v>1.62</v>
       </c>
       <c r="H37" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I37" t="n">
         <v>10.5</v>
@@ -7565,7 +7565,7 @@
         <v>7</v>
       </c>
       <c r="L37" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M37" t="n">
         <v>1.01</v>
@@ -7580,19 +7580,19 @@
         <v>1.25</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
         <v>1.11</v>
@@ -7601,10 +7601,10 @@
         <v>2.62</v>
       </c>
       <c r="X37" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="Y37" t="n">
-        <v>34</v>
+        <v>950</v>
       </c>
       <c r="Z37" t="n">
         <v>85</v>
@@ -7619,7 +7619,7 @@
         <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
@@ -7631,7 +7631,7 @@
         <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>28</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
@@ -7655,62 +7655,62 @@
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AQ37" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="AV37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ37" t="n">
         <v>3.95</v>
       </c>
-      <c r="AW37" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BA37" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="BD37" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.04</v>
+        <v>1.16</v>
       </c>
       <c r="G38" t="n">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H38" t="n">
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="J38" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K38" t="n">
         <v>950</v>
@@ -7783,10 +7783,10 @@
         <v>1.26</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V38" t="n">
         <v>1.01</v>
@@ -7849,52 +7849,52 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF38" t="n">
         <v>1.01</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-29 22:41:48</t>
+          <t>2026-04-30 00:59:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,49 +757,49 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="H2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
         <v>5.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="O2" t="n">
         <v>1.32</v>
       </c>
       <c r="P2" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="U2" t="n">
         <v>1.7</v>
@@ -808,119 +808,119 @@
         <v>1.09</v>
       </c>
       <c r="W2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="n">
         <v>110</v>
       </c>
       <c r="AA2" t="n">
-        <v>470</v>
+        <v>440</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>12.5</v>
       </c>
-      <c r="AD2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>13</v>
-      </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM2" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
         <v>350</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>22</v>
       </c>
       <c r="AR2" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX2" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AY2" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>5</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
         <v>120</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="G3" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="I3" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="L3" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O3" t="n">
         <v>1.38</v>
       </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.35</v>
-      </c>
       <c r="P3" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.72</v>
-      </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y3" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="Z3" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AA3" t="n">
-        <v>330</v>
+        <v>510</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="AC3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH3" t="n">
         <v>32</v>
       </c>
-      <c r="AE3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG3" t="n">
+      <c r="AI3" t="n">
+        <v>950</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>14.5</v>
       </c>
       <c r="AK3" t="n">
         <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM3" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN3" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO3" t="n">
-        <v>240</v>
+        <v>400</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AS3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX3" t="n">
         <v>6.6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AY3" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="BE3" t="n">
         <v>120</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.95</v>
+        <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.6</v>
+        <v>10</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1145,52 +1145,52 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="I4" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>2.72</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L4" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="M4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="R4" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="V4" t="n">
         <v>1.55</v>
@@ -1199,116 +1199,116 @@
         <v>1.37</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>970</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AH4" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AO4" t="n">
         <v>65</v>
       </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>44</v>
-      </c>
       <c r="AP4" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.96</v>
+        <v>12.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.9</v>
+        <v>30</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.84</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>2.56</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.94</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>2.94</v>
+        <v>8.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>3.35</v>
+        <v>9</v>
       </c>
       <c r="BD4" t="n">
-        <v>2.96</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
         <v>130</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.94</v>
+        <v>6</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.9</v>
+        <v>30</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>2.42</v>
       </c>
       <c r="J5" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O5" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.71</v>
       </c>
       <c r="W5" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.5</v>
+        <v>14</v>
       </c>
       <c r="AA5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AG5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="AM5" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN5" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AO5" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV5" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>5.8</v>
       </c>
       <c r="AX5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG5" t="n">
         <v>5.9</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1533,28 +1533,28 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="G6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
@@ -1566,10 +1566,10 @@
         <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
         <v>3.65</v>
@@ -1578,13 +1578,13 @@
         <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1599,7 +1599,7 @@
         <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
         <v>970</v>
@@ -1614,89 +1614,89 @@
         <v>48</v>
       </c>
       <c r="AG6" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
         <v>46</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AK6" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AL6" t="n">
         <v>110</v>
       </c>
       <c r="AM6" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN6" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AT6" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AU6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE6" t="n">
         <v>3.95</v>
       </c>
-      <c r="AV6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF6" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1727,58 +1727,58 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="G7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I7" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.46</v>
+        <v>2.94</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="P7" t="n">
-        <v>1.52</v>
+        <v>1.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.05</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1787,10 +1787,10 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>970</v>
@@ -1802,7 +1802,7 @@
         <v>970</v>
       </c>
       <c r="AE7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AF7" t="n">
         <v>22</v>
@@ -1811,76 +1811,76 @@
         <v>970</v>
       </c>
       <c r="AH7" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AJ7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL7" t="n">
         <v>60</v>
       </c>
-      <c r="AK7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>80</v>
-      </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="AR7" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AS7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW7" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AX7" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BB7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BC7" t="n">
         <v>4.3</v>
       </c>
-      <c r="BC7" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BD7" t="n">
-        <v>4.4</v>
+        <v>2.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="BF7" t="n">
         <v>4.3</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -1939,13 +1939,13 @@
         <v>3.8</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
         <v>1.33</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="H9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>3.5</v>
       </c>
       <c r="J9" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K9" t="n">
         <v>3.15</v>
       </c>
       <c r="L9" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="M9" t="n">
         <v>1.15</v>
@@ -2145,10 +2145,10 @@
         <v>1.66</v>
       </c>
       <c r="P9" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
         <v>1.14</v>
@@ -2157,7 +2157,7 @@
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U9" t="n">
         <v>1.64</v>
@@ -2166,13 +2166,13 @@
         <v>1.41</v>
       </c>
       <c r="W9" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="X9" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z9" t="n">
         <v>24</v>
@@ -2181,10 +2181,10 @@
         <v>80</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD9" t="n">
         <v>19.5</v>
@@ -2193,7 +2193,7 @@
         <v>65</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG9" t="n">
         <v>17</v>
@@ -2214,7 +2214,7 @@
         <v>110</v>
       </c>
       <c r="AM9" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AN9" t="n">
         <v>80</v>
@@ -2223,62 +2223,62 @@
         <v>100</v>
       </c>
       <c r="AP9" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AR9" t="n">
+      <c r="AU9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX9" t="n">
         <v>14</v>
       </c>
-      <c r="AS9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV9" t="n">
+      <c r="AY9" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>4</v>
-      </c>
       <c r="AZ9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB9" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF9" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.2</v>
+        <v>2.58</v>
       </c>
       <c r="G10" t="n">
-        <v>3.65</v>
+        <v>2.88</v>
       </c>
       <c r="H10" t="n">
-        <v>2.42</v>
+        <v>2.9</v>
       </c>
       <c r="I10" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="M10" t="n">
         <v>1.14</v>
       </c>
       <c r="N10" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T10" t="n">
         <v>2.26</v>
       </c>
-      <c r="O10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="U10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP10" t="n">
         <v>7</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X10" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>360</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>130</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>75</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY10" t="n">
         <v>10</v>
       </c>
-      <c r="AS10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ10" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2506,58 +2506,58 @@
         <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
         <v>3.3</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="K11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
         <v>1.15</v>
       </c>
       <c r="N11" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="P11" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S11" t="n">
         <v>6.2</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U11" t="n">
         <v>1.69</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="X11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Y11" t="n">
         <v>11</v>
@@ -2569,10 +2569,10 @@
         <v>95</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD11" t="n">
         <v>20</v>
@@ -2581,10 +2581,10 @@
         <v>75</v>
       </c>
       <c r="AF11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH11" t="n">
         <v>30</v>
@@ -2611,62 +2611,62 @@
         <v>110</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.35</v>
+        <v>7.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.1</v>
+        <v>19.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="AT11" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>5.5</v>
       </c>
-      <c r="AU11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD11" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2697,61 +2697,61 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="G12" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I12" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="O12" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="P12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="T12" t="n">
         <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W12" t="n">
         <v>2.24</v>
       </c>
       <c r="X12" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -2769,19 +2769,19 @@
         <v>970</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>970</v>
+        <v>9.6</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
       </c>
       <c r="AH12" t="n">
-        <v>44</v>
+        <v>950</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
@@ -2790,13 +2790,13 @@
         <v>970</v>
       </c>
       <c r="AK12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AN12" t="n">
         <v>24</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.26</v>
+        <v>2.86</v>
       </c>
       <c r="AT12" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>3.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.4</v>
+        <v>2.66</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.5</v>
+        <v>2.7</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.26</v>
+        <v>2.84</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.7</v>
+        <v>2.54</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.2</v>
+        <v>2.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.22</v>
+        <v>2.78</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="BF12" t="n">
-        <v>5</v>
+        <v>2.58</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.28</v>
+        <v>2.86</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -2891,112 +2891,112 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>9.4</v>
+        <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="I13" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="P13" t="n">
         <v>2.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="T13" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="V13" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="W13" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD13" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z13" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>34</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>12</v>
-      </c>
       <c r="AE13" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AF13" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="AG13" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>38</v>
       </c>
       <c r="AJ13" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AK13" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM13" t="n">
         <v>120</v>
       </c>
-      <c r="AL13" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>130</v>
-      </c>
       <c r="AN13" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AO13" t="n">
-        <v>7.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP13" t="n">
         <v>4.2</v>
@@ -3005,31 +3005,31 @@
         <v>3.55</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="AV13" t="n">
         <v>3.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BA13" t="n">
         <v>4.5</v>
@@ -3038,23 +3038,23 @@
         <v>5</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF13" t="n">
         <v>4.9</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3085,170 +3085,170 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R14" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
       </c>
       <c r="V14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z14" t="n">
         <v>42</v>
       </c>
       <c r="AA14" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="AC14" t="n">
-        <v>950</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE14" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH14" t="n">
         <v>950</v>
       </c>
       <c r="AI14" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK14" t="n">
         <v>23</v>
       </c>
-      <c r="AK14" t="n">
-        <v>22</v>
-      </c>
       <c r="AL14" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO14" t="n">
         <v>75</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>5.9</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB14" t="n">
         <v>4.3</v>
       </c>
-      <c r="AU14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BC14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE14" t="n">
         <v>5</v>
       </c>
-      <c r="BD14" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>6</v>
-      </c>
       <c r="BF14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG14" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3279,94 +3279,94 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="G15" t="n">
-        <v>990</v>
+        <v>18.5</v>
       </c>
       <c r="H15" t="n">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>990</v>
+        <v>1.35</v>
       </c>
       <c r="J15" t="n">
-        <v>1.52</v>
+        <v>4.9</v>
       </c>
       <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X15" t="n">
         <v>950</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AF15" t="n">
         <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ15" t="n">
         <v>1000</v>
@@ -3384,65 +3384,65 @@
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.02</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>990</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="I16" t="n">
-        <v>990</v>
+        <v>2.46</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1</v>
+        <v>3.55</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N16" t="n">
         <v>1.1</v>
       </c>
       <c r="O16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S16" t="n">
-        <v>1.24</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.63</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3667,170 +3667,170 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="G17" t="n">
-        <v>990</v>
+        <v>3.8</v>
       </c>
       <c r="H17" t="n">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>990</v>
+        <v>2.68</v>
       </c>
       <c r="J17" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O17" t="n">
         <v>1.25</v>
       </c>
-      <c r="O17" t="n">
-        <v>1.23</v>
-      </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.94</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.23</v>
+        <v>1.69</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>1.23</v>
+        <v>2.72</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>1.61</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -3861,55 +3861,55 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G18" t="n">
         <v>4.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="I18" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="J18" t="n">
         <v>3.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>1.23</v>
       </c>
       <c r="P18" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R18" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="S18" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="T18" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U18" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="V18" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="W18" t="n">
         <v>1.27</v>
@@ -3936,7 +3936,7 @@
         <v>11</v>
       </c>
       <c r="AE18" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AF18" t="n">
         <v>36</v>
@@ -3951,10 +3951,10 @@
         <v>32</v>
       </c>
       <c r="AJ18" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AK18" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AL18" t="n">
         <v>50</v>
@@ -3963,37 +3963,37 @@
         <v>80</v>
       </c>
       <c r="AN18" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AO18" t="n">
         <v>10.5</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
         <v>11</v>
       </c>
       <c r="AS18" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU18" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV18" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX18" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY18" t="n">
         <v>14.5</v>
@@ -4002,29 +4002,29 @@
         <v>14</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.6</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
         <v>32</v>
       </c>
       <c r="BD18" t="n">
-        <v>34</v>
+        <v>7.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.800000000000001</v>
+        <v>24</v>
       </c>
       <c r="BF18" t="n">
         <v>28</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4055,170 +4055,170 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K19" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M19" t="n">
         <v>1.06</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O19" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="P19" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R19" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
         <v>3.05</v>
       </c>
       <c r="T19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U19" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V19" t="n">
         <v>1.11</v>
       </c>
       <c r="W19" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
       <c r="X19" t="n">
         <v>18.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="Z19" t="n">
         <v>90</v>
       </c>
       <c r="AA19" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="AB19" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC19" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD19" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AE19" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF19" t="n">
         <v>8.4</v>
       </c>
       <c r="AG19" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI19" t="n">
         <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AK19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL19" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM19" t="n">
         <v>200</v>
       </c>
       <c r="AN19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>260</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS19" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AO19" t="n">
-        <v>270</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="AT19" t="n">
         <v>7</v>
       </c>
-      <c r="AS19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AU19" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ19" t="n">
         <v>7.4</v>
       </c>
-      <c r="AX19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="BA19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE19" t="n">
         <v>9</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BF19" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="G20" t="n">
         <v>1.45</v>
       </c>
       <c r="H20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I20" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J20" t="n">
         <v>5.4</v>
       </c>
       <c r="K20" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="L20" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.02</v>
@@ -4279,25 +4279,25 @@
         <v>1.14</v>
       </c>
       <c r="P20" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="S20" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="T20" t="n">
         <v>1.7</v>
       </c>
       <c r="U20" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W20" t="n">
         <v>3.2</v>
@@ -4309,16 +4309,16 @@
         <v>950</v>
       </c>
       <c r="Z20" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB20" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="AC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AD20" t="n">
         <v>950</v>
@@ -4327,16 +4327,16 @@
         <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH20" t="n">
         <v>950</v>
       </c>
       <c r="AI20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
         <v>970</v>
@@ -4345,74 +4345,74 @@
         <v>970</v>
       </c>
       <c r="AL20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN20" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AO20" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.9</v>
+        <v>8.6</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT20" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="AV20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY20" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.3</v>
+        <v>11.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.1</v>
+        <v>21</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G21" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="I21" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="R21" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>3.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W21" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z21" t="n">
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AB21" t="n">
         <v>970</v>
       </c>
       <c r="AC21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AH21" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI21" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN21" t="n">
         <v>80</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>90</v>
       </c>
       <c r="AO21" t="n">
         <v>970</v>
       </c>
       <c r="AP21" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AQ21" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF21" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG21" t="n">
-        <v>3.75</v>
+        <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.02</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>990</v>
+        <v>2.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="I22" t="n">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>1.09</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>950</v>
+        <v>85</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="V22" t="n">
         <v>1.33</v>
       </c>
-      <c r="O22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.03</v>
+        <v>3.45</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M23" t="n">
         <v>1.02</v>
       </c>
-      <c r="G23" t="n">
-        <v>990</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="I23" t="n">
-        <v>990</v>
-      </c>
-      <c r="J23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K23" t="n">
-        <v>950</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N23" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.14</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>2.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.14</v>
+        <v>1.41</v>
       </c>
       <c r="R23" t="n">
-        <v>1.24</v>
+        <v>1.7</v>
       </c>
       <c r="S23" t="n">
-        <v>1.14</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
-        <v>1.11</v>
+        <v>1.47</v>
       </c>
       <c r="U23" t="n">
-        <v>1.11</v>
+        <v>2.52</v>
       </c>
       <c r="V23" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W23" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD23" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5025,55 +5025,55 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G24" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H24" t="n">
         <v>2.84</v>
       </c>
       <c r="I24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q24" t="n">
         <v>2.02</v>
       </c>
       <c r="R24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T24" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V24" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.55</v>
@@ -5082,25 +5082,25 @@
         <v>16</v>
       </c>
       <c r="Y24" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z24" t="n">
         <v>24</v>
       </c>
       <c r="AA24" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB24" t="n">
         <v>13</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD24" t="n">
         <v>15.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF24" t="n">
         <v>22</v>
@@ -5118,43 +5118,43 @@
         <v>48</v>
       </c>
       <c r="AK24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN24" t="n">
         <v>34</v>
       </c>
       <c r="AO24" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
         <v>14.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AT24" t="n">
         <v>9.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AV24" t="n">
         <v>9.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX24" t="n">
         <v>13</v>
@@ -5163,32 +5163,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4.1</v>
+        <v>15</v>
       </c>
       <c r="BA24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC24" t="n">
         <v>4.4</v>
       </c>
-      <c r="BB24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD24" t="n">
-        <v>4.4</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BF24" t="n">
-        <v>20</v>
+        <v>4.8</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.5</v>
+        <v>23</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5222,49 +5222,49 @@
         <v>1.13</v>
       </c>
       <c r="G25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="H25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="K25" t="n">
         <v>13</v>
       </c>
       <c r="L25" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="O25" t="n">
         <v>1.07</v>
       </c>
       <c r="P25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="R25" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="S25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="T25" t="n">
         <v>1.91</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="V25" t="n">
         <v>1.03</v>
@@ -5285,7 +5285,7 @@
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>24</v>
+        <v>970</v>
       </c>
       <c r="AC25" t="n">
         <v>29</v>
@@ -5297,13 +5297,13 @@
         <v>320</v>
       </c>
       <c r="AF25" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
@@ -5321,16 +5321,16 @@
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="AO25" t="n">
-        <v>280</v>
+        <v>330</v>
       </c>
       <c r="AP25" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AQ25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AR25" t="n">
         <v>50</v>
@@ -5342,13 +5342,13 @@
         <v>20</v>
       </c>
       <c r="AU25" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AW25" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX25" t="n">
         <v>11</v>
@@ -5357,10 +5357,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB25" t="n">
         <v>8.800000000000001</v>
@@ -5372,17 +5372,17 @@
         <v>22</v>
       </c>
       <c r="BE25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BG25" t="n">
         <v>50</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="G26" t="n">
-        <v>3.75</v>
+        <v>3.15</v>
       </c>
       <c r="H26" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.94</v>
       </c>
       <c r="J26" t="n">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>2.48</v>
+        <v>3.4</v>
       </c>
       <c r="O26" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="T26" t="n">
-        <v>1.11</v>
+        <v>1.67</v>
       </c>
       <c r="U26" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="W26" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5607,58 +5607,58 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="G27" t="n">
-        <v>600</v>
+        <v>1.91</v>
       </c>
       <c r="H27" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="K27" t="n">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.1</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.64</v>
+        <v>1.95</v>
       </c>
       <c r="U27" t="n">
-        <v>1.53</v>
+        <v>1.88</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="X27" t="n">
         <v>970</v>
@@ -5670,19 +5670,19 @@
         <v>48</v>
       </c>
       <c r="AA27" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AD27" t="n">
         <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
         <v>12</v>
@@ -5694,37 +5694,37 @@
         <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK27" t="n">
         <v>24</v>
       </c>
-      <c r="AK27" t="n">
-        <v>25</v>
-      </c>
       <c r="AL27" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
         <v>970</v>
       </c>
       <c r="AO27" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="AT27" t="n">
         <v>6.4</v>
@@ -5733,44 +5733,44 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>4.3</v>
+        <v>5.8</v>
       </c>
       <c r="AW27" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AX27" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AY27" t="n">
         <v>8</v>
       </c>
       <c r="AZ27" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="BB27" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>11.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG27" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5801,58 +5801,58 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="G28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="H28" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="L28" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="M28" t="n">
         <v>1.05</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R28" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="V28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="X28" t="n">
         <v>950</v>
@@ -5861,110 +5861,110 @@
         <v>950</v>
       </c>
       <c r="Z28" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>970</v>
+        <v>14.5</v>
       </c>
       <c r="AD28" t="n">
         <v>950</v>
       </c>
       <c r="AE28" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ28" t="n">
         <v>15</v>
       </c>
       <c r="AK28" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN28" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO28" t="n">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AS28" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="AV28" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>11.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -5995,61 +5995,61 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G29" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="H29" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="I29" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="J29" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K29" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L29" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M29" t="n">
         <v>1.06</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="O29" t="n">
         <v>1.29</v>
       </c>
       <c r="P29" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="S29" t="n">
-        <v>2.18</v>
+        <v>3.25</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>2.26</v>
       </c>
       <c r="V29" t="n">
         <v>1.54</v>
       </c>
       <c r="W29" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X29" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y29" t="n">
         <v>14</v>
@@ -6061,10 +6061,10 @@
         <v>46</v>
       </c>
       <c r="AB29" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD29" t="n">
         <v>14.5</v>
@@ -6103,62 +6103,62 @@
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>10.5</v>
       </c>
       <c r="AR29" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU29" t="n">
         <v>7.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG29" t="n">
         <v>5.7</v>
       </c>
-      <c r="AX29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6189,170 +6189,170 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G30" t="n">
         <v>4.2</v>
       </c>
       <c r="H30" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I30" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.39</v>
+        <v>1.51</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P30" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R30" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="T30" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V30" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W30" t="n">
         <v>1.31</v>
       </c>
       <c r="X30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB30" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>11</v>
       </c>
       <c r="AE30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AF30" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI30" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AJ30" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK30" t="n">
         <v>60</v>
       </c>
       <c r="AL30" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AM30" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
         <v>11</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
         <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX30" t="n">
         <v>25</v>
       </c>
       <c r="AY30" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
         <v>36</v>
       </c>
       <c r="BB30" t="n">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="BD30" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BE30" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BF30" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="BG30" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6383,64 +6383,64 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.26</v>
       </c>
-      <c r="G31" t="n">
-        <v>2.3</v>
-      </c>
       <c r="H31" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I31" t="n">
         <v>3.75</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P31" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R31" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S31" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U31" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V31" t="n">
         <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="n">
         <v>25</v>
@@ -6449,7 +6449,7 @@
         <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
@@ -6461,52 +6461,52 @@
         <v>44</v>
       </c>
       <c r="AF31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG31" t="n">
         <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI31" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ31" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL31" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM31" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AN31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AO31" t="n">
         <v>44</v>
       </c>
       <c r="AP31" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
-        <v>15.5</v>
+        <v>60</v>
       </c>
       <c r="AT31" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV31" t="n">
         <v>13.5</v>
@@ -6515,38 +6515,38 @@
         <v>38</v>
       </c>
       <c r="AX31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY31" t="n">
         <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>25</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF31" t="n">
         <v>15.5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>26</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>22</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>28</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>17</v>
       </c>
       <c r="BG31" t="n">
         <v>38</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6583,10 +6583,10 @@
         <v>2.88</v>
       </c>
       <c r="H32" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I32" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J32" t="n">
         <v>3.4</v>
@@ -6601,16 +6601,16 @@
         <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R32" t="n">
         <v>1.33</v>
@@ -6619,13 +6619,13 @@
         <v>3.85</v>
       </c>
       <c r="T32" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="U32" t="n">
         <v>2.16</v>
       </c>
       <c r="V32" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W32" t="n">
         <v>1.53</v>
@@ -6634,10 +6634,10 @@
         <v>12.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA32" t="n">
         <v>44</v>
@@ -6652,7 +6652,7 @@
         <v>12.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF32" t="n">
         <v>18.5</v>
@@ -6661,16 +6661,16 @@
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI32" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ32" t="n">
         <v>44</v>
       </c>
       <c r="AK32" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL32" t="n">
         <v>44</v>
@@ -6679,10 +6679,10 @@
         <v>90</v>
       </c>
       <c r="AN32" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO32" t="n">
         <v>29</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>30</v>
       </c>
       <c r="AP32" t="n">
         <v>12</v>
@@ -6703,7 +6703,7 @@
         <v>7</v>
       </c>
       <c r="AV32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW32" t="n">
         <v>29</v>
@@ -6718,13 +6718,13 @@
         <v>16</v>
       </c>
       <c r="BA32" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB32" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BC32" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD32" t="n">
         <v>40</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6771,25 +6771,25 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="G33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H33" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="J33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.3</v>
       </c>
-      <c r="K33" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M33" t="n">
         <v>1.1</v>
@@ -6801,10 +6801,10 @@
         <v>1.44</v>
       </c>
       <c r="P33" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R33" t="n">
         <v>1.27</v>
@@ -6813,28 +6813,28 @@
         <v>4.4</v>
       </c>
       <c r="T33" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U33" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V33" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W33" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
         <v>11.5</v>
       </c>
       <c r="Z33" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA33" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AB33" t="n">
         <v>8.6</v>
@@ -6843,16 +6843,16 @@
         <v>7.2</v>
       </c>
       <c r="AD33" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AE33" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AF33" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH33" t="n">
         <v>18.5</v>
@@ -6861,80 +6861,80 @@
         <v>65</v>
       </c>
       <c r="AJ33" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK33" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AL33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN33" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP33" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ33" t="n">
         <v>10.5</v>
       </c>
       <c r="AR33" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AS33" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU33" t="n">
         <v>6.8</v>
       </c>
       <c r="AV33" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW33" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AX33" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY33" t="n">
         <v>11</v>
       </c>
       <c r="AZ33" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA33" t="n">
         <v>55</v>
       </c>
       <c r="BB33" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE33" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="BF33" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG33" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="G34" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="H34" t="n">
         <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
         <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="M34" t="n">
         <v>1.08</v>
       </c>
       <c r="N34" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O34" t="n">
         <v>1.35</v>
       </c>
       <c r="P34" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="R34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="T34" t="n">
         <v>1.84</v>
@@ -7013,10 +7013,10 @@
         <v>1.98</v>
       </c>
       <c r="V34" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W34" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="X34" t="n">
         <v>970</v>
@@ -7055,10 +7055,10 @@
         <v>80</v>
       </c>
       <c r="AJ34" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL34" t="n">
         <v>48</v>
@@ -7079,7 +7079,7 @@
         <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS34" t="n">
         <v>4.4</v>
@@ -7091,19 +7091,19 @@
         <v>6</v>
       </c>
       <c r="AV34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW34" t="n">
         <v>4.3</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.800000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="AY34" t="n">
         <v>7.8</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BA34" t="n">
         <v>4.4</v>
@@ -7112,7 +7112,7 @@
         <v>4.1</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD34" t="n">
         <v>4.2</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7183,22 +7183,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
       </c>
       <c r="P35" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R35" t="n">
         <v>1.18</v>
       </c>
       <c r="S35" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="T35" t="n">
         <v>1.11</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7547,28 +7547,28 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G37" t="n">
-        <v>1.62</v>
+        <v>600</v>
       </c>
       <c r="H37" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="I37" t="n">
-        <v>10.5</v>
+        <v>990</v>
       </c>
       <c r="J37" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="K37" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L37" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N37" t="n">
         <v>1.94</v>
@@ -7586,7 +7586,7 @@
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T37" t="n">
         <v>1.11</v>
@@ -7595,122 +7595,122 @@
         <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="W37" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="X37" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y37" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z37" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD37" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE37" t="n">
         <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH37" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AL37" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
         <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX37" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AY37" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB37" t="n">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BC37" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>
@@ -7750,7 +7750,7 @@
         <v>1.04</v>
       </c>
       <c r="I38" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J38" t="n">
         <v>1.09</v>
@@ -7780,7 +7780,7 @@
         <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T38" t="n">
         <v>1.11</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-30 00:59:52</t>
+          <t>2026-04-30 03:17:28</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.39</v>
+        <v>1.99</v>
       </c>
       <c r="G2" t="n">
-        <v>1.47</v>
+        <v>2.04</v>
       </c>
       <c r="H2" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="I2" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>2.22</v>
       </c>
       <c r="K2" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="O2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="P2" t="n">
         <v>1.06</v>
       </c>
-      <c r="N2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.96</v>
-      </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>14.5</v>
       </c>
       <c r="R2" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>80</v>
       </c>
       <c r="T2" t="n">
-        <v>2.16</v>
+        <v>9.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W2" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>17</v>
+        <v>2.78</v>
       </c>
       <c r="Y2" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Z2" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>7.6</v>
+        <v>3.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>11.5</v>
+        <v>24</v>
       </c>
       <c r="AD2" t="n">
-        <v>38</v>
+        <v>290</v>
       </c>
       <c r="AE2" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>250</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AR2" t="n">
         <v>170</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>240</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>350</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>220</v>
       </c>
       <c r="AT2" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="AV2" t="n">
-        <v>6.8</v>
+        <v>150</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="AX2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AY2" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17.5</v>
+        <v>150</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>270</v>
       </c>
       <c r="BB2" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BC2" t="n">
-        <v>14.5</v>
+        <v>70</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>370</v>
       </c>
       <c r="BE2" t="n">
-        <v>120</v>
+        <v>6.2</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>60</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.41</v>
+        <v>1.93</v>
       </c>
       <c r="G3" t="n">
-        <v>1.47</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>11</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>4.3</v>
       </c>
-      <c r="K3" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W3" t="n">
-        <v>3</v>
-      </c>
-      <c r="X3" t="n">
+      <c r="AH3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN3" t="n">
         <v>15</v>
       </c>
-      <c r="Y3" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>510</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>240</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AO3" t="n">
-        <v>400</v>
+        <v>190</v>
       </c>
       <c r="AP3" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS3" t="n">
         <v>10</v>
       </c>
       <c r="AT3" t="n">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF3" t="n">
         <v>12</v>
       </c>
-      <c r="AW3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE3" t="n">
+      <c r="BG3" t="n">
         <v>120</v>
       </c>
-      <c r="BF3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>10</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.2</v>
+        <v>3.95</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="H4" t="n">
-        <v>2.46</v>
+        <v>3.5</v>
       </c>
       <c r="I4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X4" t="n">
         <v>2.84</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S4" t="n">
+      <c r="Y4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
         <v>6.2</v>
       </c>
-      <c r="T4" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>990</v>
       </c>
       <c r="AE4" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AG4" t="n">
-        <v>18</v>
+        <v>990</v>
       </c>
       <c r="AH4" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="AI4" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>5.7</v>
+        <v>2.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AR4" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AT4" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="AY4" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="AZ4" t="n">
-        <v>7.2</v>
+        <v>95</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>320</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.4</v>
+        <v>120</v>
       </c>
       <c r="BC4" t="n">
+        <v>200</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>440</v>
+      </c>
+      <c r="BE4" t="n">
         <v>9</v>
       </c>
-      <c r="BD4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>130</v>
-      </c>
       <c r="BF4" t="n">
-        <v>6</v>
+        <v>390</v>
       </c>
       <c r="BG4" t="n">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1342,61 +1342,61 @@
         <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="O5" t="n">
         <v>1.53</v>
       </c>
       <c r="P5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
         <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="T5" t="n">
         <v>2.08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V5" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" t="n">
         <v>14</v>
@@ -1408,7 +1408,7 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
         <v>12.5</v>
@@ -1417,92 +1417,92 @@
         <v>36</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AJ5" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK5" t="n">
         <v>100</v>
       </c>
-      <c r="AK5" t="n">
-        <v>75</v>
-      </c>
       <c r="AL5" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM5" t="n">
         <v>220</v>
       </c>
       <c r="AN5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="n">
         <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY5" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT5" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>5.4</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1533,58 +1533,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="G6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="H6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="I6" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
         <v>3.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
         <v>15</v>
@@ -1596,7 +1596,7 @@
         <v>970</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
         <v>970</v>
@@ -1611,7 +1611,7 @@
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AG6" t="n">
         <v>950</v>
@@ -1620,10 +1620,10 @@
         <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
         <v>100</v>
@@ -1635,68 +1635,68 @@
         <v>160</v>
       </c>
       <c r="AN6" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AO6" t="n">
         <v>970</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.3</v>
       </c>
-      <c r="AU6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>2.64</v>
+        <v>2.82</v>
       </c>
       <c r="I7" t="n">
         <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K7" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.48</v>
@@ -1751,34 +1751,34 @@
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
         <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X7" t="n">
         <v>970</v>
@@ -1787,7 +1787,7 @@
         <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
         <v>55</v>
@@ -1805,7 +1805,7 @@
         <v>42</v>
       </c>
       <c r="AF7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG7" t="n">
         <v>970</v>
@@ -1832,65 +1832,65 @@
         <v>44</v>
       </c>
       <c r="AO7" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
         <v>3.95</v>
       </c>
       <c r="AQ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AT7" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>3.75</v>
-      </c>
       <c r="AU7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AV7" t="n">
         <v>4.1</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4</v>
+        <v>2.76</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="BE7" t="n">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.3</v>
+        <v>2.94</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.3</v>
+        <v>2.98</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -1921,58 +1921,58 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="G8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="H8" t="n">
         <v>3.15</v>
       </c>
       <c r="I8" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N8" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Q8" t="n">
         <v>1.84</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.96</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>3.2</v>
+        <v>2.68</v>
       </c>
       <c r="T8" t="n">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="U8" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="X8" t="n">
         <v>16</v>
@@ -1984,7 +1984,7 @@
         <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB8" t="n">
         <v>11.5</v>
@@ -1993,10 +1993,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
         <v>17.5</v>
@@ -2005,86 +2005,86 @@
         <v>13</v>
       </c>
       <c r="AH8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN8" t="n">
         <v>21</v>
       </c>
-      <c r="AI8" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>24</v>
-      </c>
       <c r="AO8" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV8" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AW8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.48</v>
       </c>
       <c r="H9" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="M9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R9" t="n">
         <v>1.15</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.14</v>
       </c>
       <c r="S9" t="n">
         <v>6.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="X9" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA9" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE9" t="n">
         <v>80</v>
       </c>
-      <c r="AB9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>65</v>
-      </c>
       <c r="AF9" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG9" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>140</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR9" t="n">
         <v>17</v>
       </c>
-      <c r="AH9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>110</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>310</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AP9" t="n">
+      <c r="AS9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AT9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>5.8</v>
       </c>
-      <c r="AT9" t="n">
+      <c r="BA9" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU9" t="n">
+      <c r="BB9" t="n">
         <v>6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.7</v>
       </c>
       <c r="BC9" t="n">
         <v>6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE9" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF9" t="n">
         <v>6.2</v>
       </c>
-      <c r="BF9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BG9" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2309,40 +2309,40 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="G10" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K10" t="n">
         <v>3.4</v>
       </c>
       <c r="L10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.67</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.65</v>
       </c>
       <c r="P10" t="n">
         <v>1.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
         <v>1.14</v>
@@ -2351,128 +2351,128 @@
         <v>6.8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="U10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="X10" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="Z10" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AA10" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AC10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD10" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AF10" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH10" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AI10" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="AJ10" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AK10" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AM10" t="n">
         <v>270</v>
       </c>
       <c r="AN10" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AQ10" t="n">
         <v>7.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>15.5</v>
+        <v>20</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AY10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>25</v>
+      </c>
+      <c r="BA10" t="n">
         <v>10</v>
       </c>
-      <c r="AZ10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BB10" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD10" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BE10" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2494,179 +2494,179 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Avenir S Marsa</t>
+          <t>Sportive De Tunis</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esperance Sportive Zarzis</t>
+          <t>Club Sportif Sfaxien</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.04</v>
       </c>
       <c r="H11" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N11" t="n">
         <v>2.4</v>
       </c>
       <c r="O11" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="P11" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.16</v>
       </c>
       <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X11" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB11" t="n">
         <v>6.2</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>27</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB11" t="n">
+      <c r="AC11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>320</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR11" t="n">
         <v>7.6</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AS11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AZ11" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>250</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>22</v>
-      </c>
       <c r="BA11" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sportive De Tunis</t>
+          <t>Avenir S Marsa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Club Sportif Sfaxien</t>
+          <t>Esperance Sportive Zarzis</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.79</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8</v>
+        <v>2.72</v>
       </c>
       <c r="H12" t="n">
-        <v>5.8</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>3.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>2.84</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="M12" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N12" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="O12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="P12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
         <v>1.16</v>
       </c>
       <c r="S12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="U12" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="V12" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
-        <v>2.24</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z12" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="AC12" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF12" t="n">
-        <v>9.6</v>
+        <v>18</v>
       </c>
       <c r="AG12" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AH12" t="n">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ12" t="n">
-        <v>970</v>
+        <v>50</v>
       </c>
       <c r="AK12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AL12" t="n">
         <v>85</v>
       </c>
       <c r="AM12" t="n">
-        <v>410</v>
+        <v>250</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>2.46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.76</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.86</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.1</v>
+        <v>6.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.66</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.84</v>
+        <v>5.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AY12" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="AZ12" t="n">
-        <v>2.7</v>
+        <v>22</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.84</v>
+        <v>6</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.54</v>
+        <v>5.7</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.6</v>
+        <v>5.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.78</v>
+        <v>6</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.86</v>
+        <v>6.2</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.58</v>
+        <v>6.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.86</v>
+        <v>6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -2891,76 +2891,76 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>7.2</v>
       </c>
       <c r="H13" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="I13" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
         <v>4.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S13" t="n">
-        <v>2.68</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.16</v>
       </c>
       <c r="X13" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA13" t="n">
         <v>18</v>
       </c>
       <c r="AB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
         <v>11.5</v>
@@ -2999,62 +2999,62 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.2</v>
+        <v>15.5</v>
       </c>
       <c r="AQ13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG13" t="n">
         <v>3.55</v>
       </c>
-      <c r="AR13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.35</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
         <v>3.35</v>
@@ -3103,152 +3103,152 @@
         <v>3.75</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S14" t="n">
         <v>3.5</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.4</v>
-      </c>
       <c r="T14" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="W14" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="X14" t="n">
         <v>970</v>
       </c>
       <c r="Y14" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
         <v>970</v>
       </c>
-      <c r="Z14" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>950</v>
-      </c>
       <c r="AI14" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AJ14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK14" t="n">
         <v>25</v>
       </c>
-      <c r="AK14" t="n">
-        <v>23</v>
-      </c>
       <c r="AL14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AO14" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AQ14" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU14" t="n">
-        <v>3.55</v>
+        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX14" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.8</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>7.6</v>
       </c>
       <c r="G15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="H15" t="n">
         <v>1.23</v>
       </c>
       <c r="I15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J15" t="n">
         <v>4.9</v>
@@ -3297,13 +3297,13 @@
         <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>2.04</v>
       </c>
       <c r="O15" t="n">
         <v>1.17</v>
@@ -3312,7 +3312,7 @@
         <v>2.44</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
         <v>1.58</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,191 +3459,191 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>12:30:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Svg Bleiburg</t>
+          <t>NK Slovenska Bistrica</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KAC 1909</t>
+          <t>NK Bilje</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
-        <v>2.46</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="K16" t="n">
         <v>4.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M16" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="P16" t="n">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="S16" t="n">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="T16" t="n">
-        <v>1.63</v>
+        <v>1.82</v>
       </c>
       <c r="U16" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="V16" t="n">
-        <v>1.68</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>1.39</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="Y16" t="n">
-        <v>14.5</v>
+        <v>950</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="AA16" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>10</v>
       </c>
       <c r="AC16" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="AE16" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>950</v>
       </c>
       <c r="AH16" t="n">
-        <v>19.5</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="AJ16" t="n">
-        <v>65</v>
+        <v>24</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="AL16" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO16" t="n">
         <v>90</v>
       </c>
-      <c r="AN16" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AP16" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AR16" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="AV16" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="AW16" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="AY16" t="n">
         <v>3.55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BA16" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Slovenian 2 SNL</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,186 +3658,186 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Krsko</t>
+          <t>Svg Bleiburg</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slovan Ljublana</t>
+          <t>KAC 1909</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.92</v>
+        <v>2.44</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8</v>
+        <v>2.78</v>
       </c>
       <c r="H17" t="n">
-        <v>2.14</v>
+        <v>2.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>1.94</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R17" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S17" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="T17" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="W17" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="X17" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="Y17" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AA17" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AB17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AD17" t="n">
         <v>13.5</v>
       </c>
       <c r="AE17" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK17" t="n">
         <v>28</v>
       </c>
-      <c r="AF17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI17" t="n">
+      <c r="AL17" t="n">
         <v>40</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>48</v>
-      </c>
       <c r="AM17" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AP17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>4</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AR17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT17" t="n">
         <v>4</v>
       </c>
-      <c r="AS17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AU17" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AW17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY17" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC17" t="n">
         <v>4.6</v>
       </c>
-      <c r="BC17" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BF17" t="n">
         <v>4.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Slovenian 2 SNL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,191 +3847,191 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Al-Akhdoud</t>
+          <t>Krsko</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Ettifaq</t>
+          <t>Slovan Ljublana</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="G18" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="H18" t="n">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="I18" t="n">
-        <v>1.94</v>
+        <v>2.68</v>
       </c>
       <c r="J18" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="O18" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.32</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R18" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="T18" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="U18" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="V18" t="n">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="W18" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="X18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="Y18" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA18" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AB18" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AF18" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AG18" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AI18" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ18" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AK18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AL18" t="n">
         <v>48</v>
       </c>
-      <c r="AL18" t="n">
-        <v>50</v>
-      </c>
       <c r="AM18" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AN18" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>10.5</v>
+        <v>19</v>
       </c>
       <c r="AP18" t="n">
-        <v>6.8</v>
+        <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>10</v>
+        <v>3.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT18" t="n">
-        <v>17</v>
+        <v>3.9</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.199999999999999</v>
+        <v>3.4</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AW18" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY18" t="n">
-        <v>14.5</v>
+        <v>3.9</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="BA18" t="n">
-        <v>24</v>
+        <v>4.4</v>
       </c>
       <c r="BB18" t="n">
-        <v>28</v>
+        <v>4.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>32</v>
+        <v>4.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.8</v>
+        <v>4.5</v>
       </c>
       <c r="BE18" t="n">
-        <v>24</v>
+        <v>4.7</v>
       </c>
       <c r="BF18" t="n">
-        <v>28</v>
+        <v>4.4</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FC Voluntari</t>
+          <t>Al-Akhdoud</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Bihor Oradea</t>
+          <t>Al-Ettifaq</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="G19" t="n">
-        <v>1.49</v>
+        <v>4.4</v>
       </c>
       <c r="H19" t="n">
-        <v>7.4</v>
+        <v>1.93</v>
       </c>
       <c r="I19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X19" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD19" t="n">
         <v>11</v>
       </c>
-      <c r="J19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N19" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S19" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W19" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>400</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>36</v>
-      </c>
       <c r="AE19" t="n">
-        <v>170</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
-        <v>8.4</v>
+        <v>60</v>
       </c>
       <c r="AG19" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AH19" t="n">
         <v>30</v>
       </c>
       <c r="AI19" t="n">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="AK19" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW19" t="n">
         <v>16</v>
       </c>
-      <c r="AL19" t="n">
-        <v>46</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>8</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR19" t="n">
+      <c r="AX19" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG19" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS19" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>9</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Estonian Premier League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>FC Voluntari</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Harju JK Laagri</t>
+          <t>Bihor Oradea</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H20" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>470</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>220</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>320</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>22</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU20" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="J20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>970</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AV20" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX20" t="n">
         <v>7</v>
       </c>
-      <c r="AW20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BB20" t="n">
         <v>11</v>
       </c>
       <c r="BC20" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BD20" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF20" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BG20" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H21" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I21" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="J21" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K21" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
         <v>1.39</v>
@@ -4470,67 +4470,67 @@
         <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
         <v>2.04</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="T21" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="W21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X21" t="n">
         <v>970</v>
       </c>
       <c r="Y21" t="n">
-        <v>970</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
         <v>970</v>
       </c>
       <c r="AA21" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AB21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD21" t="n">
         <v>970</v>
       </c>
       <c r="AE21" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AF21" t="n">
         <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
@@ -4539,74 +4539,74 @@
         <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM21" t="n">
         <v>120</v>
       </c>
       <c r="AN21" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO21" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AS21" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="AT21" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AV21" t="n">
         <v>6.2</v>
       </c>
-      <c r="AU21" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>4.8</v>
-      </c>
       <c r="AW21" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AZ21" t="n">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BC21" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BG21" t="n">
         <v>8.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="G22" t="n">
         <v>2.3</v>
@@ -4646,13 +4646,13 @@
         <v>2.86</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>85</v>
+        <v>4.6</v>
       </c>
       <c r="L22" t="n">
         <v>1.26</v>
@@ -4661,7 +4661,7 @@
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>1.2</v>
@@ -4679,13 +4679,13 @@
         <v>2.28</v>
       </c>
       <c r="T22" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="U22" t="n">
         <v>2.4</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
         <v>1.76</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Austrian Landesliga</t>
+          <t>Estonian Premier League</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Asco Atsv Wolfsberg</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>SV Donau Klagenfurt</t>
+          <t>Harju JK Laagri</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="G23" t="n">
-        <v>1.98</v>
+        <v>1.38</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="K23" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="L23" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M23" t="n">
         <v>1.02</v>
       </c>
       <c r="N23" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="O23" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P23" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="R23" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>1.47</v>
+        <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.52</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="W23" t="n">
-        <v>2.02</v>
+        <v>3.55</v>
       </c>
       <c r="X23" t="n">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y23" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL23" t="n">
         <v>30</v>
       </c>
-      <c r="Z23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AM23" t="n">
         <v>90</v>
       </c>
-      <c r="AB23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>60</v>
-      </c>
       <c r="AN23" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="AO23" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="AP23" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>4.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT23" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.7</v>
+        <v>12</v>
       </c>
       <c r="AV23" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BB23" t="n">
-        <v>4.2</v>
+        <v>11.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Austrian Landesliga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Asco Atsv Wolfsberg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>SV Donau Klagenfurt</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.68</v>
+        <v>1.81</v>
       </c>
       <c r="G24" t="n">
-        <v>2.82</v>
+        <v>1.96</v>
       </c>
       <c r="H24" t="n">
-        <v>2.84</v>
+        <v>3.7</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T24" t="n">
         <v>1.43</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.78</v>
-      </c>
       <c r="U24" t="n">
-        <v>2.16</v>
+        <v>2.74</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="X24" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="Y24" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG24" t="n">
         <v>13</v>
       </c>
-      <c r="Z24" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA24" t="n">
+      <c r="AH24" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AM24" t="n">
         <v>55</v>
       </c>
-      <c r="AB24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>110</v>
-      </c>
       <c r="AN24" t="n">
-        <v>34</v>
+        <v>6.8</v>
       </c>
       <c r="AO24" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AP24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>4.9</v>
       </c>
       <c r="AR24" t="n">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="AS24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB24" t="n">
         <v>4.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.7</v>
       </c>
       <c r="BC24" t="n">
         <v>4.4</v>
       </c>
       <c r="BD24" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>23</v>
+        <v>4.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Norwegian Eliteserien</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bodo Glimt</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.13</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.14</v>
+        <v>2.76</v>
       </c>
       <c r="H25" t="n">
-        <v>23</v>
+        <v>2.86</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="J25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X25" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG25" t="n">
         <v>12.5</v>
       </c>
-      <c r="K25" t="n">
+      <c r="AH25" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX25" t="n">
         <v>13</v>
       </c>
-      <c r="L25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P25" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="R25" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>950</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>280</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>320</v>
-      </c>
-      <c r="AF25" t="n">
+      <c r="AY25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ25" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>36</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>330</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>40</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT25" t="n">
+      <c r="BA25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF25" t="n">
         <v>20</v>
       </c>
-      <c r="AU25" t="n">
-        <v>20</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>34</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>2.12</v>
-      </c>
       <c r="BG25" t="n">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Turkish 2 Lig</t>
+          <t>Norwegian Eliteserien</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sanliurfaspor</t>
+          <t>Bodo Glimt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Muglaspor</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.62</v>
+        <v>1.13</v>
       </c>
       <c r="G26" t="n">
-        <v>3.15</v>
+        <v>1.14</v>
       </c>
       <c r="H26" t="n">
-        <v>2.48</v>
+        <v>23</v>
       </c>
       <c r="I26" t="n">
-        <v>2.94</v>
+        <v>32</v>
       </c>
       <c r="J26" t="n">
-        <v>2.98</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L26" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="M26" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>3.4</v>
+        <v>13</v>
       </c>
       <c r="O26" t="n">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="P26" t="n">
-        <v>1.93</v>
+        <v>4.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.82</v>
+        <v>1.23</v>
       </c>
       <c r="R26" t="n">
-        <v>1.36</v>
+        <v>2.5</v>
       </c>
       <c r="S26" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="V26" t="n">
-        <v>1.51</v>
+        <v>1.03</v>
       </c>
       <c r="W26" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>440</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>340</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>46</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT26" t="n">
         <v>17.5</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AU26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>36</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY26" t="n">
         <v>14</v>
       </c>
-      <c r="Z26" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA26" t="n">
+      <c r="AZ26" t="n">
+        <v>38</v>
+      </c>
+      <c r="BA26" t="n">
         <v>46</v>
       </c>
-      <c r="AB26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC26" t="n">
+      <c r="BB26" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD26" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ26" t="n">
+      <c r="BC26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG26" t="n">
         <v>50</v>
       </c>
-      <c r="AK26" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>30</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>27</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>French National</t>
+          <t>Turkish 2 Lig</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sanliurfaspor</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Muglaspor</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.85</v>
+        <v>2.62</v>
       </c>
       <c r="G27" t="n">
-        <v>1.91</v>
+        <v>3.15</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="I27" t="n">
-        <v>5.4</v>
+        <v>2.94</v>
       </c>
       <c r="J27" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="P27" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AQ27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="X27" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>970</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>130</v>
-      </c>
-      <c r="AP27" t="n">
+      <c r="AR27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS27" t="n">
         <v>5</v>
       </c>
-      <c r="AQ27" t="n">
+      <c r="AT27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE27" t="n">
         <v>5.3</v>
       </c>
-      <c r="AR27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX27" t="n">
+      <c r="BF27" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BG27" t="n">
         <v>4.6</v>
       </c>
-      <c r="AY27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Chateauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="G28" t="n">
-        <v>1.48</v>
+        <v>1.9</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>5.4</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="M28" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>2.3</v>
+        <v>1.77</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.74</v>
+        <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="V28" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="W28" t="n">
-        <v>2.74</v>
+        <v>1.95</v>
       </c>
       <c r="X28" t="n">
-        <v>950</v>
+        <v>13.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="Z28" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB28" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC28" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AD28" t="n">
         <v>950</v>
       </c>
       <c r="AE28" t="n">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH28" t="n">
         <v>950</v>
       </c>
       <c r="AI28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="AK28" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AM28" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN28" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW28" t="n">
         <v>7.6</v>
       </c>
-      <c r="AO28" t="n">
-        <v>180</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT28" t="n">
+      <c r="AX28" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD28" t="n">
         <v>7</v>
       </c>
-      <c r="AU28" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BE28" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BF28" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>French National</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Al-Kholood Club</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al-Feiha</t>
+          <t>Chateauroux</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.62</v>
+        <v>1.42</v>
       </c>
       <c r="G29" t="n">
-        <v>2.72</v>
+        <v>1.45</v>
       </c>
       <c r="H29" t="n">
+        <v>8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>10</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="S29" t="n">
         <v>2.78</v>
       </c>
-      <c r="I29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="T29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="X29" t="n">
+        <v>950</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>190</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY29" t="n">
         <v>4.2</v>
       </c>
-      <c r="O29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U29" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="X29" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>26</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR29" t="n">
+      <c r="AZ29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA29" t="n">
         <v>5.5</v>
       </c>
-      <c r="AS29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV29" t="n">
+      <c r="BB29" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BD29" t="n">
         <v>4.9</v>
       </c>
-      <c r="AW29" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UEFA Europa Conference League</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Shakhtar</t>
+          <t>Al-Kholood Club</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Al-Feiha</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4.1</v>
+        <v>2.64</v>
       </c>
       <c r="G30" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="H30" t="n">
-        <v>2.12</v>
+        <v>2.76</v>
       </c>
       <c r="I30" t="n">
-        <v>2.16</v>
+        <v>2.92</v>
       </c>
       <c r="J30" t="n">
         <v>3.45</v>
       </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L30" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="O30" t="n">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="P30" t="n">
-        <v>1.72</v>
+        <v>1.98</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.36</v>
+        <v>1.97</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.37</v>
       </c>
       <c r="S30" t="n">
-        <v>4.6</v>
+        <v>3.35</v>
       </c>
       <c r="T30" t="n">
-        <v>2.02</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.87</v>
+        <v>1.54</v>
       </c>
       <c r="W30" t="n">
-        <v>1.31</v>
+        <v>1.55</v>
       </c>
       <c r="X30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE30" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>46</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>95</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>50</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>60</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>19</v>
-      </c>
       <c r="BF30" t="n">
-        <v>60</v>
+        <v>8.6</v>
       </c>
       <c r="BG30" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6374,186 +6374,186 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Shakhtar</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.24</v>
+        <v>4.1</v>
       </c>
       <c r="G31" t="n">
-        <v>2.26</v>
+        <v>4.2</v>
       </c>
       <c r="H31" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="I31" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="J31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.5</v>
       </c>
-      <c r="K31" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L31" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="O31" t="n">
-        <v>1.34</v>
+        <v>1.46</v>
       </c>
       <c r="P31" t="n">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="Q31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T31" t="n">
         <v>2.02</v>
       </c>
-      <c r="R31" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.81</v>
-      </c>
       <c r="U31" t="n">
-        <v>2.18</v>
+        <v>1.92</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.89</v>
       </c>
       <c r="W31" t="n">
-        <v>1.79</v>
+        <v>1.31</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="Z31" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AA31" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AB31" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AC31" t="n">
         <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="AF31" t="n">
-        <v>13.5</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR31" t="n">
         <v>11</v>
       </c>
-      <c r="AH31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL31" t="n">
+      <c r="AS31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>26</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA31" t="n">
         <v>38</v>
       </c>
-      <c r="AM31" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS31" t="n">
+      <c r="BB31" t="n">
+        <v>80</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>48</v>
+      </c>
+      <c r="BD31" t="n">
         <v>60</v>
       </c>
-      <c r="AT31" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>46</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>25</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>32</v>
-      </c>
       <c r="BE31" t="n">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="BF31" t="n">
-        <v>15.5</v>
+        <v>65</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>19.5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UEFA Europa League</t>
+          <t>UEFA Europa Conference League</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6568,179 +6568,179 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.84</v>
+        <v>2.2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.88</v>
+        <v>2.22</v>
       </c>
       <c r="H32" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="I32" t="n">
-        <v>2.82</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="O32" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
         <v>1.37</v>
       </c>
-      <c r="P32" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S32" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="T32" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U32" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V32" t="n">
-        <v>1.54</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="X32" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Y32" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="Z32" t="n">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="AA32" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE32" t="n">
         <v>44</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AF32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG32" t="n">
         <v>11</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>12.5</v>
       </c>
       <c r="AH32" t="n">
         <v>17</v>
       </c>
       <c r="AI32" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AJ32" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AK32" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM32" t="n">
         <v>90</v>
       </c>
       <c r="AN32" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="AO32" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="AP32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ32" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY32" t="n">
         <v>10</v>
       </c>
-      <c r="AR32" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AZ32" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BB32" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="BC32" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BD32" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BE32" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF32" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -6762,186 +6762,186 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Braga</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="G33" t="n">
-        <v>2.4</v>
+        <v>2.96</v>
       </c>
       <c r="H33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N33" t="n">
         <v>3.6</v>
       </c>
-      <c r="I33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3.2</v>
-      </c>
       <c r="O33" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="P33" t="n">
-        <v>1.74</v>
+        <v>1.87</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="R33" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="U33" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V33" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="W33" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="X33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB33" t="n">
         <v>11</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AC33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>38</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV33" t="n">
         <v>11.5</v>
       </c>
-      <c r="Z33" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>70</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AW33" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY33" t="n">
         <v>11.5</v>
       </c>
-      <c r="AH33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK33" t="n">
+      <c r="AZ33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>44</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>80</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>28</v>
+      </c>
+      <c r="BG33" t="n">
         <v>27</v>
       </c>
-      <c r="AL33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>120</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>14</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>44</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>100</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>23</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>50</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Chilean Primera B</t>
+          <t>UEFA Europa League</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Union Espanola</t>
+          <t>Braga</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Curico Unido</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="G34" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="H34" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S34" t="n">
         <v>4.8</v>
       </c>
-      <c r="J34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.55</v>
-      </c>
       <c r="T34" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="U34" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V34" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="W34" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="X34" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="Z34" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="AA34" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AB34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP34" t="n">
         <v>10</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>27</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>970</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
         <v>10.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.4</v>
+        <v>60</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.1</v>
+        <v>14.5</v>
       </c>
       <c r="AW34" t="n">
-        <v>4.3</v>
+        <v>48</v>
       </c>
       <c r="AX34" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY34" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="BA34" t="n">
-        <v>4.4</v>
+        <v>55</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.1</v>
+        <v>30</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.2</v>
+        <v>44</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.5</v>
+        <v>100</v>
       </c>
       <c r="BF34" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.4</v>
+        <v>60</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Chilean Primera B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7145,184 +7145,184 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>22:00:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lobos UPNFM</t>
+          <t>Union Espanola</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CD Motagua</t>
+          <t>Curico Unido</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G35" t="n">
-        <v>990</v>
+        <v>2.08</v>
       </c>
       <c r="H35" t="n">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>990</v>
+        <v>4.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K35" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M35" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="X35" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>970</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>120</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD35" t="n">
         <v>950</v>
       </c>
-      <c r="L35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF35" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH35" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK35" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL35" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM35" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN35" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO35" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT35" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU35" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AV35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD35" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG35" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="G36" t="n">
-        <v>990</v>
+        <v>600</v>
       </c>
       <c r="H36" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>990</v>
+        <v>110</v>
       </c>
       <c r="J36" t="n">
         <v>1.09</v>
       </c>
       <c r="K36" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7377,13 +7377,13 @@
         <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O36" t="n">
         <v>1.2</v>
       </c>
       <c r="P36" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q36" t="n">
         <v>1.2</v>
@@ -7401,10 +7401,10 @@
         <v>1.11</v>
       </c>
       <c r="V36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7547,170 +7547,170 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H37" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K37" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="L37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M37" t="n">
         <v>1.04</v>
       </c>
-      <c r="G37" t="n">
-        <v>600</v>
-      </c>
-      <c r="H37" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="I37" t="n">
-        <v>990</v>
-      </c>
-      <c r="J37" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="N37" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P37" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X37" t="n">
         <v>950</v>
       </c>
-      <c r="L37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R37" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W37" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1000</v>
-      </c>
       <c r="Y37" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z37" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AA37" t="n">
         <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD37" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE37" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH37" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI37" t="n">
         <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL37" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM37" t="n">
         <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="AS37" t="n">
-        <v>1.01</v>
+        <v>2.88</v>
       </c>
       <c r="AT37" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AV37" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BA37" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC37" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD37" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG37" t="n">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-30 03:17:28</t>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>
@@ -7732,179 +7732,373 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>Lobos UPNFM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>CD Motagua</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>17</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>170</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>75</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:36:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Honduras Liga Nacional</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>22:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
           <t>Olancho</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Genesis Huracan</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G38" t="n">
-        <v>990</v>
-      </c>
-      <c r="H38" t="n">
+      <c r="F39" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G39" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="H39" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>11</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K39" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M39" t="n">
         <v>1.04</v>
       </c>
-      <c r="I38" t="n">
-        <v>990</v>
-      </c>
-      <c r="J38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K38" t="n">
+      <c r="N39" t="n">
+        <v>4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="X39" t="n">
         <v>950</v>
       </c>
-      <c r="L38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X38" t="n">
+      <c r="Y39" t="n">
+        <v>950</v>
+      </c>
+      <c r="Z39" t="n">
         <v>1000</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="AA39" t="n">
         <v>1000</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="AB39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>950</v>
+      </c>
+      <c r="AE39" t="n">
         <v>1000</v>
       </c>
-      <c r="AA38" t="n">
+      <c r="AF39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>950</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1000</v>
       </c>
-      <c r="AB38" t="n">
+      <c r="AJ39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM39" t="n">
         <v>1000</v>
       </c>
-      <c r="AC38" t="n">
+      <c r="AN39" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO39" t="n">
         <v>1000</v>
       </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-04-30 03:17:28</t>
+      <c r="AP39" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-04-30 05:36:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>3.7</v>
+        <v>7.2</v>
       </c>
       <c r="H2" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>2.48</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>1.55</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>2.32</v>
       </c>
       <c r="N2" t="n">
-        <v>2.74</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>10.5</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.62</v>
+        <v>60</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4</v>
+        <v>300</v>
       </c>
       <c r="T2" t="n">
-        <v>2.08</v>
+        <v>15.5</v>
       </c>
       <c r="U2" t="n">
-        <v>1.78</v>
+        <v>1.05</v>
       </c>
       <c r="V2" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
       <c r="X2" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>230</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS2" t="n">
         <v>11</v>
       </c>
-      <c r="Y2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AT2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU2" t="n">
         <v>18</v>
       </c>
-      <c r="AH2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV2" t="n">
-        <v>10</v>
+        <v>110</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AX2" t="n">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="AY2" t="n">
-        <v>13.5</v>
+        <v>140</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>170</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>100</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>130</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>100</v>
       </c>
       <c r="BE2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>130</v>
       </c>
-      <c r="BF2" t="n">
-        <v>7</v>
-      </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>6</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>55</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="S3" t="n">
+        <v>260</v>
+      </c>
+      <c r="T3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>310</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>280</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>4.9</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>170</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN3" t="n">
+      <c r="AR3" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>190</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>140</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AY3" t="n">
         <v>120</v>
       </c>
-      <c r="AO3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>5.4</v>
+        <v>150</v>
       </c>
       <c r="BA3" t="n">
-        <v>6</v>
+        <v>290</v>
       </c>
       <c r="BB3" t="n">
-        <v>6.8</v>
+        <v>190</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.4</v>
+        <v>260</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.4</v>
+        <v>120</v>
       </c>
       <c r="BE3" t="n">
         <v>100</v>
       </c>
       <c r="BF3" t="n">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="BG3" t="n">
-        <v>9.4</v>
+        <v>280</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="G4" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="H4" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K4" t="n">
         <v>2.82</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>2.24</v>
       </c>
       <c r="M4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.09</v>
       </c>
-      <c r="N4" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.25</v>
-      </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
-        <v>1.9</v>
+        <v>1.45</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W4" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>5.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>970</v>
+        <v>7.6</v>
       </c>
       <c r="Z4" t="n">
         <v>23</v>
       </c>
       <c r="AA4" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>530</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>95</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>46</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>65</v>
+      </c>
+      <c r="BG4" t="n">
         <v>60</v>
       </c>
-      <c r="AB4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -1342,79 +1342,79 @@
         <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U5" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.69</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA5" t="n">
         <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF5" t="n">
         <v>18</v>
@@ -1423,86 +1423,86 @@
         <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC5" t="n">
         <v>20</v>
       </c>
-      <c r="AO5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD5" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="G6" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="H6" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="O6" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="P6" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="R6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.16</v>
       </c>
-      <c r="S6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="T6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W6" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="X6" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AA6" t="n">
-        <v>250</v>
+        <v>310</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="AE6" t="n">
         <v>160</v>
       </c>
       <c r="AF6" t="n">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>11</v>
       </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>38</v>
       </c>
       <c r="AI6" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AJ6" t="n">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="AK6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL6" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
-        <v>420</v>
+        <v>290</v>
       </c>
       <c r="AN6" t="n">
-        <v>27</v>
+        <v>17.5</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AP6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR6" t="n">
         <v>40</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.54</v>
+        <v>12</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.6</v>
+        <v>23</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.55</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.54</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>2.54</v>
+        <v>12</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.54</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -1727,22 +1727,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.9</v>
       </c>
-      <c r="I7" t="n">
-        <v>4.1</v>
-      </c>
       <c r="J7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.45</v>
       </c>
       <c r="L7" t="n">
         <v>1.62</v>
@@ -1751,73 +1751,73 @@
         <v>1.13</v>
       </c>
       <c r="N7" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="O7" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P7" t="n">
         <v>1.49</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
         <v>1.7</v>
       </c>
       <c r="V7" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W7" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z7" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AA7" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="AB7" t="n">
         <v>7</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE7" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG7" t="n">
         <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI7" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
         <v>36</v>
@@ -1826,71 +1826,71 @@
         <v>70</v>
       </c>
       <c r="AM7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AN7" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO7" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AP7" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT7" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
         <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AX7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.2</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>6.4</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.6</v>
+        <v>30</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>13.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -1921,70 +1921,70 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L8" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M8" t="n">
         <v>1.17</v>
       </c>
       <c r="N8" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="U8" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AB8" t="n">
         <v>6.4</v>
@@ -1993,10 +1993,10 @@
         <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE8" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2005,10 +2005,10 @@
         <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AJ8" t="n">
         <v>980</v>
@@ -2017,74 +2017,74 @@
         <v>40</v>
       </c>
       <c r="AL8" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AM8" t="n">
-        <v>390</v>
+        <v>360</v>
       </c>
       <c r="AN8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AO8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP8" t="n">
         <v>6.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>11</v>
       </c>
       <c r="AZ8" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF8" t="n">
         <v>29</v>
       </c>
-      <c r="BA8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC8" t="n">
+      <c r="BG8" t="n">
         <v>10</v>
       </c>
-      <c r="BD8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -2115,25 +2115,25 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="J9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.3</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M9" t="n">
         <v>1.14</v>
@@ -2148,7 +2148,7 @@
         <v>1.44</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="R9" t="n">
         <v>1.15</v>
@@ -2160,43 +2160,43 @@
         <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="V9" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="W9" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="X9" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="Z9" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AA9" t="n">
         <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
         <v>32</v>
@@ -2205,19 +2205,19 @@
         <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AK9" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
         <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="AN9" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO9" t="n">
         <v>170</v>
@@ -2226,59 +2226,59 @@
         <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.6</v>
+        <v>25</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="AX9" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>5.8</v>
+        <v>25</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB9" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="BC9" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BF9" t="n">
-        <v>5.8</v>
+        <v>29</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -2309,55 +2309,55 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="G10" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="H10" t="n">
         <v>1.57</v>
       </c>
       <c r="I10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="J10" t="n">
         <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.04</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q10" t="n">
         <v>1.66</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S10" t="n">
         <v>2.68</v>
       </c>
       <c r="T10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U10" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V10" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="W10" t="n">
         <v>1.16</v>
@@ -2387,40 +2387,40 @@
         <v>18</v>
       </c>
       <c r="AF10" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AG10" t="n">
         <v>32</v>
       </c>
       <c r="AH10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI10" t="n">
         <v>38</v>
       </c>
       <c r="AJ10" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AK10" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM10" t="n">
         <v>130</v>
       </c>
       <c r="AN10" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR10" t="n">
         <v>8.199999999999999</v>
@@ -2429,50 +2429,50 @@
         <v>11.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="n">
         <v>8.4</v>
       </c>
-      <c r="AV10" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AW10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>4.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC10" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.8</v>
       </c>
       <c r="BD10" t="n">
         <v>4.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG10" t="n">
         <v>6</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -2503,97 +2503,97 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="G11" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="K11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
         <v>3.4</v>
       </c>
-      <c r="L11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.45</v>
-      </c>
       <c r="O11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P11" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R11" t="n">
         <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="U11" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="V11" t="n">
         <v>1.34</v>
       </c>
       <c r="W11" t="n">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y11" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
         <v>85</v>
       </c>
       <c r="AB11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
       </c>
       <c r="AF11" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AG11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
         <v>65</v>
       </c>
       <c r="AJ11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK11" t="n">
         <v>32</v>
@@ -2611,62 +2611,62 @@
         <v>55</v>
       </c>
       <c r="AP11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
         <v>13</v>
       </c>
       <c r="AY11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE11" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1.09</v>
       </c>
       <c r="G12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="H12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="I12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="J12" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="K12" t="n">
-        <v>500</v>
+        <v>12</v>
       </c>
       <c r="L12" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="M12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N12" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="O12" t="n">
         <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R12" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="S12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
         <v>950</v>
@@ -2784,7 +2784,7 @@
         <v>950</v>
       </c>
       <c r="AI12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ12" t="n">
         <v>1000</v>
@@ -2802,65 +2802,65 @@
         <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AP12" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AS12" t="n">
         <v>3.3</v>
       </c>
       <c r="AT12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AU12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY12" t="n">
+      <c r="BA12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AZ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BB12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -2891,82 +2891,82 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="G13" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H13" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>5.7</v>
       </c>
       <c r="J13" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M13" t="n">
         <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>1.27</v>
       </c>
       <c r="P13" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="R13" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S13" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U13" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W13" t="n">
         <v>2.06</v>
       </c>
       <c r="X13" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="Y13" t="n">
         <v>970</v>
       </c>
       <c r="Z13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA13" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB13" t="n">
         <v>970</v>
       </c>
       <c r="AC13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD13" t="n">
         <v>970</v>
       </c>
-      <c r="AD13" t="n">
-        <v>950</v>
-      </c>
       <c r="AE13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF13" t="n">
         <v>970</v>
@@ -2975,86 +2975,86 @@
         <v>970</v>
       </c>
       <c r="AH13" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI13" t="n">
         <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AK13" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM13" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN13" t="n">
         <v>970</v>
       </c>
       <c r="AO13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV13" t="n">
         <v>5.4</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AW13" t="n">
-        <v>4</v>
+        <v>2.56</v>
       </c>
       <c r="AX13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AY13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ13" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB13" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BC13" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>6.2</v>
+        <v>3.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="BF13" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>4</v>
+        <v>2.96</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="G14" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="H14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I14" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J14" t="n">
         <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>990</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.28</v>
@@ -3109,37 +3109,37 @@
         <v>1.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.1</v>
+        <v>4.3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P14" t="n">
         <v>2.14</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R14" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="T14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U14" t="n">
         <v>2.3</v>
       </c>
       <c r="V14" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X14" t="n">
-        <v>950</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="n">
         <v>16.5</v>
@@ -3148,7 +3148,7 @@
         <v>23</v>
       </c>
       <c r="AA14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB14" t="n">
         <v>16.5</v>
@@ -3163,92 +3163,92 @@
         <v>32</v>
       </c>
       <c r="AF14" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG14" t="n">
         <v>15</v>
       </c>
       <c r="AH14" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AJ14" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK14" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL14" t="n">
         <v>42</v>
       </c>
       <c r="AM14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN14" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AO14" t="n">
         <v>22</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.84</v>
+        <v>16</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.86</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT14" t="n">
-        <v>3.15</v>
+        <v>11.5</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.96</v>
+        <v>7.8</v>
       </c>
       <c r="AV14" t="n">
-        <v>3.1</v>
+        <v>10.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>3.5</v>
+        <v>22</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.84</v>
+        <v>17</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.25</v>
+        <v>10.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.25</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.38</v>
+        <v>4.6</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.34</v>
+        <v>4.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.44</v>
+        <v>4.7</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.52</v>
+        <v>17.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.3</v>
+        <v>15.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -3279,61 +3279,61 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G15" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
         <v>2.32</v>
       </c>
       <c r="I15" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="J15" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K15" t="n">
         <v>4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.05</v>
       </c>
       <c r="N15" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="O15" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P15" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>2.72</v>
+        <v>2.96</v>
       </c>
       <c r="T15" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="U15" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V15" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Y15" t="n">
         <v>13.5</v>
@@ -3372,7 +3372,7 @@
         <v>65</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL15" t="n">
         <v>48</v>
@@ -3387,62 +3387,62 @@
         <v>19</v>
       </c>
       <c r="AP15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>3.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.3</v>
+        <v>19.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.9</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -3473,25 +3473,25 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H16" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="I16" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
@@ -3500,82 +3500,82 @@
         <v>4.8</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="V16" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X16" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Y16" t="n">
         <v>11.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AB16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>10.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF16" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AG16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AJ16" t="n">
         <v>95</v>
       </c>
       <c r="AK16" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM16" t="n">
         <v>80</v>
       </c>
-      <c r="AL16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>70</v>
-      </c>
       <c r="AN16" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AO16" t="n">
         <v>11</v>
@@ -3587,56 +3587,56 @@
         <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AS16" t="n">
         <v>20</v>
       </c>
       <c r="AT16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>29</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>15.5</v>
       </c>
-      <c r="AU16" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>14</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.199999999999999</v>
+        <v>40</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>9.4</v>
+        <v>16.5</v>
       </c>
       <c r="BF16" t="n">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BG16" t="n">
         <v>9.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="H17" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="J17" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K17" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="L17" t="n">
         <v>1.24</v>
@@ -3694,10 +3694,10 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q17" t="n">
         <v>1.45</v>
@@ -3709,64 +3709,64 @@
         <v>2.14</v>
       </c>
       <c r="T17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W17" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="X17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y17" t="n">
         <v>950</v>
       </c>
-      <c r="Y17" t="n">
-        <v>48</v>
-      </c>
       <c r="Z17" t="n">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="AA17" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="AB17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>950</v>
+        <v>44</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>160</v>
       </c>
       <c r="AF17" t="n">
-        <v>970</v>
+        <v>12</v>
       </c>
       <c r="AG17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH17" t="n">
-        <v>950</v>
+        <v>23</v>
       </c>
       <c r="AI17" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="n">
         <v>14</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="AM17" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AN17" t="n">
         <v>4.6</v>
@@ -3775,62 +3775,62 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT17" t="n">
         <v>11.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY17" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ17" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>25</v>
       </c>
       <c r="BB17" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
         <v>11.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BG17" t="n">
-        <v>20</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -3864,70 +3864,70 @@
         <v>1.45</v>
       </c>
       <c r="G18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H18" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K18" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M18" t="n">
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P18" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
         <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U18" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V18" t="n">
         <v>1.11</v>
       </c>
       <c r="W18" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X18" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z18" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AA18" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="AB18" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AC18" t="n">
         <v>11</v>
@@ -3939,92 +3939,92 @@
         <v>170</v>
       </c>
       <c r="AF18" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AG18" t="n">
         <v>11</v>
       </c>
       <c r="AH18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL18" t="n">
         <v>46</v>
       </c>
       <c r="AM18" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN18" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AO18" t="n">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AP18" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR18" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AS18" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT18" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY18" t="n">
         <v>9</v>
       </c>
-      <c r="AV18" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BB18" t="n">
         <v>11</v>
       </c>
       <c r="BC18" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>13.5</v>
+        <v>36</v>
       </c>
       <c r="BE18" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF18" t="n">
         <v>6.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -4058,55 +4058,55 @@
         <v>2.2</v>
       </c>
       <c r="G19" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>2.86</v>
+        <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1</v>
+        <v>3.75</v>
       </c>
       <c r="K19" t="n">
         <v>4.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="M19" t="n">
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="O19" t="n">
         <v>1.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="S19" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>2.4</v>
       </c>
       <c r="V19" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
         <v>950</v>
@@ -4118,7 +4118,7 @@
         <v>34</v>
       </c>
       <c r="AA19" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="n">
         <v>970</v>
@@ -4154,7 +4154,7 @@
         <v>36</v>
       </c>
       <c r="AM19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN19" t="n">
         <v>970</v>
@@ -4163,62 +4163,62 @@
         <v>32</v>
       </c>
       <c r="AP19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>3.65</v>
       </c>
-      <c r="AQ19" t="n">
+      <c r="AR19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT19" t="n">
         <v>3.5</v>
       </c>
-      <c r="AR19" t="n">
+      <c r="AU19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC19" t="n">
         <v>3.75</v>
       </c>
-      <c r="AS19" t="n">
+      <c r="BD19" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT19" t="n">
+      <c r="BE19" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3.35</v>
       </c>
-      <c r="AU19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA19" t="n">
+      <c r="BG19" t="n">
         <v>3.85</v>
       </c>
-      <c r="BB19" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="G20" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="I20" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="J20" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L20" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M20" t="n">
         <v>1.06</v>
@@ -4276,13 +4276,13 @@
         <v>4.3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P20" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R20" t="n">
         <v>1.43</v>
@@ -4291,128 +4291,128 @@
         <v>3.05</v>
       </c>
       <c r="T20" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U20" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V20" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="W20" t="n">
         <v>1.25</v>
       </c>
       <c r="X20" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>11</v>
-      </c>
       <c r="AE20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG20" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AJ20" t="n">
         <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL20" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN20" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AP20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>34</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB20" t="n">
         <v>13.5</v>
       </c>
-      <c r="AQ20" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT20" t="n">
+      <c r="BC20" t="n">
+        <v>32</v>
+      </c>
+      <c r="BD20" t="n">
         <v>14.5</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>6</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>6</v>
-      </c>
       <c r="BE20" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.2</v>
+        <v>46</v>
       </c>
       <c r="BG20" t="n">
-        <v>4.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="G21" t="n">
-        <v>1.96</v>
+        <v>2.16</v>
       </c>
       <c r="H21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I21" t="n">
         <v>3.5</v>
       </c>
-      <c r="I21" t="n">
-        <v>4.7</v>
-      </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="M21" t="n">
         <v>1.02</v>
       </c>
       <c r="N21" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="O21" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U21" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>2.04</v>
+        <v>1.86</v>
       </c>
       <c r="X21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y21" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Z21" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AA21" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AF21" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG21" t="n">
         <v>13.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
         <v>26</v>
       </c>
       <c r="AM21" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AO21" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AP21" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="AQ21" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="AR21" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT21" t="n">
-        <v>4.1</v>
+        <v>16.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.75</v>
+        <v>10.5</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>16.5</v>
       </c>
       <c r="AY21" t="n">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="AZ21" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>4.2</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="BE21" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="BG21" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H22" t="n">
         <v>2.7</v>
       </c>
-      <c r="G22" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.82</v>
-      </c>
       <c r="I22" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4661,7 +4661,7 @@
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O22" t="n">
         <v>1.35</v>
@@ -4670,7 +4670,7 @@
         <v>1.87</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R22" t="n">
         <v>1.33</v>
@@ -4685,10 +4685,10 @@
         <v>1.58</v>
       </c>
       <c r="V22" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W22" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="X22" t="n">
         <v>1000</v>
@@ -4718,7 +4718,7 @@
         <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AY22" t="n">
         <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.13</v>
       </c>
       <c r="H23" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>32</v>
@@ -4846,7 +4846,7 @@
         <v>12</v>
       </c>
       <c r="K23" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.16</v>
@@ -4855,28 +4855,28 @@
         <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.07</v>
       </c>
       <c r="P23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Q23" t="n">
         <v>1.24</v>
       </c>
       <c r="R23" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="S23" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="T23" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="V23" t="n">
         <v>1.02</v>
@@ -4885,7 +4885,7 @@
         <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Y23" t="n">
         <v>150</v>
@@ -4900,10 +4900,10 @@
         <v>21</v>
       </c>
       <c r="AC23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AD23" t="n">
-        <v>95</v>
+        <v>940</v>
       </c>
       <c r="AE23" t="n">
         <v>440</v>
@@ -4912,10 +4912,10 @@
         <v>12</v>
       </c>
       <c r="AG23" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH23" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4927,22 +4927,22 @@
         <v>14.5</v>
       </c>
       <c r="AL23" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AO23" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AP23" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AQ23" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AR23" t="n">
         <v>55</v>
@@ -4954,25 +4954,25 @@
         <v>18</v>
       </c>
       <c r="AU23" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AV23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AW23" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="AX23" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY23" t="n">
         <v>14.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BA23" t="n">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="BB23" t="n">
         <v>8.6</v>
@@ -4981,20 +4981,20 @@
         <v>13</v>
       </c>
       <c r="BD23" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BE23" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BF23" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="BG23" t="n">
         <v>95</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5025,76 +5025,76 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="G24" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H24" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="I24" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S24" t="n">
         <v>3.9</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="U24" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V24" t="n">
         <v>1.53</v>
       </c>
       <c r="W24" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="X24" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA24" t="n">
         <v>48</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
         <v>14</v>
@@ -5112,7 +5112,7 @@
         <v>19.5</v>
       </c>
       <c r="AI24" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ24" t="n">
         <v>55</v>
@@ -5121,74 +5121,74 @@
         <v>38</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AM24" t="n">
         <v>110</v>
       </c>
       <c r="AN24" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AO24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.9</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.7</v>
+        <v>8.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.7</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.75</v>
+        <v>9.4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX24" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.4</v>
+        <v>19.5</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="G25" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="H25" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="I25" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="K25" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V25" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="X25" t="n">
         <v>12</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="Z25" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA25" t="n">
-        <v>220</v>
+        <v>170</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD25" t="n">
         <v>950</v>
       </c>
       <c r="AE25" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AF25" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AG25" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
         <v>950</v>
       </c>
       <c r="AI25" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ25" t="n">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AK25" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
         <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN25" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AO25" t="n">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AR25" t="n">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AS25" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT25" t="n">
         <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF25" t="n">
         <v>6.2</v>
       </c>
-      <c r="AW25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG25" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="G26" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="H26" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="I26" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="K26" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M26" t="n">
         <v>1.05</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="O26" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="R26" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S26" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="T26" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="U26" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W26" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="X26" t="n">
         <v>19.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>950</v>
+        <v>32</v>
       </c>
       <c r="Z26" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AA26" t="n">
-        <v>370</v>
+        <v>260</v>
       </c>
       <c r="AB26" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF26" t="n">
         <v>11</v>
       </c>
-      <c r="AC26" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>170</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI26" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AJ26" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AK26" t="n">
         <v>18</v>
       </c>
       <c r="AL26" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AM26" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO26" t="n">
         <v>170</v>
       </c>
-      <c r="AN26" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>230</v>
-      </c>
       <c r="AP26" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.7</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX26" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AY26" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC26" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA26" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BD26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5607,124 +5607,124 @@
         </is>
       </c>
       <c r="F27" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H27" t="n">
         <v>2.72</v>
       </c>
-      <c r="G27" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H27" t="n">
-        <v>2.74</v>
-      </c>
       <c r="I27" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="T27" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V27" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W27" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="X27" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AB27" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AC27" t="n">
         <v>7.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF27" t="n">
-        <v>970</v>
+        <v>19</v>
       </c>
       <c r="AG27" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL27" t="n">
         <v>46</v>
       </c>
-      <c r="AK27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>42</v>
-      </c>
       <c r="AM27" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO27" t="n">
         <v>28</v>
       </c>
-      <c r="AO27" t="n">
-        <v>26</v>
-      </c>
       <c r="AP27" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AQ27" t="n">
         <v>10</v>
       </c>
       <c r="AR27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AT27" t="n">
         <v>10</v>
@@ -5733,44 +5733,44 @@
         <v>7</v>
       </c>
       <c r="AV27" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="AX27" t="n">
-        <v>6</v>
+        <v>15.5</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
       </c>
       <c r="AZ27" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB27" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="BC27" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD27" t="n">
         <v>34</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.2</v>
+        <v>11.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>22</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG27" t="n">
-        <v>19.5</v>
+        <v>9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
+        <v>4</v>
+      </c>
+      <c r="G28" t="n">
         <v>4.1</v>
       </c>
-      <c r="G28" t="n">
-        <v>4.2</v>
-      </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I28" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="J28" t="n">
         <v>3.4</v>
@@ -5819,58 +5819,58 @@
         <v>3.45</v>
       </c>
       <c r="L28" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P28" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R28" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
         <v>4.6</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V28" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="W28" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" t="n">
         <v>11.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB28" t="n">
         <v>12</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD28" t="n">
         <v>11</v>
@@ -5879,34 +5879,34 @@
         <v>25</v>
       </c>
       <c r="AF28" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG28" t="n">
         <v>17</v>
       </c>
       <c r="AH28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ28" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AK28" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL28" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AM28" t="n">
         <v>140</v>
       </c>
       <c r="AN28" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AO28" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP28" t="n">
         <v>10</v>
@@ -5915,7 +5915,7 @@
         <v>7.2</v>
       </c>
       <c r="AR28" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS28" t="n">
         <v>24</v>
@@ -5924,47 +5924,47 @@
         <v>11</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW28" t="n">
         <v>23</v>
       </c>
       <c r="AX28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB28" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BC28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BD28" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE28" t="n">
-        <v>18.5</v>
+        <v>30</v>
       </c>
       <c r="BF28" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BG28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="G29" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J29" t="n">
         <v>3.55</v>
@@ -6019,16 +6019,16 @@
         <v>1.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O29" t="n">
         <v>1.33</v>
       </c>
       <c r="P29" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R29" t="n">
         <v>1.38</v>
@@ -6037,7 +6037,7 @@
         <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U29" t="n">
         <v>2.2</v>
@@ -6046,13 +6046,13 @@
         <v>1.35</v>
       </c>
       <c r="W29" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X29" t="n">
         <v>14</v>
       </c>
       <c r="Y29" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z29" t="n">
         <v>26</v>
@@ -6061,16 +6061,16 @@
         <v>70</v>
       </c>
       <c r="AB29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
         <v>15</v>
       </c>
       <c r="AE29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF29" t="n">
         <v>13.5</v>
@@ -6079,7 +6079,7 @@
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>55</v>
@@ -6088,43 +6088,43 @@
         <v>27</v>
       </c>
       <c r="AK29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL29" t="n">
         <v>36</v>
       </c>
       <c r="AM29" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN29" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO29" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP29" t="n">
         <v>13.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
         <v>60</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU29" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV29" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW29" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX29" t="n">
         <v>12.5</v>
@@ -6133,7 +6133,7 @@
         <v>10</v>
       </c>
       <c r="AZ29" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA29" t="n">
         <v>46</v>
@@ -6142,13 +6142,13 @@
         <v>24</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>34</v>
       </c>
       <c r="BE29" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BF29" t="n">
         <v>15.5</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="G30" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="H30" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="I30" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.46</v>
@@ -6219,46 +6219,46 @@
         <v>1.38</v>
       </c>
       <c r="P30" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R30" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T30" t="n">
         <v>1.86</v>
       </c>
       <c r="U30" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V30" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W30" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="X30" t="n">
         <v>12.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA30" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB30" t="n">
         <v>11</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD30" t="n">
         <v>12</v>
@@ -6270,7 +6270,7 @@
         <v>18.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>17.5</v>
@@ -6279,7 +6279,7 @@
         <v>42</v>
       </c>
       <c r="AJ30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AK30" t="n">
         <v>32</v>
@@ -6288,7 +6288,7 @@
         <v>44</v>
       </c>
       <c r="AM30" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN30" t="n">
         <v>34</v>
@@ -6303,7 +6303,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AS30" t="n">
         <v>38</v>
@@ -6318,13 +6318,13 @@
         <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX30" t="n">
         <v>18</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
@@ -6345,14 +6345,14 @@
         <v>80</v>
       </c>
       <c r="BF30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG30" t="n">
         <v>26</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="G31" t="n">
         <v>2.34</v>
-      </c>
-      <c r="G31" t="n">
-        <v>2.36</v>
       </c>
       <c r="H31" t="n">
         <v>3.75</v>
@@ -6395,10 +6395,10 @@
         <v>3.8</v>
       </c>
       <c r="J31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K31" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.3</v>
       </c>
       <c r="L31" t="n">
         <v>1.54</v>
@@ -6407,40 +6407,40 @@
         <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O31" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P31" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q31" t="n">
         <v>2.48</v>
       </c>
       <c r="R31" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V31" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W31" t="n">
         <v>1.74</v>
       </c>
       <c r="X31" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
         <v>24</v>
@@ -6449,13 +6449,13 @@
         <v>75</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC31" t="n">
         <v>7</v>
       </c>
       <c r="AD31" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE31" t="n">
         <v>55</v>
@@ -6491,7 +6491,7 @@
         <v>75</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ31" t="n">
         <v>10</v>
@@ -6503,7 +6503,7 @@
         <v>70</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
         <v>6.8</v>
@@ -6518,7 +6518,7 @@
         <v>12.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
         <v>20</v>
@@ -6530,7 +6530,7 @@
         <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
         <v>48</v>
@@ -6539,14 +6539,14 @@
         <v>120</v>
       </c>
       <c r="BF31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG31" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -6580,88 +6580,88 @@
         <v>2.06</v>
       </c>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I32" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J32" t="n">
         <v>3.45</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M32" t="n">
         <v>1.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O32" t="n">
         <v>1.34</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R32" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S32" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V32" t="n">
         <v>1.29</v>
       </c>
       <c r="W32" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X32" t="n">
         <v>16.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="n">
         <v>120</v>
       </c>
       <c r="AB32" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC32" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE32" t="n">
         <v>70</v>
       </c>
       <c r="AF32" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG32" t="n">
         <v>13</v>
       </c>
       <c r="AH32" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI32" t="n">
         <v>80</v>
@@ -6670,77 +6670,77 @@
         <v>29</v>
       </c>
       <c r="AK32" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM32" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN32" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO32" t="n">
         <v>80</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="AQ32" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="AR32" t="n">
         <v>22</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT32" t="n">
-        <v>7.4</v>
+        <v>3.3</v>
       </c>
       <c r="AU32" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>4.3</v>
       </c>
-      <c r="AX32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>3.9</v>
-      </c>
       <c r="BA32" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BD32" t="n">
         <v>4.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>11.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -6771,16 +6771,16 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="G33" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
       <c r="H33" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="I33" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="J33" t="n">
         <v>1.09</v>
@@ -6795,25 +6795,25 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="O33" t="n">
         <v>1.2</v>
       </c>
       <c r="P33" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="Q33" t="n">
         <v>1.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.18</v>
+        <v>1.42</v>
       </c>
       <c r="S33" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="U33" t="n">
         <v>1.11</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -6971,13 +6971,13 @@
         <v>1.59</v>
       </c>
       <c r="H34" t="n">
-        <v>5.1</v>
+        <v>1.09</v>
       </c>
       <c r="I34" t="n">
         <v>10</v>
       </c>
       <c r="J34" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K34" t="n">
         <v>5.6</v>
@@ -6995,22 +6995,22 @@
         <v>1.22</v>
       </c>
       <c r="P34" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q34" t="n">
         <v>1.61</v>
       </c>
       <c r="R34" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S34" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T34" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U34" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V34" t="n">
         <v>1.12</v>
@@ -7034,7 +7034,7 @@
         <v>970</v>
       </c>
       <c r="AC34" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AD34" t="n">
         <v>950</v>
@@ -7055,13 +7055,13 @@
         <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="AK34" t="n">
         <v>970</v>
       </c>
       <c r="AL34" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM34" t="n">
         <v>150</v>
@@ -7073,62 +7073,62 @@
         <v>160</v>
       </c>
       <c r="AP34" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AQ34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR34" t="n">
         <v>4.9</v>
       </c>
-      <c r="AR34" t="n">
-        <v>5.5</v>
-      </c>
       <c r="AS34" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="AT34" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AU34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY34" t="n">
         <v>4</v>
       </c>
-      <c r="AV34" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>3.85</v>
-      </c>
       <c r="AZ34" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD34" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G35" t="n">
         <v>7</v>
@@ -7192,16 +7192,16 @@
         <v>2.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R35" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="T35" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U35" t="n">
         <v>2.1</v>
@@ -7219,19 +7219,19 @@
         <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA35" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB35" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AC35" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD35" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE35" t="n">
         <v>18</v>
@@ -7240,13 +7240,13 @@
         <v>60</v>
       </c>
       <c r="AG35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ35" t="n">
         <v>170</v>
@@ -7255,74 +7255,74 @@
         <v>80</v>
       </c>
       <c r="AL35" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM35" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN35" t="n">
         <v>75</v>
       </c>
       <c r="AO35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AP35" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AR35" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AS35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU35" t="n">
         <v>4</v>
       </c>
-      <c r="AT35" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV35" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AW35" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AX35" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ35" t="n">
         <v>4.7</v>
       </c>
-      <c r="AY35" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BA35" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BB35" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BG35" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="G36" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="H36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
         <v>11</v>
       </c>
       <c r="J36" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K36" t="n">
         <v>5.9</v>
@@ -7380,7 +7380,7 @@
         <v>4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P36" t="n">
         <v>2.04</v>
@@ -7389,13 +7389,13 @@
         <v>1.65</v>
       </c>
       <c r="R36" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S36" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="T36" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U36" t="n">
         <v>1.9</v>
@@ -7419,7 +7419,7 @@
         <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AC36" t="n">
         <v>14</v>
@@ -7455,68 +7455,68 @@
         <v>180</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO36" t="n">
         <v>230</v>
       </c>
       <c r="AP36" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BB36" t="n">
         <v>3.7</v>
       </c>
-      <c r="AQ36" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AZ36" t="n">
+      <c r="BC36" t="n">
         <v>3.85</v>
       </c>
-      <c r="BA36" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BD36" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BF36" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="BG36" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-30 07:56:32</t>
+          <t>2026-04-30 10:20:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-30.xlsx
@@ -241,7 +241,7 @@
     <t>Genesis Huracan</t>
   </si>
   <si>
-    <t>2026-04-30 20:17:11</t>
+    <t>2026-04-30 22:47:27</t>
   </si>
 </sst>
 </file>
@@ -801,166 +801,166 @@
         <v>70</v>
       </c>
       <c r="F2">
-        <v>2.02</v>
+        <v>1.06</v>
       </c>
       <c r="G2">
-        <v>2.1</v>
+        <v>1.07</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>50</v>
       </c>
       <c r="I2">
-        <v>4.2</v>
+        <v>160</v>
       </c>
       <c r="J2">
-        <v>3.65</v>
+        <v>17</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>26</v>
       </c>
       <c r="L2">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.92</v>
+        <v>2.96</v>
       </c>
       <c r="Q2">
-        <v>2</v>
+        <v>1.47</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S2">
         <v>3.6</v>
       </c>
       <c r="T2">
-        <v>1.8</v>
+        <v>2.42</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>1.59</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W2">
-        <v>1.91</v>
+        <v>14</v>
       </c>
       <c r="X2">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>1000</v>
+      </c>
+      <c r="AE2">
+        <v>1000</v>
+      </c>
+      <c r="AF2">
+        <v>3.25</v>
+      </c>
+      <c r="AG2">
+        <v>6</v>
+      </c>
+      <c r="AH2">
+        <v>32</v>
+      </c>
+      <c r="AI2">
+        <v>200</v>
+      </c>
+      <c r="AJ2">
+        <v>6.8</v>
+      </c>
+      <c r="AK2">
+        <v>12.5</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>310</v>
+      </c>
+      <c r="AN2">
+        <v>10.5</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.2</v>
+      </c>
+      <c r="AR2">
+        <v>7.2</v>
+      </c>
+      <c r="AS2">
+        <v>7.2</v>
+      </c>
+      <c r="AT2">
+        <v>7.2</v>
+      </c>
+      <c r="AU2">
+        <v>7.2</v>
+      </c>
+      <c r="AV2">
+        <v>7.2</v>
+      </c>
+      <c r="AW2">
+        <v>7.2</v>
+      </c>
+      <c r="AX2">
+        <v>2.96</v>
+      </c>
+      <c r="AY2">
+        <v>4.9</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
+        <v>100</v>
+      </c>
+      <c r="BB2">
+        <v>4.8</v>
+      </c>
+      <c r="BC2">
         <v>8.4</v>
       </c>
-      <c r="AD2">
-        <v>17</v>
-      </c>
-      <c r="AE2">
-        <v>60</v>
-      </c>
-      <c r="AF2">
-        <v>14</v>
-      </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
-      <c r="AH2">
-        <v>22</v>
-      </c>
-      <c r="AI2">
-        <v>80</v>
-      </c>
-      <c r="AJ2">
-        <v>32</v>
-      </c>
-      <c r="AK2">
+      <c r="BD2">
         <v>30</v>
       </c>
-      <c r="AL2">
-        <v>50</v>
-      </c>
-      <c r="AM2">
+      <c r="BE2">
         <v>160</v>
       </c>
-      <c r="AN2">
-        <v>17</v>
-      </c>
-      <c r="AO2">
-        <v>60</v>
-      </c>
-      <c r="AP2">
-        <v>12</v>
-      </c>
-      <c r="AQ2">
-        <v>12.5</v>
-      </c>
-      <c r="AR2">
-        <v>10.5</v>
-      </c>
-      <c r="AS2">
-        <v>42</v>
-      </c>
-      <c r="AT2">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU2">
-        <v>7.4</v>
-      </c>
-      <c r="AV2">
-        <v>13.5</v>
-      </c>
-      <c r="AW2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX2">
-        <v>11</v>
-      </c>
-      <c r="AY2">
-        <v>9.4</v>
-      </c>
-      <c r="AZ2">
-        <v>16</v>
-      </c>
-      <c r="BA2">
-        <v>8.4</v>
-      </c>
-      <c r="BB2">
-        <v>21</v>
-      </c>
-      <c r="BC2">
-        <v>20</v>
-      </c>
-      <c r="BD2">
-        <v>14</v>
-      </c>
-      <c r="BE2">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF2">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="BG2">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="BH2" t="s">
         <v>75</v>
@@ -983,166 +983,166 @@
         <v>71</v>
       </c>
       <c r="F3">
-        <v>5.3</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>9.199999999999999</v>
+        <v>44</v>
       </c>
       <c r="H3">
-        <v>1.41</v>
+        <v>1.1</v>
       </c>
       <c r="I3">
-        <v>1.56</v>
+        <v>1.15</v>
       </c>
       <c r="J3">
-        <v>3.95</v>
+        <v>9.6</v>
       </c>
       <c r="K3">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="L3">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>4.5</v>
+        <v>15</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="P3">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="R3">
-        <v>1.53</v>
+        <v>1.98</v>
       </c>
       <c r="S3">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="T3">
+        <v>1.88</v>
+      </c>
+      <c r="U3">
+        <v>1.83</v>
+      </c>
+      <c r="V3">
+        <v>7.2</v>
+      </c>
+      <c r="W3">
+        <v>1.02</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>18.5</v>
+      </c>
+      <c r="Z3">
+        <v>9.4</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>34</v>
+      </c>
+      <c r="AD3">
+        <v>12</v>
+      </c>
+      <c r="AE3">
+        <v>13.5</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>110</v>
+      </c>
+      <c r="AH3">
+        <v>36</v>
+      </c>
+      <c r="AI3">
+        <v>40</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>490</v>
+      </c>
+      <c r="AL3">
+        <v>220</v>
+      </c>
+      <c r="AM3">
+        <v>180</v>
+      </c>
+      <c r="AN3">
+        <v>450</v>
+      </c>
+      <c r="AO3">
+        <v>3.8</v>
+      </c>
+      <c r="AP3">
+        <v>1.75</v>
+      </c>
+      <c r="AQ3">
+        <v>13</v>
+      </c>
+      <c r="AR3">
+        <v>6.4</v>
+      </c>
+      <c r="AS3">
+        <v>6</v>
+      </c>
+      <c r="AT3">
+        <v>1.75</v>
+      </c>
+      <c r="AU3">
+        <v>2.98</v>
+      </c>
+      <c r="AV3">
+        <v>2.56</v>
+      </c>
+      <c r="AW3">
+        <v>2.64</v>
+      </c>
+      <c r="AX3">
+        <v>1.75</v>
+      </c>
+      <c r="AY3">
         <v>1.72</v>
       </c>
-      <c r="U3">
-        <v>1.98</v>
-      </c>
-      <c r="V3">
-        <v>2.78</v>
-      </c>
-      <c r="W3">
-        <v>1.12</v>
-      </c>
-      <c r="X3">
-        <v>27</v>
-      </c>
-      <c r="Y3">
-        <v>12.5</v>
-      </c>
-      <c r="Z3">
-        <v>12</v>
-      </c>
-      <c r="AA3">
-        <v>15.5</v>
-      </c>
-      <c r="AB3">
-        <v>36</v>
-      </c>
-      <c r="AC3">
-        <v>13</v>
-      </c>
-      <c r="AD3">
-        <v>11.5</v>
-      </c>
-      <c r="AE3">
-        <v>17</v>
-      </c>
-      <c r="AF3">
-        <v>85</v>
-      </c>
-      <c r="AG3">
-        <v>34</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>32</v>
-      </c>
-      <c r="AJ3">
-        <v>250</v>
-      </c>
-      <c r="AK3">
-        <v>120</v>
-      </c>
-      <c r="AL3">
-        <v>95</v>
-      </c>
-      <c r="AM3">
-        <v>110</v>
-      </c>
-      <c r="AN3">
-        <v>120</v>
-      </c>
-      <c r="AO3">
-        <v>6.4</v>
-      </c>
-      <c r="AP3">
-        <v>4.7</v>
-      </c>
-      <c r="AQ3">
-        <v>4</v>
-      </c>
-      <c r="AR3">
-        <v>3.95</v>
-      </c>
-      <c r="AS3">
-        <v>4.3</v>
-      </c>
-      <c r="AT3">
-        <v>5.1</v>
-      </c>
-      <c r="AU3">
-        <v>4</v>
-      </c>
-      <c r="AV3">
-        <v>4.2</v>
-      </c>
-      <c r="AW3">
-        <v>4.8</v>
-      </c>
-      <c r="AX3">
-        <v>5.5</v>
-      </c>
-      <c r="AY3">
-        <v>5</v>
-      </c>
       <c r="AZ3">
-        <v>4.7</v>
+        <v>1.67</v>
       </c>
       <c r="BA3">
-        <v>5</v>
+        <v>1.68</v>
       </c>
       <c r="BB3">
-        <v>5.8</v>
+        <v>1.75</v>
       </c>
       <c r="BC3">
-        <v>5.6</v>
+        <v>1.75</v>
       </c>
       <c r="BD3">
-        <v>5.6</v>
+        <v>1.74</v>
       </c>
       <c r="BE3">
-        <v>5.6</v>
+        <v>1.73</v>
       </c>
       <c r="BF3">
-        <v>5.6</v>
+        <v>1.74</v>
       </c>
       <c r="BG3">
-        <v>3.25</v>
+        <v>2.28</v>
       </c>
       <c r="BH3" t="s">
         <v>75</v>
@@ -1165,61 +1165,61 @@
         <v>72</v>
       </c>
       <c r="F4">
+        <v>1.92</v>
+      </c>
+      <c r="G4">
+        <v>2.06</v>
+      </c>
+      <c r="H4">
         <v>1.1</v>
       </c>
-      <c r="G4">
-        <v>110</v>
-      </c>
-      <c r="H4">
-        <v>1.37</v>
-      </c>
       <c r="I4">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="J4">
         <v>1.1</v>
       </c>
       <c r="K4">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>1.98</v>
+      </c>
+      <c r="O4">
+        <v>1.06</v>
+      </c>
+      <c r="P4">
+        <v>2.74</v>
+      </c>
+      <c r="Q4">
+        <v>1.36</v>
+      </c>
+      <c r="R4">
+        <v>1.6</v>
+      </c>
+      <c r="S4">
+        <v>1.38</v>
+      </c>
+      <c r="T4">
         <v>1.04</v>
       </c>
-      <c r="N4">
-        <v>4.4</v>
-      </c>
-      <c r="O4">
-        <v>1.21</v>
-      </c>
-      <c r="P4">
-        <v>1.52</v>
-      </c>
-      <c r="Q4">
-        <v>1.21</v>
-      </c>
-      <c r="R4">
-        <v>1.19</v>
-      </c>
-      <c r="S4">
-        <v>1.05</v>
-      </c>
-      <c r="T4">
-        <v>1.76</v>
-      </c>
       <c r="U4">
-        <v>1.12</v>
+        <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="X4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
         <v>1000</v>
@@ -1276,55 +1276,55 @@
         <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>1.04</v>
+        <v>19.5</v>
       </c>
       <c r="AX4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>1.04</v>
+        <v>20</v>
       </c>
       <c r="BF4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="s">
         <v>75</v>
@@ -1347,166 +1347,166 @@
         <v>73</v>
       </c>
       <c r="F5">
-        <v>1.41</v>
+        <v>1.68</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="H5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>7.4</v>
+      </c>
+      <c r="J5">
+        <v>3.45</v>
+      </c>
+      <c r="K5">
+        <v>3.95</v>
+      </c>
+      <c r="L5">
+        <v>2.14</v>
+      </c>
+      <c r="M5">
+        <v>1.12</v>
+      </c>
+      <c r="N5">
+        <v>2.64</v>
+      </c>
+      <c r="O5">
+        <v>1.53</v>
+      </c>
+      <c r="P5">
+        <v>1.52</v>
+      </c>
+      <c r="Q5">
+        <v>2.74</v>
+      </c>
+      <c r="R5">
+        <v>1.17</v>
+      </c>
+      <c r="S5">
+        <v>3.4</v>
+      </c>
+      <c r="T5">
+        <v>2.42</v>
+      </c>
+      <c r="U5">
+        <v>1.53</v>
+      </c>
+      <c r="V5">
+        <v>1.16</v>
+      </c>
+      <c r="W5">
+        <v>2.24</v>
+      </c>
+      <c r="X5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y5">
+        <v>17.5</v>
+      </c>
+      <c r="Z5">
+        <v>80</v>
+      </c>
+      <c r="AA5">
+        <v>250</v>
+      </c>
+      <c r="AB5">
+        <v>6.2</v>
+      </c>
+      <c r="AC5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5">
+        <v>34</v>
+      </c>
+      <c r="AE5">
+        <v>170</v>
+      </c>
+      <c r="AF5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG5">
+        <v>14</v>
+      </c>
+      <c r="AH5">
+        <v>42</v>
+      </c>
+      <c r="AI5">
+        <v>210</v>
+      </c>
+      <c r="AJ5">
+        <v>21</v>
+      </c>
+      <c r="AK5">
+        <v>34</v>
+      </c>
+      <c r="AL5">
+        <v>90</v>
+      </c>
+      <c r="AM5">
+        <v>430</v>
+      </c>
+      <c r="AN5">
+        <v>24</v>
+      </c>
+      <c r="AO5">
+        <v>440</v>
+      </c>
+      <c r="AP5">
+        <v>7.4</v>
+      </c>
+      <c r="AQ5">
+        <v>13</v>
+      </c>
+      <c r="AR5">
+        <v>6.4</v>
+      </c>
+      <c r="AS5">
         <v>6.8</v>
       </c>
-      <c r="I5">
-        <v>9.4</v>
-      </c>
-      <c r="J5">
-        <v>4</v>
-      </c>
-      <c r="K5">
-        <v>5.8</v>
-      </c>
-      <c r="L5">
-        <v>1.32</v>
-      </c>
-      <c r="M5">
-        <v>1.04</v>
-      </c>
-      <c r="N5">
-        <v>4.2</v>
-      </c>
-      <c r="O5">
-        <v>1.22</v>
-      </c>
-      <c r="P5">
-        <v>2.18</v>
-      </c>
-      <c r="Q5">
-        <v>1.64</v>
-      </c>
-      <c r="R5">
-        <v>1.45</v>
-      </c>
-      <c r="S5">
-        <v>2.62</v>
-      </c>
-      <c r="T5">
-        <v>1.84</v>
-      </c>
-      <c r="U5">
-        <v>1.85</v>
-      </c>
-      <c r="V5">
-        <v>1.12</v>
-      </c>
-      <c r="W5">
-        <v>2.72</v>
-      </c>
-      <c r="X5">
-        <v>23</v>
-      </c>
-      <c r="Y5">
-        <v>950</v>
-      </c>
-      <c r="Z5">
-        <v>85</v>
-      </c>
-      <c r="AA5">
-        <v>310</v>
-      </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>12.5</v>
-      </c>
-      <c r="AD5">
-        <v>950</v>
-      </c>
-      <c r="AE5">
-        <v>150</v>
-      </c>
-      <c r="AF5">
-        <v>10</v>
-      </c>
-      <c r="AG5">
-        <v>11.5</v>
-      </c>
-      <c r="AH5">
-        <v>950</v>
-      </c>
-      <c r="AI5">
-        <v>120</v>
-      </c>
-      <c r="AJ5">
-        <v>14.5</v>
-      </c>
-      <c r="AK5">
-        <v>13</v>
-      </c>
-      <c r="AL5">
-        <v>38</v>
-      </c>
-      <c r="AM5">
-        <v>160</v>
-      </c>
-      <c r="AN5">
-        <v>7.2</v>
-      </c>
-      <c r="AO5">
-        <v>180</v>
-      </c>
-      <c r="AP5">
-        <v>5.5</v>
-      </c>
-      <c r="AQ5">
-        <v>5.8</v>
-      </c>
-      <c r="AR5">
-        <v>6.6</v>
-      </c>
-      <c r="AS5">
-        <v>7</v>
-      </c>
       <c r="AT5">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU5">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="AV5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW5">
         <v>6.8</v>
       </c>
       <c r="AX5">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="AY5">
-        <v>4.7</v>
+        <v>9.6</v>
       </c>
       <c r="AZ5">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA5">
         <v>6.8</v>
       </c>
       <c r="BB5">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="BC5">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD5">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF5">
-        <v>3.8</v>
+        <v>15</v>
       </c>
       <c r="BG5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="s">
         <v>75</v>
@@ -1529,166 +1529,166 @@
         <v>74</v>
       </c>
       <c r="F6">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K6">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L6">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="O6">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="P6">
         <v>2.08</v>
       </c>
       <c r="Q6">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
-        <v>2.68</v>
+        <v>2.36</v>
       </c>
       <c r="T6">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="U6">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="V6">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>8.4</v>
+      </c>
+      <c r="AC6">
+        <v>8.4</v>
+      </c>
+      <c r="AD6">
+        <v>26</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG6">
+        <v>7.6</v>
+      </c>
+      <c r="AH6">
+        <v>18</v>
+      </c>
+      <c r="AI6">
+        <v>85</v>
+      </c>
+      <c r="AJ6">
+        <v>21</v>
+      </c>
+      <c r="AK6">
         <v>23</v>
       </c>
-      <c r="Y6">
-        <v>950</v>
-      </c>
-      <c r="Z6">
-        <v>110</v>
-      </c>
-      <c r="AA6">
-        <v>1000</v>
-      </c>
-      <c r="AB6">
-        <v>9.6</v>
-      </c>
-      <c r="AC6">
-        <v>14</v>
-      </c>
-      <c r="AD6">
-        <v>950</v>
-      </c>
-      <c r="AE6">
-        <v>190</v>
-      </c>
-      <c r="AF6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>950</v>
-      </c>
-      <c r="AI6">
-        <v>150</v>
-      </c>
-      <c r="AJ6">
-        <v>970</v>
-      </c>
-      <c r="AK6">
-        <v>970</v>
-      </c>
       <c r="AL6">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AM6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN6">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AO6">
-        <v>250</v>
+        <v>180</v>
       </c>
       <c r="AP6">
         <v>4.5</v>
       </c>
       <c r="AQ6">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AR6">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AS6">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT6">
-        <v>3.85</v>
+        <v>5.4</v>
       </c>
       <c r="AU6">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
+        <v>14</v>
+      </c>
+      <c r="AW6">
+        <v>4.6</v>
+      </c>
+      <c r="AX6">
+        <v>5.7</v>
+      </c>
+      <c r="AY6">
         <v>5.6</v>
       </c>
-      <c r="AW6">
-        <v>5.7</v>
-      </c>
-      <c r="AX6">
-        <v>3.9</v>
-      </c>
-      <c r="AY6">
-        <v>4.1</v>
-      </c>
       <c r="AZ6">
-        <v>4.8</v>
+        <v>10</v>
       </c>
       <c r="BA6">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BB6">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BC6">
-        <v>4.4</v>
+        <v>13.5</v>
       </c>
       <c r="BD6">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>5.6</v>
+        <v>4.6</v>
       </c>
       <c r="BF6">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="s">
         <v>75</v>
